--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/GKIM website/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/GitHub Repos/GKIMWebsite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D42525C-3BB5-1444-8F13-26B76C629D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457AC588-17D3-7745-B8C2-ECB28EB8C85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="564">
   <si>
     <t>GKIM Digital — Multilingual Content Workbook</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>/de/</t>
-  </si>
-  <si>
-    <t>draft</t>
   </si>
   <si>
     <t>2</t>
@@ -2461,118 +2458,118 @@
       <c r="E3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>51</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2596,28 +2593,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
@@ -2625,25 +2622,25 @@
         <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
@@ -2651,129 +2648,129 @@
         <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2795,10 +2792,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>47</v>
@@ -2810,18 +2807,18 @@
         <v>54</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -2834,210 +2831,210 @@
     </row>
     <row r="3" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -3050,181 +3047,181 @@
     </row>
     <row r="11" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="E12" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="E13" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>205</v>
-      </c>
       <c r="D15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3237,152 +3234,152 @@
     </row>
     <row r="18" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="E18" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="D19" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="E20" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="E21" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="E22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3395,239 +3392,239 @@
     </row>
     <row r="24" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="D24" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C25" s="9" t="s">
+      <c r="D25" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="E25" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="E26" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="D27" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C28" s="9" t="s">
+      <c r="D28" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="E28" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="D29" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="E29" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E30" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="D31" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="E31" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3640,123 +3637,123 @@
     </row>
     <row r="33" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>265</v>
-      </c>
       <c r="D33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="I33" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="C34" s="9" t="s">
+      <c r="D34" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>268</v>
-      </c>
       <c r="E34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="C35" s="9" t="s">
+      <c r="D35" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="E35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="E36" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3769,326 +3766,326 @@
     </row>
     <row r="38" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="C38" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="E38" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="E39" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="9" t="s">
+      <c r="D40" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>283</v>
-      </c>
       <c r="E40" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C41" s="9" t="s">
+      <c r="D41" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="E41" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C42" s="9" t="s">
+      <c r="D42" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="E42" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C43" s="9" t="s">
+      <c r="D43" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="E43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C44" s="9" t="s">
+      <c r="D44" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="E44" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C45" s="9" t="s">
+      <c r="D45" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="E45" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C46" s="9" t="s">
+      <c r="D46" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="E46" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C47" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C47" s="9" t="s">
+      <c r="D47" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="E47" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C48" s="9" t="s">
+      <c r="D48" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="E48" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -4101,384 +4098,384 @@
     </row>
     <row r="50" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="C50" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="E50" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="E51" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C52" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C52" s="9" t="s">
+      <c r="D52" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C53" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="E53" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C54" s="9" t="s">
+      <c r="D54" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C55" s="9" t="s">
+      <c r="D55" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="E55" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C56" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C56" s="9" t="s">
+      <c r="D56" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C57" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C57" s="9" t="s">
+      <c r="D57" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="E57" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C58" s="9" t="s">
+      <c r="D58" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="E58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C59" s="9" t="s">
+      <c r="D59" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="E59" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C60" s="9" t="s">
+      <c r="D60" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="E60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C61" s="9" t="s">
+      <c r="D61" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="E61" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C62" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C62" s="9" t="s">
+      <c r="D62" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="E62" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
@@ -4491,152 +4488,152 @@
     </row>
     <row r="64" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="E64" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C65" s="9" t="s">
+      <c r="D65" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="E65" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C66" s="9" t="s">
+      <c r="D66" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="E66" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C67" s="9" t="s">
+      <c r="D67" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="E67" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C68" s="9" t="s">
+      <c r="D68" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="E68" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
@@ -4649,181 +4646,181 @@
     </row>
     <row r="70" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="C70" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="E70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="E71" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C72" s="9" t="s">
+      <c r="D72" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>371</v>
-      </c>
       <c r="E72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C73" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C73" s="9" t="s">
+      <c r="D73" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="E73" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="E74" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="E75" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
@@ -4836,239 +4833,239 @@
     </row>
     <row r="77" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="C77" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C77" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="E77" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="E78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C79" s="9" t="s">
+      <c r="D79" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="E79" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>389</v>
-      </c>
       <c r="E80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>391</v>
-      </c>
       <c r="E81" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="E82" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C83" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C83" s="9" t="s">
+      <c r="D83" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>396</v>
-      </c>
       <c r="E83" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C84" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C84" s="9" t="s">
+      <c r="D84" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>399</v>
-      </c>
       <c r="E84" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
@@ -5081,94 +5078,94 @@
     </row>
     <row r="86" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B86" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="C86" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C86" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>403</v>
-      </c>
       <c r="E86" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="C87" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B87" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="C87" s="9" t="s">
+      <c r="D87" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="E87" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="C88" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="B88" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="C88" s="9" t="s">
+      <c r="D88" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>409</v>
-      </c>
       <c r="E88" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
@@ -5181,152 +5178,152 @@
     </row>
     <row r="90" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="B90" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="C90" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C90" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>413</v>
-      </c>
       <c r="E90" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C91" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="B91" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="C91" s="9" t="s">
+      <c r="D91" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="E91" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C92" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="B92" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="C92" s="9" t="s">
+      <c r="D92" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>419</v>
-      </c>
       <c r="E92" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C93" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="B93" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="9" t="s">
+      <c r="D93" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="E93" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C94" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="B94" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="C94" s="9" t="s">
+      <c r="D94" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="E94" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
@@ -5339,326 +5336,326 @@
     </row>
     <row r="96" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="B96" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="B96" s="8" t="s">
-        <v>428</v>
-      </c>
       <c r="C96" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C97" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C97" s="9" t="s">
+      <c r="D97" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="E97" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C98" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C98" s="9" t="s">
+      <c r="D98" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="E98" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C99" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="B99" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C99" s="9" t="s">
+      <c r="D99" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="E99" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C100" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="B100" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C100" s="9" t="s">
+      <c r="D100" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>440</v>
-      </c>
       <c r="E100" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C101" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="B101" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C101" s="9" t="s">
+      <c r="D101" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="H101" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="I101" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B102" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="D102" s="2" t="s">
+      <c r="E102" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="F102" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="G102" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="H102" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="H102" s="2" t="s">
+      <c r="I102" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B103" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="D103" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="F103" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="F103" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="G103" s="2" t="s">
+      <c r="H103" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="H103" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="I103" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C104" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="B104" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C104" s="9" t="s">
+      <c r="D104" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="E104" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C105" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="B105" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C105" s="9" t="s">
+      <c r="D105" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="E105" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C106" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="B106" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C106" s="9" t="s">
+      <c r="D106" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="E106" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
@@ -5671,123 +5668,123 @@
     </row>
     <row r="108" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B108" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="C108" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="D108" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>473</v>
-      </c>
       <c r="E108" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="C109" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="B109" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="C109" s="9" t="s">
+      <c r="D109" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="E109" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="F110" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="G110" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="H110" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="I110" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="C111" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="C111" s="9" t="s">
+      <c r="D111" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="E111" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
@@ -5800,152 +5797,152 @@
     </row>
     <row r="113" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="B113" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="C113" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="C113" s="9" t="s">
+      <c r="D113" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="E113" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C114" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="B114" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C114" s="9" t="s">
+      <c r="D114" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="E114" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="E115" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C116" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="B116" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C116" s="9" t="s">
+      <c r="D116" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="E116" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C117" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="B117" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C117" s="9" t="s">
+      <c r="D117" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="E117" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B118" s="11"/>
       <c r="C118" s="11"/>
@@ -5958,42 +5955,42 @@
     </row>
     <row r="119" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="B119" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="C119" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="C119" s="9" t="s">
+      <c r="D119" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>501</v>
-      </c>
       <c r="E119" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C120" s="9" t="s">
         <v>502</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="C120" s="9" t="s">
-        <v>503</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>48</v>
@@ -6002,16 +5999,16 @@
         <v>54</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -6052,22 +6049,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6075,19 +6072,19 @@
         <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6095,99 +6092,99 @@
         <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -6210,31 +6207,31 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6242,28 +6239,28 @@
         <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6271,144 +6268,144 @@
         <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="H3" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="G4" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>562</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>548</v>
-      </c>
       <c r="E7" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="H7" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
   </sheetData>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/GitHub Repos/GKIMWebsite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457AC588-17D3-7745-B8C2-ECB28EB8C85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEF55A3-2FE8-A149-94E0-DD56C40FC364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="960">
   <si>
     <t>GKIM Digital — Multilingual Content Workbook</t>
   </si>
@@ -609,7 +609,13 @@
     <t>Design your AI-Native Business</t>
   </si>
   <si>
-    <t>— TO BE TRANSLATED —</t>
+    <t>Systematisch. Strukturiert. Zukunftsfähig.</t>
+  </si>
+  <si>
+    <t>Concevez-la. Construisez-la. Faites-la tourner.</t>
+  </si>
+  <si>
+    <t>Ontwerp het. Bouw het. Laat het draaien.</t>
   </si>
   <si>
     <t>设计您的AI原生企业</t>
@@ -627,6 +633,21 @@
     <t>Competitive advantage is no longer strategic. It's structural.</t>
   </si>
   <si>
+    <t>Die meisten KI-Initiativen erzeugen Werkzeuge. Wir bauen Unternehmen — von Grund auf konzipiert, um messbaren Wert zu schaffen.</t>
+  </si>
+  <si>
+    <t>La plupart des initiatives IA produisent des outils. Nous construisons des entreprises — conçues dès l'origine pour créer de la valeur mesurable.</t>
+  </si>
+  <si>
+    <t>De meeste AI-initiatieven leveren tools op. Wij bouwen bedrijven — ontworpen om meetbare waarde te creëren.</t>
+  </si>
+  <si>
+    <t>大多数AI项目只是构建工具。我们构建企业——从根本上设计，以创造可衡量的价值。</t>
+  </si>
+  <si>
+    <t>Hầu hết các sáng kiến AI chỉ tạo ra công cụ. Chúng tôi xây dựng doanh nghiệp — được thiết kế từ nền tảng để tạo ra giá trị đo lường được.</t>
+  </si>
+  <si>
     <t>hero.support</t>
   </si>
   <si>
@@ -636,6 +657,21 @@
     <t>We define the missing layer between strategy and engineering — how your business actually works as a system designed to create value.</t>
   </si>
   <si>
+    <t>GKIM arbeitet mit Gründern und Unternehmern zusammen, um KI-native Unternehmen zu entwerfen, aufzubauen und zu betreiben. Wir nutzen GEARS™ — unsere proprietäre Systemdesign-Methodik — um genau zu definieren, wie Ihr Unternehmen Wert schöpft, bevor eine Zeile Code geschrieben wird.</t>
+  </si>
+  <si>
+    <t>GKIM s'associe à des fondateurs et des opérateurs pour concevoir, construire et piloter des entreprises AI-natives. Nous utilisons GEARS™ — notre méthodologie propriétaire de conception systémique — pour définir précisément comment votre entreprise crée de la valeur, avant d'écrire une seule ligne de code.</t>
+  </si>
+  <si>
+    <t>GKIM werkt samen met founders en operators om AI-native bedrijven te ontwerpen, bouwen en beheren. We gebruiken GEARS™ — onze eigen systeemontwerpmethodologie — om exact te definiëren hoe uw bedrijf waarde creëert, vóórdat er een regel code wordt geschreven.</t>
+  </si>
+  <si>
+    <t>GKIM与创始人和运营者合作，设计、构建和运营AI原生企业。我们使用GEARS™——我们专有的系统设计方法论——在编写任何代码之前，精确定义您的企业如何创造价值。</t>
+  </si>
+  <si>
+    <t>GKIM hợp tác với các nhà sáng lập và nhà vận hành để thiết kế, xây dựng và vận hành các doanh nghiệp AI-native. Chúng tôi sử dụng GEARS™ — phương pháp thiết kế hệ thống độc quyền của mình — để xác định chính xác cách doanh nghiệp của bạn tạo ra giá trị trước khi viết bất kỳ dòng code nào.</t>
+  </si>
+  <si>
     <t>hero.cta.primary</t>
   </si>
   <si>
@@ -681,6 +717,21 @@
     <t>Business Systems Designed</t>
   </si>
   <si>
+    <t>Entworfene Unternehmenssysteme</t>
+  </si>
+  <si>
+    <t>Systèmes d'entreprise conçus</t>
+  </si>
+  <si>
+    <t>Bedrijfssystemen ontworpen</t>
+  </si>
+  <si>
+    <t>已设计业务系统</t>
+  </si>
+  <si>
+    <t>Hệ thống kinh doanh được thiết kế</t>
+  </si>
+  <si>
     <t>stat.2.label</t>
   </si>
   <si>
@@ -690,6 +741,21 @@
     <t>Daily Transactions Structured</t>
   </si>
   <si>
+    <t>Täglich strukturierte Transaktionen</t>
+  </si>
+  <si>
+    <t>Transactions structurées par jour</t>
+  </si>
+  <si>
+    <t>Dagelijks gestructureerde transacties</t>
+  </si>
+  <si>
+    <t>每日结构化交易</t>
+  </si>
+  <si>
+    <t>Giao dịch được cấu trúc hàng ngày</t>
+  </si>
+  <si>
     <t>stat.3.label</t>
   </si>
   <si>
@@ -699,6 +765,21 @@
     <t>Systems Delivered</t>
   </si>
   <si>
+    <t>Umgesetzte Systeme</t>
+  </si>
+  <si>
+    <t>Systèmes livrés</t>
+  </si>
+  <si>
+    <t>Systemen opgeleverd</t>
+  </si>
+  <si>
+    <t>已交付系统</t>
+  </si>
+  <si>
+    <t>Hệ thống đã triển khai</t>
+  </si>
+  <si>
     <t>stat.4.label</t>
   </si>
   <si>
@@ -708,6 +789,21 @@
     <t>Strategy &amp; Engineering Intersection</t>
   </si>
   <si>
+    <t>Jahre an der Schnittstelle von Strategie &amp; Engineering</t>
+  </si>
+  <si>
+    <t>Ans à l'intersection stratégie &amp; ingénierie</t>
+  </si>
+  <si>
+    <t>Jaar op het snijvlak van strategie &amp; engineering</t>
+  </si>
+  <si>
+    <t>年战略与工程交汇经验</t>
+  </si>
+  <si>
+    <t>Năm kinh nghiệm tại giao điểm chiến lược &amp; kỹ thuật</t>
+  </si>
+  <si>
     <t>stat.tag</t>
   </si>
   <si>
@@ -717,6 +813,21 @@
     <t>Designed for scale from day one — not refactored into it later.</t>
   </si>
   <si>
+    <t>Von Anfang an für Skalierung konzipiert — nicht nachträglich angepasst.</t>
+  </si>
+  <si>
+    <t>Conçu pour passer à l'échelle dès le premier jour — sans refonte ultérieure.</t>
+  </si>
+  <si>
+    <t>Ontworpen voor schaal vanaf dag één — niet achteraf aangepast.</t>
+  </si>
+  <si>
+    <t>从第一天起就为规模化而设计——而非事后改造。</t>
+  </si>
+  <si>
+    <t>Được thiết kế để mở rộng quy mô ngay từ ngày đầu — không phải cải tổ sau.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  SHIFT</t>
   </si>
   <si>
@@ -756,6 +867,21 @@
     <t>Businesses Are Starting to Look Different</t>
   </si>
   <si>
+    <t>Unternehmen beginnen, anders auszusehen</t>
+  </si>
+  <si>
+    <t>Les entreprises commencent à changer de visage</t>
+  </si>
+  <si>
+    <t>Bedrijven beginnen er anders uit te zien</t>
+  </si>
+  <si>
+    <t>企业正在开始呈现新面貌</t>
+  </si>
+  <si>
+    <t>Các doanh nghiệp đang bắt đầu trông khác đi</t>
+  </si>
+  <si>
     <t>shift.p1</t>
   </si>
   <si>
@@ -765,6 +891,21 @@
     <t>AI has given every company the same building speed.</t>
   </si>
   <si>
+    <t>Die meisten KI-Initiativen scheitern daran, echte Unternehmen zu werden.</t>
+  </si>
+  <si>
+    <t>La plupart des initiatives IA échouent à devenir de véritables entreprises.</t>
+  </si>
+  <si>
+    <t>De meeste AI-initiatieven slagen er niet in echte bedrijven te worden.</t>
+  </si>
+  <si>
+    <t>大多数AI项目未能转化为真正的企业。</t>
+  </si>
+  <si>
+    <t>Hầu hết các sáng kiến AI thất bại trong việc trở thành doanh nghiệp thực sự.</t>
+  </si>
+  <si>
     <t>shift.p2</t>
   </si>
   <si>
@@ -774,6 +915,21 @@
     <t>But speed doesn't matter if the business was never properly defined as a system. That's where most digital businesses break.</t>
   </si>
   <si>
+    <t>Unternehmen bauen Werkzeuge statt Systeme. Sie automatisieren ohne Struktur. Sie investieren in KI ohne klaren Bezug zu Umsatz, Marge oder betrieblicher Leistung.</t>
+  </si>
+  <si>
+    <t>Les organisations construisent des outils plutôt que des systèmes. Elles automatisent sans structure. Elles investissent dans l'IA sans lien clair avec le chiffre d'affaires, la marge ou la performance opérationnelle.</t>
+  </si>
+  <si>
+    <t>Organisaties bouwen tools in plaats van systemen. Ze automatiseren zonder structuur. Ze investeren in AI zonder duidelijke link naar omzet, marge of operationele prestaties.</t>
+  </si>
+  <si>
+    <t>组织构建工具而非系统。自动化缺乏结构。AI投资与收入、利润或运营绩效之间没有清晰的关联。</t>
+  </si>
+  <si>
+    <t>Các tổ chức xây dựng công cụ thay vì hệ thống. Họ tự động hóa mà không có cấu trúc. Họ đầu tư vào AI mà không có mối liên hệ rõ ràng với doanh thu, biên lợi nhuận hay hiệu suất vận hành.</t>
+  </si>
+  <si>
     <t>shift.p3</t>
   </si>
   <si>
@@ -781,6 +937,21 @@
   </si>
   <si>
     <t>The constraint has shifted from development — to definition.</t>
+  </si>
+  <si>
+    <t>Die Einschränkung ist nicht die Technologie. Sie ist die Fähigkeit, das Unternehmen zu gestalten und zu führen.</t>
+  </si>
+  <si>
+    <t>La contrainte n'est pas la technologie. C'est la capacité à concevoir et piloter l'entreprise.</t>
+  </si>
+  <si>
+    <t>De beperking is niet de technologie. Het is het vermogen om het bedrijf te ontwerpen en te runnen.</t>
+  </si>
+  <si>
+    <t>制约因素不是技术，而是设计和运营企业的能力。</t>
+  </si>
+  <si>
+    <t>Rào cản không phải là công nghệ. Đó là khả năng thiết kế và vận hành doanh nghiệp.</t>
   </si>
   <si>
     <t>shift.quote</t>
@@ -793,6 +964,26 @@
 Design is.</t>
   </si>
   <si>
+    <t>Geschwindigkeit ist kein Vorteil.
+Design ist es.</t>
+  </si>
+  <si>
+    <t>La vitesse n'est pas l'avantage.
+La conception l'est.</t>
+  </si>
+  <si>
+    <t>Snelheid is geen voordeel.
+Ontwerp wel.</t>
+  </si>
+  <si>
+    <t>速度不是优势。
+设计才是。</t>
+  </si>
+  <si>
+    <t>Tốc độ không phải là lợi thế.
+Thiết kế mới là.</t>
+  </si>
+  <si>
     <t>struct.label</t>
   </si>
   <si>
@@ -802,6 +993,21 @@
     <t>The core principle of GEARS™</t>
   </si>
   <si>
+    <t>Das Grundprinzip von GEARS™</t>
+  </si>
+  <si>
+    <t>Le principe fondateur de GEARS™</t>
+  </si>
+  <si>
+    <t>Het kernprincipe van GEARS™</t>
+  </si>
+  <si>
+    <t>GEARS™的核心原则</t>
+  </si>
+  <si>
+    <t>Nguyên tắc cốt lõi của GEARS™</t>
+  </si>
+  <si>
     <t>struct.quote</t>
   </si>
   <si>
@@ -811,6 +1017,21 @@
     <t>AI implements structure, not intention. Business models must be expressed as explicit hierarchies.</t>
   </si>
   <si>
+    <t>KI implementiert Struktur, keine Absicht. Geschäftsmodelle müssen als explizite Hierarchien ausgedrückt werden.</t>
+  </si>
+  <si>
+    <t>L'IA met en œuvre la structure, non l'intention. Les modèles d'entreprise doivent être exprimés sous forme de hiérarchies explicites.</t>
+  </si>
+  <si>
+    <t>AI implementeert structuur, niet intentie. Bedrijfsmodellen moeten worden uitgedrukt als expliciete hiërarchieën.</t>
+  </si>
+  <si>
+    <t>AI实现的是结构，而非意图。商业模式必须表达为明确的层次体系。</t>
+  </si>
+  <si>
+    <t>AI thực thi cấu trúc, không phải ý định. Các mô hình kinh doanh phải được biểu đạt dưới dạng phân cấp rõ ràng.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  VISION</t>
   </si>
   <si>
@@ -832,6 +1053,21 @@
     <t>The AI-Native Business</t>
   </si>
   <si>
+    <t>Das KI-native Unternehmen</t>
+  </si>
+  <si>
+    <t>L'entreprise AI-native</t>
+  </si>
+  <si>
+    <t>Het AI-native bedrijf</t>
+  </si>
+  <si>
+    <t>AI原生企业</t>
+  </si>
+  <si>
+    <t>Doanh nghiệp AI-native</t>
+  </si>
+  <si>
     <t>vision.fear.intro</t>
   </si>
   <si>
@@ -839,6 +1075,21 @@
   </si>
   <si>
     <t>AI raises legitimate questions. What happens to the people inside these businesses? What do customers experience? What does it mean for those who invest? The answer depends entirely on how the system is designed.</t>
+  </si>
+  <si>
+    <t>KI wirft berechtigte Fragen auf. Was geschieht mit den Menschen in diesen Unternehmen? Was erleben Kunden? Was bedeutet es für Investoren? Die Antwort hängt vollständig davon ab, wie das System gestaltet ist.</t>
+  </si>
+  <si>
+    <t>L'IA soulève des questions légitimes. Que se passe-t-il pour les personnes au sein de ces entreprises? Quelle est l'expérience des clients? Qu'est-ce que cela signifie pour les investisseurs? La réponse dépend entièrement de la façon dont le système est conçu.</t>
+  </si>
+  <si>
+    <t>AI roept legitieme vragen op. Wat gebeurt er met de mensen in deze bedrijven? Wat ervaren klanten? Wat betekent het voor investeerders? Het antwoord hangt volledig af van hoe het systeem is ontworpen.</t>
+  </si>
+  <si>
+    <t>AI提出了合理的问题。这些企业内部的人会发生什么？客户会有怎样的体验？对于投资者意味着什么？答案完全取决于系统的设计方式。</t>
+  </si>
+  <si>
+    <t>AI đặt ra những câu hỏi chính đáng. Điều gì xảy ra với những người bên trong các doanh nghiệp này? Khách hàng trải nghiệm gì? Điều đó có nghĩa gì với các nhà đầu tư? Câu trả lời hoàn toàn phụ thuộc vào cách hệ thống được thiết kế.</t>
   </si>
   <si>
     <t>vision.kl</t>
@@ -851,6 +1102,26 @@
 A better designed business.</t>
   </si>
   <si>
+    <t>Nicht bessere Software.
+Ein besser gestaltetes Unternehmen.</t>
+  </si>
+  <si>
+    <t>Pas de meilleurs logiciels.
+Une entreprise mieux conçue.</t>
+  </si>
+  <si>
+    <t>Niet betere software.
+Een beter ontworpen bedrijf.</t>
+  </si>
+  <si>
+    <t>不是更好的软件。
+而是更好设计的企业。</t>
+  </si>
+  <si>
+    <t>Không phải phần mềm tốt hơn.
+Mà là doanh nghiệp được thiết kế tốt hơn.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  GEARS</t>
   </si>
   <si>
@@ -863,12 +1134,42 @@
     <t>GEARS™ — Business-Led System Design</t>
   </si>
   <si>
+    <t>GEARS™ — Unternehmensgeführtes Systemdesign</t>
+  </si>
+  <si>
+    <t>GEARS™ — Conception de systèmes pilotée par l'entreprise</t>
+  </si>
+  <si>
+    <t>GEARS™ — Bedrijfsgestuurd systeemontwerp</t>
+  </si>
+  <si>
+    <t>GEARS™ — 以业务为导向的系统设计</t>
+  </si>
+  <si>
+    <t>GEARS™ — Thiết kế hệ thống dẫn dắt bởi doanh nghiệp</t>
+  </si>
+  <si>
     <t>gears.h</t>
   </si>
   <si>
     <t>Define the System Before You Build It</t>
   </si>
   <si>
+    <t>Definieren Sie das System, bevor Sie es bauen</t>
+  </si>
+  <si>
+    <t>Définir le système avant de le construire</t>
+  </si>
+  <si>
+    <t>Definieer het systeem voordat u het bouwt</t>
+  </si>
+  <si>
+    <t>在构建之前定义系统</t>
+  </si>
+  <si>
+    <t>Xác định hệ thống trước khi xây dựng</t>
+  </si>
+  <si>
     <t>gears.intro.p1</t>
   </si>
   <si>
@@ -878,6 +1179,21 @@
     <t>GEARS™ is the method GKIM uses to turn business ideas into functioning business engines.</t>
   </si>
   <si>
+    <t>GEARS™ ist die Methode, mit der GKIM Geschäftsideen in funktionierende Unternehmensmaschinen verwandelt.</t>
+  </si>
+  <si>
+    <t>GEARS™ est la méthode que GKIM utilise pour transformer des idées d'entreprise en systèmes opérationnels.</t>
+  </si>
+  <si>
+    <t>GEARS™ is de methode die GKIM gebruikt om bedrijfsideeën om te zetten in werkende bedrijfssystemen.</t>
+  </si>
+  <si>
+    <t>GEARS™是GKIM用于将商业理念转化为运作中的业务引擎的方法论。</t>
+  </si>
+  <si>
+    <t>GEARS™ là phương pháp GKIM sử dụng để biến các ý tưởng kinh doanh thành các động cơ doanh nghiệp hoạt động thực sự.</t>
+  </si>
+  <si>
     <t>gears.intro.p2</t>
   </si>
   <si>
@@ -887,6 +1203,21 @@
     <t>It does not start with features. It starts with: how the business must actually work to create value.</t>
   </si>
   <si>
+    <t>Es beginnt nicht mit Funktionen. Es beginnt mit: Wie muss das Unternehmen tatsächlich funktionieren, um Wert zu schaffen.</t>
+  </si>
+  <si>
+    <t>Il ne commence pas par les fonctionnalités. Il commence par: comment l'entreprise doit-elle réellement fonctionner pour créer de la valeur.</t>
+  </si>
+  <si>
+    <t>Het begint niet met features. Het begint met: hoe moet het bedrijf daadwerkelijk werken om waarde te creëren.</t>
+  </si>
+  <si>
+    <t>它不从功能开始，而是从这个问题开始：企业必须如何实际运作才能创造价值。</t>
+  </si>
+  <si>
+    <t>Nó không bắt đầu từ các tính năng. Nó bắt đầu từ câu hỏi: doanh nghiệp phải hoạt động như thế nào để tạo ra giá trị.</t>
+  </si>
+  <si>
     <t>gears.intro.p3</t>
   </si>
   <si>
@@ -896,6 +1227,21 @@
     <t>Each gear is a named unit of value creation — defined by what it produces, not how it operates.</t>
   </si>
   <si>
+    <t>Jedes Zahnrad ist eine benannte Einheit der Wertschöpfung — definiert durch das, was es produziert, nicht wie es funktioniert.</t>
+  </si>
+  <si>
+    <t>Chaque engrenage est une unité nommée de création de valeur — définie par ce qu'elle produit, non par son mode de fonctionnement.</t>
+  </si>
+  <si>
+    <t>Elk tandwiel is een benoemde eenheid van waardecreatie — gedefinieerd door wat het produceert, niet hoe het werkt.</t>
+  </si>
+  <si>
+    <t>每个齿轮都是一个命名的价值创造单元——由其产出定义，而非运作方式。</t>
+  </si>
+  <si>
+    <t>Mỗi gear là một đơn vị tạo giá trị được đặt tên — được định nghĩa bởi những gì nó tạo ra, không phải cách nó vận hành.</t>
+  </si>
+  <si>
     <t>gears.step1.title</t>
   </si>
   <si>
@@ -905,6 +1251,21 @@
     <t>Discover — Define the Business Engine</t>
   </si>
   <si>
+    <t>Entdecken — Das Unternehmensmodell definieren</t>
+  </si>
+  <si>
+    <t>Découvrir — Définir le moteur de l'entreprise</t>
+  </si>
+  <si>
+    <t>Ontdekken — Definieer de bedrijfsmotor</t>
+  </si>
+  <si>
+    <t>发现——定义业务引擎</t>
+  </si>
+  <si>
+    <t>Khám phá — Xác định động cơ doanh nghiệp</t>
+  </si>
+  <si>
     <t>gears.step2.title</t>
   </si>
   <si>
@@ -914,6 +1275,21 @@
     <t>Design — Structure the System</t>
   </si>
   <si>
+    <t>Gestalten — Das System strukturieren</t>
+  </si>
+  <si>
+    <t>Concevoir — Structurer le système</t>
+  </si>
+  <si>
+    <t>Ontwerpen — Structureer het systeem</t>
+  </si>
+  <si>
+    <t>设计——构建系统结构</t>
+  </si>
+  <si>
+    <t>Thiết kế — Cấu trúc hóa hệ thống</t>
+  </si>
+  <si>
     <t>gears.step3.title</t>
   </si>
   <si>
@@ -923,6 +1299,21 @@
     <t>Deliver — Build-Ready Outputs</t>
   </si>
   <si>
+    <t>Liefern — Baufertige Ergebnisse</t>
+  </si>
+  <si>
+    <t>Livrer — Des livrables prêts à construire</t>
+  </si>
+  <si>
+    <t>Opleveren — Bouwklare resultaten</t>
+  </si>
+  <si>
+    <t>交付——可构建的成果</t>
+  </si>
+  <si>
+    <t>Bàn giao — Kết quả sẵn sàng để xây dựng</t>
+  </si>
+  <si>
     <t>gears.kl</t>
   </si>
   <si>
@@ -932,6 +1323,21 @@
     <t>GEARS™ does not stop at insight. It produces the structure required to build.</t>
   </si>
   <si>
+    <t>GEARS™ hört nicht bei der Erkenntnis auf. Es liefert die Struktur, die zum Aufbau erforderlich ist.</t>
+  </si>
+  <si>
+    <t>GEARS™ ne s'arrête pas à la compréhension. Il produit la structure nécessaire à la construction.</t>
+  </si>
+  <si>
+    <t>GEARS™ stopt niet bij inzicht. Het levert de structuur die nodig is om te bouwen.</t>
+  </si>
+  <si>
+    <t>GEARS™不止步于洞察。它提供构建所需的结构。</t>
+  </si>
+  <si>
+    <t>GEARS™ không dừng lại ở sự hiểu biết. Nó tạo ra cấu trúc cần thiết để xây dựng.</t>
+  </si>
+  <si>
     <t>gears.naming.title</t>
   </si>
   <si>
@@ -941,6 +1347,21 @@
     <t>Every gear is named with a verb and a noun. Precisely.</t>
   </si>
   <si>
+    <t>Jedes Zahnrad wird mit einem Verb und einem Substantiv benannt. Präzise.</t>
+  </si>
+  <si>
+    <t>Chaque engrenage est nommé avec un verbe et un nom. Précisément.</t>
+  </si>
+  <si>
+    <t>Elk tandwiel krijgt een naam met een werkwoord en een zelfstandig naamwoord. Precies.</t>
+  </si>
+  <si>
+    <t>每个齿轮都以动词和名词精确命名。</t>
+  </si>
+  <si>
+    <t>Mỗi gear được đặt tên bằng một động từ và một danh từ. Chính xác.</t>
+  </si>
+  <si>
     <t>gears.naming.body</t>
   </si>
   <si>
@@ -950,6 +1371,21 @@
     <t>A gear name is a contract. It declares what the gear does and what it acts on. Vague names hide complexity. Precise names make the system legible — and therefore buildable.</t>
   </si>
   <si>
+    <t>Ein Zahnrad-Name ist ein Vertrag. Er erklärt, was das Zahnrad tut und worauf es einwirkt. Vage Namen verbergen Komplexität. Präzise Namen machen das System lesbar — und damit baubar.</t>
+  </si>
+  <si>
+    <t>Un nom d'engrenage est un contrat. Il déclare ce que l'engrenage fait et sur quoi il agit. Les noms vagues cachent la complexité. Les noms précis rendent le système lisible — et donc constructible.</t>
+  </si>
+  <si>
+    <t>Een tandwielnaam is een contract. Het verklaart wat het tandwiel doet en waarop het inwerkt. Vage namen verbergen complexiteit. Precieze namen maken het systeem leesbaar — en daardoor bouwbaar.</t>
+  </si>
+  <si>
+    <t>齿轮名称是一份合约。它声明齿轮做什么以及作用于什么。模糊的名称隐藏复杂性。精确的名称使系统易于理解——从而可以构建。</t>
+  </si>
+  <si>
+    <t>Tên gear là một hợp đồng. Nó tuyên bố gear làm gì và tác động lên cái gì. Tên mơ hồ che giấu sự phức tạp. Tên chính xác làm cho hệ thống dễ đọc — và do đó có thể xây dựng được.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  OUTPUTS</t>
   </si>
   <si>
@@ -960,6 +1396,21 @@
   </si>
   <si>
     <t>What You Actually Get</t>
+  </si>
+  <si>
+    <t>Was Sie tatsächlich erhalten</t>
+  </si>
+  <si>
+    <t>Ce que vous obtenez réellement</t>
+  </si>
+  <si>
+    <t>Wat u daadwerkelijk krijgt</t>
+  </si>
+  <si>
+    <t>您实际获得的内容</t>
+  </si>
+  <si>
+    <t>Những gì bạn thực sự nhận được</t>
   </si>
   <si>
     <t>outputs.h</t>
@@ -969,6 +1420,26 @@
 Production.</t>
   </si>
   <si>
+    <t>Keine Beratung.
+Produktion.</t>
+  </si>
+  <si>
+    <t>Pas de conseil.
+De la production.</t>
+  </si>
+  <si>
+    <t>Geen advies.
+Productie.</t>
+  </si>
+  <si>
+    <t>不是咨询。
+而是交付。</t>
+  </si>
+  <si>
+    <t>Không phải tư vấn.
+Mà là sản xuất.</t>
+  </si>
+  <si>
     <t>outputs.intro.p1</t>
   </si>
   <si>
@@ -978,6 +1449,21 @@
     <t>Each engagement produces a set of connected outputs that together define how your business works as a system.</t>
   </si>
   <si>
+    <t>Jedes Engagement erzeugt eine Reihe verbundener Ergebnisse, die zusammen definieren, wie Ihr Unternehmen als System funktioniert.</t>
+  </si>
+  <si>
+    <t>Chaque engagement produit un ensemble de livrables connectés qui définissent ensemble le fonctionnement de votre entreprise en tant que système.</t>
+  </si>
+  <si>
+    <t>Elke opdracht levert een reeks verbonden resultaten op die samen definiëren hoe uw bedrijf als systeem werkt.</t>
+  </si>
+  <si>
+    <t>每次合作都会产生一系列相互关联的成果，共同定义您的企业作为系统的运作方式。</t>
+  </si>
+  <si>
+    <t>Mỗi cam kết tạo ra một bộ kết quả có liên kết với nhau, cùng nhau xác định cách doanh nghiệp của bạn hoạt động như một hệ thống.</t>
+  </si>
+  <si>
     <t>outputs.intro.p2</t>
   </si>
   <si>
@@ -987,6 +1473,21 @@
     <t>The hierarchy is the source of truth. Everything else is a projection of it.</t>
   </si>
   <si>
+    <t>Die Hierarchie ist die Quelle der Wahrheit. Alles andere ist eine Projektion davon.</t>
+  </si>
+  <si>
+    <t>La hiérarchie est la source de vérité. Tout le reste en est une projection.</t>
+  </si>
+  <si>
+    <t>De hiërarchie is de bron van waarheid. Al het andere is een projectie daarvan.</t>
+  </si>
+  <si>
+    <t>层次结构是真理的来源。其他一切都是它的投影。</t>
+  </si>
+  <si>
+    <t>Hệ thống phân cấp là nguồn của sự thật. Mọi thứ khác đều là hình chiếu của nó.</t>
+  </si>
+  <si>
     <t>output.1.label</t>
   </si>
   <si>
@@ -996,6 +1497,21 @@
     <t>Output 01 — Capability Map</t>
   </si>
   <si>
+    <t>Ergebnis 01 — Fähigkeitskarte</t>
+  </si>
+  <si>
+    <t>Livrable 01 — Cartographie des capacités</t>
+  </si>
+  <si>
+    <t>Resultaat 01 — Capaciteitskaart</t>
+  </si>
+  <si>
+    <t>成果01——能力图谱</t>
+  </si>
+  <si>
+    <t>Kết quả 01 — Bản đồ năng lực</t>
+  </si>
+  <si>
     <t>output.1.title</t>
   </si>
   <si>
@@ -1005,6 +1521,21 @@
     <t>Business Engine Definition</t>
   </si>
   <si>
+    <t>Definition der Unternehmensmaschine</t>
+  </si>
+  <si>
+    <t>Définition du moteur d'entreprise</t>
+  </si>
+  <si>
+    <t>Definitie van de bedrijfsmotor</t>
+  </si>
+  <si>
+    <t>业务引擎定义</t>
+  </si>
+  <si>
+    <t>Định nghĩa động cơ doanh nghiệp</t>
+  </si>
+  <si>
     <t>output.2.label</t>
   </si>
   <si>
@@ -1014,6 +1545,21 @@
     <t>Output 02 — Workflow Architecture</t>
   </si>
   <si>
+    <t>Ergebnis 02 — Workflow-Architektur</t>
+  </si>
+  <si>
+    <t>Livrable 02 — Architecture des flux de travail</t>
+  </si>
+  <si>
+    <t>Resultaat 02 — Workflowarchitectuur</t>
+  </si>
+  <si>
+    <t>成果02——工作流架构</t>
+  </si>
+  <si>
+    <t>Kết quả 02 — Kiến trúc quy trình làm việc</t>
+  </si>
+  <si>
     <t>output.2.title</t>
   </si>
   <si>
@@ -1023,6 +1569,21 @@
     <t>Process &amp; Authority Design</t>
   </si>
   <si>
+    <t>Prozess- &amp; Autoritätsdesign</t>
+  </si>
+  <si>
+    <t>Conception des processus &amp; des responsabilités</t>
+  </si>
+  <si>
+    <t>Proces- &amp; bevoegdheidsontwerp</t>
+  </si>
+  <si>
+    <t>流程与权限设计</t>
+  </si>
+  <si>
+    <t>Thiết kế quy trình &amp; thẩm quyền</t>
+  </si>
+  <si>
     <t>output.3.title</t>
   </si>
   <si>
@@ -1032,6 +1593,21 @@
     <t>Decision Structures &amp; Rules</t>
   </si>
   <si>
+    <t>Entscheidungsstrukturen &amp; Regeln</t>
+  </si>
+  <si>
+    <t>Structures de décision &amp; règles</t>
+  </si>
+  <si>
+    <t>Beslissingsstructuren &amp; regels</t>
+  </si>
+  <si>
+    <t>决策结构与规则</t>
+  </si>
+  <si>
+    <t>Cấu trúc quyết định &amp; quy tắc</t>
+  </si>
+  <si>
     <t>output.4.title</t>
   </si>
   <si>
@@ -1041,6 +1617,21 @@
     <t>Build Specification (PRD)</t>
   </si>
   <si>
+    <t>Bauspezifikation (PRD)</t>
+  </si>
+  <si>
+    <t>Spécification de construction (PRD)</t>
+  </si>
+  <si>
+    <t>Bouwspecificatie (PRD)</t>
+  </si>
+  <si>
+    <t>构建规范（PRD）</t>
+  </si>
+  <si>
+    <t>Đặc tả xây dựng (PRD)</t>
+  </si>
+  <si>
     <t>output.5.title</t>
   </si>
   <si>
@@ -1050,6 +1641,21 @@
     <t>KPIs &amp; Observability Design</t>
   </si>
   <si>
+    <t>KPIs &amp; Observability-Design</t>
+  </si>
+  <si>
+    <t>KPIs &amp; conception de l'observabilité</t>
+  </si>
+  <si>
+    <t>KPI's &amp; observabiliteitsontwerp</t>
+  </si>
+  <si>
+    <t>KPI与可观测性设计</t>
+  </si>
+  <si>
+    <t>KPI &amp; thiết kế khả năng quan sát</t>
+  </si>
+  <si>
     <t>output.6.title</t>
   </si>
   <si>
@@ -1059,6 +1665,21 @@
     <t>Machine-Consumable System Spec</t>
   </si>
   <si>
+    <t>Maschinenlesbare Systemspezifikation</t>
+  </si>
+  <si>
+    <t>Spécification système consommable par machine</t>
+  </si>
+  <si>
+    <t>Machineleesbare systeemspecificatie</t>
+  </si>
+  <si>
+    <t>机器可消费的系统规范</t>
+  </si>
+  <si>
+    <t>Đặc tả hệ thống có thể tiêu thụ bằng máy</t>
+  </si>
+  <si>
     <t>outputs.foot</t>
   </si>
   <si>
@@ -1068,6 +1689,21 @@
     <t>For most teams, it's the first time the business becomes something that can actually be tested and reasoned about.</t>
   </si>
   <si>
+    <t>Für die meisten Teams ist es das erste Mal, dass das Unternehmen zu etwas wird, das tatsächlich getestet und durchdacht werden kann.</t>
+  </si>
+  <si>
+    <t>Pour la plupart des équipes, c'est la première fois que l'entreprise devient quelque chose qui peut réellement être testé et raisonné.</t>
+  </si>
+  <si>
+    <t>Voor de meeste teams is het de eerste keer dat het bedrijf iets wordt dat daadwerkelijk getest en beredeneerd kan worden.</t>
+  </si>
+  <si>
+    <t>对于大多数团队来说，这是企业第一次成为可以真正测试和推理的事物。</t>
+  </si>
+  <si>
+    <t>Đối với hầu hết các đội nhóm, đây là lần đầu tiên doanh nghiệp trở thành thứ gì đó có thể được kiểm tra và lý luận thực sự.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  CASE</t>
   </si>
   <si>
@@ -1080,6 +1716,21 @@
     <t>Proven in Real Systems</t>
   </si>
   <si>
+    <t>In echten Systemen bewährt</t>
+  </si>
+  <si>
+    <t>Éprouvé dans des systèmes réels</t>
+  </si>
+  <si>
+    <t>Bewezen in echte systemen</t>
+  </si>
+  <si>
+    <t>在真实系统中得到验证</t>
+  </si>
+  <si>
+    <t>Đã được chứng minh trong các hệ thống thực tế</t>
+  </si>
+  <si>
     <t>case.tag</t>
   </si>
   <si>
@@ -1089,6 +1740,21 @@
     <t>Flagship Case Study</t>
   </si>
   <si>
+    <t>Leitfallstudie</t>
+  </si>
+  <si>
+    <t>Étude de cas phare</t>
+  </si>
+  <si>
+    <t>Belangrijkste case study</t>
+  </si>
+  <si>
+    <t>旗舰案例研究</t>
+  </si>
+  <si>
+    <t>Nghiên cứu điển hình hàng đầu</t>
+  </si>
+  <si>
     <t>case.h</t>
   </si>
   <si>
@@ -1098,6 +1764,21 @@
     <t>Designing a $1B Genetics Business System</t>
   </si>
   <si>
+    <t>Gestaltung eines Genetikunternehmenssystems im Milliardenmaßstab</t>
+  </si>
+  <si>
+    <t>Concevoir un système d'entreprise en génétique à l'échelle du milliard</t>
+  </si>
+  <si>
+    <t>Ontwerpen van een genetica bedrijfssysteem op miljardenschaal</t>
+  </si>
+  <si>
+    <t>设计一个十亿美元规模的基因企业系统</t>
+  </si>
+  <si>
+    <t>Thiết kế hệ thống doanh nghiệp di truyền học tỷ đô</t>
+  </si>
+  <si>
     <t>case.sub</t>
   </si>
   <si>
@@ -1107,6 +1788,21 @@
     <t>How a complex, multi-actor healthcare platform was structured to scale — before volume exposed its weaknesses.</t>
   </si>
   <si>
+    <t>Wie eine komplexe, mehrschichtige Gesundheitsplattform so strukturiert wurde, dass sie skaliert — bevor das Volumen ihre Schwächen aufdeckte.</t>
+  </si>
+  <si>
+    <t>Comment une plateforme de santé complexe et multi-acteurs a été structurée pour passer à l'échelle — avant que le volume n'expose ses faiblesses.</t>
+  </si>
+  <si>
+    <t>Hoe een complex, multi-actor gezondheidszorgplatform werd gestructureerd om te schalen — voordat het volume de zwakke punten blootlegde.</t>
+  </si>
+  <si>
+    <t>一个复杂的多方医疗健康平台如何被结构化以实现规模化——在规模暴露其弱点之前。</t>
+  </si>
+  <si>
+    <t>Cách một nền tảng chăm sóc sức khỏe phức tạp, đa tác nhân được cấu trúc để mở rộng quy mô — trước khi khối lượng công việc phơi bày những điểm yếu của nó.</t>
+  </si>
+  <si>
     <t>case.kl</t>
   </si>
   <si>
@@ -1116,6 +1812,21 @@
     <t>The system scaled because it was designed to work — not because it was iterated into shape.</t>
   </si>
   <si>
+    <t>Das System skalierte, weil es so konzipiert wurde, dass es funktioniert — nicht weil es schrittweise verbessert wurde.</t>
+  </si>
+  <si>
+    <t>Le système a pu passer à l'échelle parce qu'il a été conçu pour fonctionner — non pas parce qu'il a été amélioré par itérations.</t>
+  </si>
+  <si>
+    <t>Het systeem kon schalen omdat het ontworpen was om te werken — niet omdat het stapsgewijs werd verbeterd.</t>
+  </si>
+  <si>
+    <t>系统得以扩展，是因为它被设计为能够运作——而不是通过不断迭代改进而成。</t>
+  </si>
+  <si>
+    <t>Hệ thống đã mở rộng quy mô vì nó được thiết kế để hoạt động — không phải vì nó được cải thiện dần dần.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  FOR</t>
   </si>
   <si>
@@ -1128,12 +1839,42 @@
     <t>Who This Is For</t>
   </si>
   <si>
+    <t>Für wen das ist</t>
+  </si>
+  <si>
+    <t>Pour qui c'est fait</t>
+  </si>
+  <si>
+    <t>Voor wie dit is</t>
+  </si>
+  <si>
+    <t>适合谁</t>
+  </si>
+  <si>
+    <t>Dành cho ai</t>
+  </si>
+  <si>
     <t>for.h</t>
   </si>
   <si>
     <t>Built for the people who have to get it right</t>
   </si>
   <si>
+    <t>Für die Menschen, die es richtig machen müssen</t>
+  </si>
+  <si>
+    <t>Conçu pour ceux qui doivent bien faire les choses</t>
+  </si>
+  <si>
+    <t>Gebouwd voor de mensen die het goed moeten doen</t>
+  </si>
+  <si>
+    <t>专为那些必须做对的人而建</t>
+  </si>
+  <si>
+    <t>Được xây dựng cho những người phải làm đúng</t>
+  </si>
+  <si>
     <t>for.founders.role</t>
   </si>
   <si>
@@ -1143,6 +1884,18 @@
     <t>Founders</t>
   </si>
   <si>
+    <t>Gründer</t>
+  </si>
+  <si>
+    <t>Fondateurs</t>
+  </si>
+  <si>
+    <t>创始人</t>
+  </si>
+  <si>
+    <t>Nhà sáng lập</t>
+  </si>
+  <si>
     <t>for.founders.body</t>
   </si>
   <si>
@@ -1152,18 +1905,60 @@
     <t>Turn ideas into structured, buildable systems. Build the right business, not just fast software.</t>
   </si>
   <si>
+    <t>Ideen in strukturierte, baufertige Systeme verwandeln. Das richtige Unternehmen aufbauen, nicht nur schnelle Software.</t>
+  </si>
+  <si>
+    <t>Transformer des idées en systèmes structurés et constructibles. Bâtir la bonne entreprise, pas seulement un logiciel rapide.</t>
+  </si>
+  <si>
+    <t>Ideeën omzetten in gestructureerde, bouwklare systemen. Het juiste bedrijf bouwen, niet alleen snelle software.</t>
+  </si>
+  <si>
+    <t>将想法转化为结构化的可构建系统。构建正确的企业，而不仅仅是快速的软件。</t>
+  </si>
+  <si>
+    <t>Biến ý tưởng thành các hệ thống có cấu trúc, sẵn sàng để xây dựng. Xây dựng doanh nghiệp đúng đắn, không chỉ là phần mềm nhanh.</t>
+  </si>
+  <si>
     <t>for.operators.role</t>
   </si>
   <si>
     <t>Operators</t>
   </si>
   <si>
+    <t>Betreiber</t>
+  </si>
+  <si>
+    <t>Opérateurs</t>
+  </si>
+  <si>
+    <t>运营者</t>
+  </si>
+  <si>
+    <t>Nhà vận hành</t>
+  </si>
+  <si>
     <t>for.investors.role</t>
   </si>
   <si>
     <t>Investors &amp; PE</t>
   </si>
   <si>
+    <t>Investoren &amp; PE</t>
+  </si>
+  <si>
+    <t>Investisseurs &amp; PE</t>
+  </si>
+  <si>
+    <t>Investeerders &amp; PE</t>
+  </si>
+  <si>
+    <t>投资者与私募股权</t>
+  </si>
+  <si>
+    <t>Nhà đầu tư &amp; PE</t>
+  </si>
+  <si>
     <t xml:space="preserve">  LADDER</t>
   </si>
   <si>
@@ -1174,6 +1969,21 @@
   </si>
   <si>
     <t>How We Work</t>
+  </si>
+  <si>
+    <t>Wie wir arbeiten</t>
+  </si>
+  <si>
+    <t>Comment nous travaillons</t>
+  </si>
+  <si>
+    <t>Hoe wij werken</t>
+  </si>
+  <si>
+    <t>我们的工作方式</t>
+  </si>
+  <si>
+    <t>Cách chúng tôi làm việc</t>
   </si>
   <si>
     <t>ladder.h</t>
@@ -1183,6 +1993,26 @@
 Go as far as you need.</t>
   </si>
   <si>
+    <t>Beginnen Sie überall.
+Gehen Sie so weit wie nötig.</t>
+  </si>
+  <si>
+    <t>Commencez où vous voulez.
+Allez aussi loin que nécessaire.</t>
+  </si>
+  <si>
+    <t>Begin waar u wilt.
+Ga zo ver als nodig.</t>
+  </si>
+  <si>
+    <t>从任何地方开始。
+走到您需要的地方。</t>
+  </si>
+  <si>
+    <t>Bắt đầu từ bất cứ đâu.
+Đi xa đến mức bạn cần.</t>
+  </si>
+  <si>
     <t>ladder.sub</t>
   </si>
   <si>
@@ -1192,24 +2022,84 @@
     <t>Most clients begin with a single session. No commitment beyond that.</t>
   </si>
   <si>
+    <t>Die meisten Kunden beginnen mit einer einzigen Sitzung. Keine Verpflichtung darüber hinaus.</t>
+  </si>
+  <si>
+    <t>La plupart de nos clients commencent par une seule session. Sans engagement au-delà.</t>
+  </si>
+  <si>
+    <t>De meeste klanten beginnen met één sessie. Geen verplichtingen daarna.</t>
+  </si>
+  <si>
+    <t>大多数客户从单次会议开始。无需进一步承诺。</t>
+  </si>
+  <si>
+    <t>Hầu hết khách hàng bắt đầu bằng một buổi làm việc duy nhất. Không có cam kết nào hơn thế.</t>
+  </si>
+  <si>
     <t>ladder.step1.title</t>
   </si>
   <si>
     <t>Discovery Session</t>
   </si>
   <si>
+    <t>Discovery-Session</t>
+  </si>
+  <si>
+    <t>Session de découverte</t>
+  </si>
+  <si>
+    <t>Discovery sessie</t>
+  </si>
+  <si>
+    <t>发现会议</t>
+  </si>
+  <si>
+    <t>Phiên khám phá</t>
+  </si>
+  <si>
     <t>ladder.step2.title</t>
   </si>
   <si>
     <t>GEARS™ System Design</t>
   </si>
   <si>
+    <t>GEARS™ Systemdesign</t>
+  </si>
+  <si>
+    <t>Conception système GEARS™</t>
+  </si>
+  <si>
+    <t>GEARS™ systeemontwerp</t>
+  </si>
+  <si>
+    <t>GEARS™系统设计</t>
+  </si>
+  <si>
+    <t>Thiết kế hệ thống GEARS™</t>
+  </si>
+  <si>
     <t>ladder.step3.title</t>
   </si>
   <si>
     <t>Build Partnership</t>
   </si>
   <si>
+    <t>Build-Partnerschaft</t>
+  </si>
+  <si>
+    <t>Partenariat de construction</t>
+  </si>
+  <si>
+    <t>Bouwpartnerschap</t>
+  </si>
+  <si>
+    <t>构建合作</t>
+  </si>
+  <si>
+    <t>Đối tác xây dựng</t>
+  </si>
+  <si>
     <t>ladder.step4.title</t>
   </si>
   <si>
@@ -1219,6 +2109,21 @@
     <t>Operate &amp; Evolve</t>
   </si>
   <si>
+    <t>Betreiben &amp; Weiterentwickeln</t>
+  </si>
+  <si>
+    <t>Opérer &amp; évoluer</t>
+  </si>
+  <si>
+    <t>Beheren &amp; evolueren</t>
+  </si>
+  <si>
+    <t>运营与演进</t>
+  </si>
+  <si>
+    <t>Vận hành &amp; phát triển</t>
+  </si>
+  <si>
     <t>ladder.step1.cta</t>
   </si>
   <si>
@@ -1228,6 +2133,21 @@
     <t>Book a session</t>
   </si>
   <si>
+    <t>Sitzung buchen</t>
+  </si>
+  <si>
+    <t>Réserver une session</t>
+  </si>
+  <si>
+    <t>Sessie boeken</t>
+  </si>
+  <si>
+    <t>预约会议</t>
+  </si>
+  <si>
+    <t>Đặt lịch hẹn</t>
+  </si>
+  <si>
     <t xml:space="preserve">  TESTI</t>
   </si>
   <si>
@@ -1240,6 +2160,21 @@
     <t>Trusted by Operators</t>
   </si>
   <si>
+    <t>Vertrauen von Unternehmern</t>
+  </si>
+  <si>
+    <t>La confiance des opérateurs</t>
+  </si>
+  <si>
+    <t>Vertrouwd door operators</t>
+  </si>
+  <si>
+    <t>受运营者信赖</t>
+  </si>
+  <si>
+    <t>Được các nhà vận hành tin tưởng</t>
+  </si>
+  <si>
     <t>testi.quote</t>
   </si>
   <si>
@@ -1249,6 +2184,21 @@
     <t>"GKIM helped brainstorm my vision and build it into a well thought out business, product and technology offering. The team have excelled at execution."</t>
   </si>
   <si>
+    <t>„GKIM hat mir geholfen, meine Vision zu entwickeln und sie in ein durchdachtes Geschäfts-, Produkt- und Technologieangebot umzusetzen. Das Team hat bei der Ausführung hervorragende Arbeit geleistet."</t>
+  </si>
+  <si>
+    <t>« GKIM m'a aidé à brainstormer ma vision et à la transformer en une offre commerciale, produit et technologique bien réfléchie. L'équipe a excellé dans l'exécution. »</t>
+  </si>
+  <si>
+    <t>"GKIM heeft mij geholpen mijn visie te verkennen en om te zetten in een goed doordacht business-, product- en technologieaanbod. Het team heeft uitstekend gepresteerd bij de uitvoering."</t>
+  </si>
+  <si>
+    <t>"GKIM帮助我构思了愿景，并将其转化为一个经过深思熟虑的业务、产品和技术方案。团队在执行方面表现卓越。"</t>
+  </si>
+  <si>
+    <t>"GKIM đã giúp tôi phát triển tầm nhìn và biến nó thành một đề xuất kinh doanh, sản phẩm và công nghệ được suy nghĩ kỹ lưỡng. Đội ngũ đã xuất sắc trong việc thực thi."</t>
+  </si>
+  <si>
     <t>testi.attr</t>
   </si>
   <si>
@@ -1258,6 +2208,18 @@
     <t>Founder &amp; CEO</t>
   </si>
   <si>
+    <t>Gründer &amp; CEO</t>
+  </si>
+  <si>
+    <t>Fondateur &amp; PDG</t>
+  </si>
+  <si>
+    <t>创始人兼首席执行官</t>
+  </si>
+  <si>
+    <t>Nhà sáng lập &amp; CEO</t>
+  </si>
+  <si>
     <t xml:space="preserve">  ABOUT</t>
   </si>
   <si>
@@ -1270,6 +2232,21 @@
     <t>Why GKIM Exists</t>
   </si>
   <si>
+    <t>Warum GKIM existiert</t>
+  </si>
+  <si>
+    <t>Pourquoi GKIM existe</t>
+  </si>
+  <si>
+    <t>Waarom GKIM bestaat</t>
+  </si>
+  <si>
+    <t>GKIM存在的原因</t>
+  </si>
+  <si>
+    <t>Tại sao GKIM tồn tại</t>
+  </si>
+  <si>
     <t>about.h</t>
   </si>
   <si>
@@ -1279,6 +2256,21 @@
     <t>Built by Someone Who Has Done This Before</t>
   </si>
   <si>
+    <t>Aufgebaut von jemandem, der dies bereits getan hat</t>
+  </si>
+  <si>
+    <t>Construit par quelqu'un qui l'a déjà fait</t>
+  </si>
+  <si>
+    <t>Gebouwd door iemand die dit al heeft gedaan</t>
+  </si>
+  <si>
+    <t>由曾经做到过的人创建</t>
+  </si>
+  <si>
+    <t>Được xây dựng bởi người đã làm điều này trước đây</t>
+  </si>
+  <si>
     <t>about.letter.salutation</t>
   </si>
   <si>
@@ -1288,6 +2280,21 @@
     <t>To the Founders and Leaders Building the Future,</t>
   </si>
   <si>
+    <t>An die Gründer und Führungskräfte, die die Zukunft gestalten,</t>
+  </si>
+  <si>
+    <t>Aux fondateurs et dirigeants qui construisent l'avenir,</t>
+  </si>
+  <si>
+    <t>Aan de founders en leiders die de toekomst bouwen,</t>
+  </si>
+  <si>
+    <t>致正在构建未来的创始人和领导者，</t>
+  </si>
+  <si>
+    <t>Kính gửi các nhà sáng lập và lãnh đạo đang xây dựng tương lai,</t>
+  </si>
+  <si>
     <t>about.sig</t>
   </si>
   <si>
@@ -1306,6 +2313,21 @@
     <t>What Makes GKIM Different</t>
   </si>
   <si>
+    <t>Was GKIM anders macht</t>
+  </si>
+  <si>
+    <t>Ce qui distingue GKIM</t>
+  </si>
+  <si>
+    <t>Wat GKIM anders maakt</t>
+  </si>
+  <si>
+    <t>是什么让GKIM与众不同</t>
+  </si>
+  <si>
+    <t>Điều làm GKIM khác biệt</t>
+  </si>
+  <si>
     <t xml:space="preserve">  START</t>
   </si>
   <si>
@@ -1315,6 +2337,21 @@
     <t>start</t>
   </si>
   <si>
+    <t>Mit GKIM sprechen</t>
+  </si>
+  <si>
+    <t>Parler à GKIM</t>
+  </si>
+  <si>
+    <t>Praat met GKIM</t>
+  </si>
+  <si>
+    <t>与GKIM对话</t>
+  </si>
+  <si>
+    <t>Nói chuyện với GKIM</t>
+  </si>
+  <si>
     <t>start.h</t>
   </si>
   <si>
@@ -1324,6 +2361,21 @@
     <t>Before you build or scale, understand how your business actually works.</t>
   </si>
   <si>
+    <t>Bevor Sie aufbauen oder skalieren, verstehen Sie, wie Ihr Unternehmen tatsächlich funktioniert.</t>
+  </si>
+  <si>
+    <t>Avant de construire ou de passer à l'échelle, comprenez comment votre entreprise fonctionne réellement.</t>
+  </si>
+  <si>
+    <t>Voordat u bouwt of schaalt, begrijp hoe uw bedrijf werkelijk functioneert.</t>
+  </si>
+  <si>
+    <t>在构建或扩展之前，了解您的企业实际上是如何运作的。</t>
+  </si>
+  <si>
+    <t>Trước khi xây dựng hoặc mở rộng quy mô, hãy hiểu cách doanh nghiệp của bạn thực sự hoạt động.</t>
+  </si>
+  <si>
     <t>start.sub</t>
   </si>
   <si>
@@ -1333,6 +2385,21 @@
     <t>This is not a sales call. It is a working session to understand your business model, explore how the system currently operates, and identify gaps, risks, and assumptions.</t>
   </si>
   <si>
+    <t>Dies ist kein Verkaufsgespräch. Es ist eine Arbeitssitzung, um Ihr Geschäftsmodell zu verstehen, die aktuelle Funktionsweise des Systems zu erkunden und Lücken, Risiken und Annahmen zu identifizieren.</t>
+  </si>
+  <si>
+    <t>Ce n'est pas un appel commercial. C'est une session de travail pour comprendre votre modèle d'entreprise, explorer le fonctionnement actuel du système et identifier les lacunes, les risques et les hypothèses.</t>
+  </si>
+  <si>
+    <t>Dit is geen verkoopgesprek. Het is een werksessie om uw bedrijfsmodel te begrijpen, te onderzoeken hoe het systeem momenteel werkt en om hiaten, risico's en aannames te identificeren.</t>
+  </si>
+  <si>
+    <t>这不是销售电话。这是一次工作会议，旨在了解您的商业模式，探索系统当前的运作方式，并识别差距、风险和假设。</t>
+  </si>
+  <si>
+    <t>Đây không phải là cuộc gọi bán hàng. Đây là một buổi làm việc để hiểu mô hình kinh doanh của bạn, khám phá cách hệ thống hiện đang hoạt động, và xác định các khoảng cách, rủi ro và giả định.</t>
+  </si>
+  <si>
     <t>start.kl</t>
   </si>
   <si>
@@ -1342,6 +2409,21 @@
     <t>Clarity replaces assumption.</t>
   </si>
   <si>
+    <t>Klarheit ersetzt Annahme.</t>
+  </si>
+  <si>
+    <t>La clarté remplace l'hypothèse.</t>
+  </si>
+  <si>
+    <t>Duidelijkheid vervangt aanname.</t>
+  </si>
+  <si>
+    <t>清晰取代假设。</t>
+  </si>
+  <si>
+    <t>Sự rõ ràng thay thế giả định.</t>
+  </si>
+  <si>
     <t>form.intro</t>
   </si>
   <si>
@@ -1351,6 +2433,21 @@
     <t>Tell us what you're building, where you are in the journey, and what feels unclear or not working.</t>
   </si>
   <si>
+    <t>Erzählen Sie uns, was Sie aufbauen, wo Sie sich auf dem Weg befinden und was sich unklar oder nicht funktionierend anfühlt.</t>
+  </si>
+  <si>
+    <t>Dites-nous ce que vous construisez, où vous en êtes dans votre parcours, et ce qui vous semble flou ou ne fonctionne pas.</t>
+  </si>
+  <si>
+    <t>Vertel ons wat u bouwt, waar u zich bevindt op de reis en wat onduidelijk voelt of niet werkt.</t>
+  </si>
+  <si>
+    <t>告诉我们您正在构建什么，您在旅程中处于哪个阶段，以及什么感觉不清晰或不起作用。</t>
+  </si>
+  <si>
+    <t>Hãy cho chúng tôi biết bạn đang xây dựng gì, bạn đang ở đâu trong hành trình, và điều gì cảm thấy chưa rõ ràng hoặc chưa hoạt động tốt.</t>
+  </si>
+  <si>
     <t>form.label.name</t>
   </si>
   <si>
@@ -1417,6 +2514,21 @@
     <t>What are you building or what isn't working?</t>
   </si>
   <si>
+    <t>Was bauen Sie oder was funktioniert nicht?</t>
+  </si>
+  <si>
+    <t>Que construisez-vous ou qu'est-ce qui ne fonctionne pas?</t>
+  </si>
+  <si>
+    <t>Wat bouwt u of wat werkt niet?</t>
+  </si>
+  <si>
+    <t>您在构建什么，或者什么不起作用？</t>
+  </si>
+  <si>
+    <t>Bạn đang xây dựng gì hoặc điều gì chưa hoạt động?</t>
+  </si>
+  <si>
     <t>form.placeholder.message</t>
   </si>
   <si>
@@ -1426,6 +2538,21 @@
     <t>Share as much or as little as you'd like...</t>
   </si>
   <si>
+    <t>Teilen Sie so viel oder so wenig mit, wie Sie möchten...</t>
+  </si>
+  <si>
+    <t>Partagez autant ou aussi peu que vous le souhaitez...</t>
+  </si>
+  <si>
+    <t>Deel zoveel of zo weinig als u wilt...</t>
+  </si>
+  <si>
+    <t>分享您想要的任意多或少的内容......</t>
+  </si>
+  <si>
+    <t>Chia sẻ nhiều hay ít tùy ý bạn...</t>
+  </si>
+  <si>
     <t>form.btn</t>
   </si>
   <si>
@@ -1450,6 +2577,21 @@
     <t>Design the business before you build it</t>
   </si>
   <si>
+    <t>Gestalten Sie das Unternehmen, bevor Sie es bauen.</t>
+  </si>
+  <si>
+    <t>Concevez l'entreprise avant de la construire.</t>
+  </si>
+  <si>
+    <t>Ontwerp het bedrijf voordat u het bouwt.</t>
+  </si>
+  <si>
+    <t>在构建之前设计企业。</t>
+  </si>
+  <si>
+    <t>Thiết kế doanh nghiệp trước khi xây dựng nó.</t>
+  </si>
+  <si>
     <t>cta.body</t>
   </si>
   <si>
@@ -1459,6 +2601,21 @@
     <t>Most teams start with code. The best teams start with clarity.</t>
   </si>
   <si>
+    <t>Die meisten Teams beginnen mit Code. Die besten Teams beginnen mit Klarheit.</t>
+  </si>
+  <si>
+    <t>La plupart des équipes commencent par le code. Les meilleures commencent par la clarté.</t>
+  </si>
+  <si>
+    <t>De meeste teams beginnen met code. De beste teams beginnen met duidelijkheid.</t>
+  </si>
+  <si>
+    <t>大多数团队从代码开始。最优秀的团队从清晰开始。</t>
+  </si>
+  <si>
+    <t>Hầu hết các đội nhóm bắt đầu bằng code. Những đội nhóm tốt nhất bắt đầu bằng sự rõ ràng.</t>
+  </si>
+  <si>
     <t>cta.btn.primary</t>
   </si>
   <si>
@@ -1486,6 +2643,21 @@
     <t>We define the missing layer between strategy and engineering — how your business actually works as a system.</t>
   </si>
   <si>
+    <t>Wir definieren die fehlende Schicht zwischen Strategie und Engineering — wie Ihr Unternehmen tatsächlich als System funktioniert.</t>
+  </si>
+  <si>
+    <t>Nous définissons la couche manquante entre stratégie et ingénierie — comment votre entreprise fonctionne réellement en tant que système.</t>
+  </si>
+  <si>
+    <t>Wij definiëren de ontbrekende laag tussen strategie en engineering — hoe uw bedrijf werkelijk als systeem functioneert.</t>
+  </si>
+  <si>
+    <t>我们定义战略与工程之间缺失的层——您的企业作为创造价值的系统实际上是如何运作的。</t>
+  </si>
+  <si>
+    <t>Chúng tôi xác định lớp còn thiếu giữa chiến lược và kỹ thuật — cách doanh nghiệp của bạn thực sự hoạt động như một hệ thống.</t>
+  </si>
+  <si>
     <t>footer.col.explore</t>
   </si>
   <si>
@@ -1495,12 +2667,33 @@
     <t>Explore</t>
   </si>
   <si>
+    <t>Erkunden</t>
+  </si>
+  <si>
+    <t>Explorer</t>
+  </si>
+  <si>
+    <t>Verkennen</t>
+  </si>
+  <si>
+    <t>探索</t>
+  </si>
+  <si>
+    <t>Khám phá</t>
+  </si>
+  <si>
     <t>footer.col.contact</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
+    <t>Kontakt</t>
+  </si>
+  <si>
+    <t>联系方式</t>
+  </si>
+  <si>
     <t>footer.copyright</t>
   </si>
   <si>
@@ -1519,6 +2712,21 @@
     <t>System definition. AI-native business design.</t>
   </si>
   <si>
+    <t>Systemdefinition. KI-natives Unternehmensdesign.</t>
+  </si>
+  <si>
+    <t>Définition de système. Conception d'entreprise AI-native.</t>
+  </si>
+  <si>
+    <t>Systeemdefinitie. AI-native bedrijfsontwerp.</t>
+  </si>
+  <si>
+    <t>系统定义。AI原生企业设计。</t>
+  </si>
+  <si>
+    <t>Định nghĩa hệ thống. Thiết kế doanh nghiệp AI-native.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  META</t>
   </si>
   <si>
@@ -1534,6 +2742,21 @@
     <t>GKIM Digital — Design Your AI-Native Business</t>
   </si>
   <si>
+    <t>GKIM Digital — KI-natives Unternehmen systematisch gestalten</t>
+  </si>
+  <si>
+    <t>GKIM Digital — Concevoir votre entreprise AI-native</t>
+  </si>
+  <si>
+    <t>GKIM Digital — Bouw het juiste AI-native bedrijf</t>
+  </si>
+  <si>
+    <t>GKIM Digital — 设计您的AI原生企业</t>
+  </si>
+  <si>
+    <t>GKIM Digital — Thiết kế doanh nghiệp AI-native của bạn</t>
+  </si>
+  <si>
     <t>page.lang</t>
   </si>
   <si>
@@ -1567,9 +2790,6 @@
     <t>https://gkim.digital/en/</t>
   </si>
   <si>
-    <t>GKIM Digital — KI-natives Unternehmen systematisch gestalten</t>
-  </si>
-  <si>
     <t>GKIM Digital hilft Gründern und Unternehmern, KI-native Unternehmen zu gestalten. GEARS™ ist unsere Methode zur strukturierten Systemdefinition. Hauptsitz in Cambridge.</t>
   </si>
   <si>
@@ -1582,9 +2802,6 @@
     <t>https://gkim.digital/de/</t>
   </si>
   <si>
-    <t>GKIM Digital — Concevoir votre entreprise AI-native</t>
-  </si>
-  <si>
     <t>GKIM Digital accompagne les fondateurs dans la conception d'entreprises AI-natives. GEARS™ est notre méthodologie de définition systémique. Basé à Cambridge.</t>
   </si>
   <si>
@@ -1597,9 +2814,6 @@
     <t>https://gkim.digital/fr/</t>
   </si>
   <si>
-    <t>GKIM Digital — Bouw het juiste AI-native bedrijf</t>
-  </si>
-  <si>
     <t>GKIM Digital helpt oprichters en operators AI-native bedrijven te ontwerpen. GEARS™ is onze methode voor gestructureerde systeemontwerp. Gevestigd in Cambridge.</t>
   </si>
   <si>
@@ -1612,9 +2826,6 @@
     <t>https://gkim.digital/nl/</t>
   </si>
   <si>
-    <t>GKIM Digital — 设计您的AI原生企业</t>
-  </si>
-  <si>
     <t>GKIM Digital帮助创始人和运营者设计AI原生企业。GEARS™是我们将商业理念转化为结构化可构建系统的方法论。总部位于英国剑桥。</t>
   </si>
   <si>
@@ -1625,9 +2836,6 @@
   </si>
   <si>
     <t>https://gkim.digital/zh/</t>
-  </si>
-  <si>
-    <t>GKIM Digital — Thiết kế doanh nghiệp AI-native của bạn</t>
   </si>
   <si>
     <t>GKIM Digital giúp các nhà sáng lập và vận hành thiết kế doanh nghiệp AI-native. GEARS™ là phương pháp chuyển ý tưởng kinh doanh thành hệ thống có cấu trúc. Văn phòng tại Cambridge và TP. Hồ Chí Minh.</t>
@@ -3091,85 +4299,85 @@
         <v>194</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>184</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>184</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>184</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>176</v>
@@ -3192,36 +4400,36 @@
     </row>
     <row r="16" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>184</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3234,152 +4442,152 @@
     </row>
     <row r="18" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>194</v>
+        <v>247</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>194</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="C22" s="9" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>194</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3392,239 +4600,239 @@
     </row>
     <row r="24" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>194</v>
+        <v>280</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>194</v>
+        <v>281</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>194</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>194</v>
+        <v>288</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>194</v>
+        <v>289</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>194</v>
+        <v>291</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>194</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>194</v>
+        <v>296</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>194</v>
+        <v>297</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>194</v>
+        <v>298</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>194</v>
+        <v>299</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>194</v>
+        <v>304</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>194</v>
+        <v>305</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>194</v>
+        <v>306</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>194</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>254</v>
+        <v>311</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>194</v>
+        <v>312</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>194</v>
+        <v>313</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>194</v>
+        <v>315</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>194</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>255</v>
+        <v>317</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>256</v>
+        <v>318</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>194</v>
+        <v>320</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>194</v>
+        <v>322</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>194</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>194</v>
+        <v>328</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>194</v>
+        <v>329</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>194</v>
+        <v>331</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>194</v>
+        <v>332</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>261</v>
+        <v>333</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3637,13 +4845,13 @@
     </row>
     <row r="33" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>262</v>
+        <v>334</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>147</v>
@@ -3666,94 +4874,94 @@
     </row>
     <row r="34" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>266</v>
+        <v>338</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>267</v>
+        <v>339</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>194</v>
+        <v>340</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>194</v>
+        <v>341</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>194</v>
+        <v>342</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>194</v>
+        <v>343</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>194</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>194</v>
+        <v>348</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>194</v>
+        <v>349</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>194</v>
+        <v>351</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>194</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>271</v>
+        <v>353</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>272</v>
+        <v>354</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>194</v>
+        <v>356</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>194</v>
+        <v>357</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>194</v>
+        <v>358</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>194</v>
+        <v>359</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>194</v>
+        <v>360</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>274</v>
+        <v>361</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3766,326 +4974,326 @@
     </row>
     <row r="38" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>277</v>
+        <v>364</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>194</v>
+        <v>365</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>194</v>
+        <v>366</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>194</v>
+        <v>367</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>194</v>
+        <v>368</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>194</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>241</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>279</v>
+        <v>371</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>194</v>
+        <v>372</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>194</v>
+        <v>373</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>194</v>
+        <v>374</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>194</v>
+        <v>375</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>194</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>280</v>
+        <v>377</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>281</v>
+        <v>378</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>282</v>
+        <v>379</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>194</v>
+        <v>381</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>194</v>
+        <v>382</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>194</v>
+        <v>383</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>194</v>
+        <v>384</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>283</v>
+        <v>385</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>284</v>
+        <v>386</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>285</v>
+        <v>387</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>194</v>
+        <v>388</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>194</v>
+        <v>389</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>194</v>
+        <v>390</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>194</v>
+        <v>392</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>286</v>
+        <v>393</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>287</v>
+        <v>394</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>288</v>
+        <v>395</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>194</v>
+        <v>396</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>194</v>
+        <v>397</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>194</v>
+        <v>398</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>194</v>
+        <v>399</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>194</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>289</v>
+        <v>401</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>290</v>
+        <v>402</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>291</v>
+        <v>403</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>194</v>
+        <v>404</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>194</v>
+        <v>405</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>194</v>
+        <v>406</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>194</v>
+        <v>407</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>194</v>
+        <v>408</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>292</v>
+        <v>409</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>293</v>
+        <v>410</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>294</v>
+        <v>411</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>194</v>
+        <v>412</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>194</v>
+        <v>413</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>194</v>
+        <v>414</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>194</v>
+        <v>415</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>194</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>295</v>
+        <v>417</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>296</v>
+        <v>418</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>297</v>
+        <v>419</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>194</v>
+        <v>420</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>194</v>
+        <v>421</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>194</v>
+        <v>422</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>194</v>
+        <v>423</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>194</v>
+        <v>424</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>298</v>
+        <v>425</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>299</v>
+        <v>426</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>300</v>
+        <v>427</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>194</v>
+        <v>428</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>194</v>
+        <v>429</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>194</v>
+        <v>430</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>194</v>
+        <v>431</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>194</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>301</v>
+        <v>433</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>302</v>
+        <v>434</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>303</v>
+        <v>435</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>194</v>
+        <v>436</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>194</v>
+        <v>437</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>194</v>
+        <v>438</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>194</v>
+        <v>439</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>194</v>
+        <v>440</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>304</v>
+        <v>441</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>305</v>
+        <v>442</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>306</v>
+        <v>443</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>194</v>
+        <v>444</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>194</v>
+        <v>445</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>194</v>
+        <v>446</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>194</v>
+        <v>447</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>194</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>307</v>
+        <v>449</v>
       </c>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -4098,384 +5306,384 @@
     </row>
     <row r="50" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>308</v>
+        <v>450</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>310</v>
+        <v>452</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>194</v>
+        <v>453</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>194</v>
+        <v>454</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>194</v>
+        <v>455</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>194</v>
+        <v>456</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>194</v>
+        <v>457</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>311</v>
+        <v>458</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>312</v>
+        <v>459</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>194</v>
+        <v>460</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>194</v>
+        <v>461</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>194</v>
+        <v>462</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>194</v>
+        <v>463</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>194</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>313</v>
+        <v>465</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>314</v>
+        <v>466</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>315</v>
+        <v>467</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>468</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>194</v>
+        <v>469</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>194</v>
+        <v>470</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>194</v>
+        <v>471</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>194</v>
+        <v>472</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>316</v>
+        <v>473</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>317</v>
+        <v>474</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>318</v>
+        <v>475</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>194</v>
+        <v>476</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>194</v>
+        <v>477</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>194</v>
+        <v>478</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>194</v>
+        <v>479</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>194</v>
+        <v>480</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>319</v>
+        <v>481</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>320</v>
+        <v>482</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>321</v>
+        <v>483</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>484</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>194</v>
+        <v>485</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>194</v>
+        <v>486</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>194</v>
+        <v>487</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>194</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>322</v>
+        <v>489</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>323</v>
+        <v>490</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>324</v>
+        <v>491</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>194</v>
+        <v>492</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>194</v>
+        <v>493</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>194</v>
+        <v>494</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>194</v>
+        <v>495</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>194</v>
+        <v>496</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>325</v>
+        <v>497</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>326</v>
+        <v>498</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>327</v>
+        <v>499</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>194</v>
+        <v>500</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>194</v>
+        <v>501</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>194</v>
+        <v>502</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>503</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>194</v>
+        <v>504</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>328</v>
+        <v>505</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>329</v>
+        <v>506</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>330</v>
+        <v>507</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>194</v>
+        <v>508</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>194</v>
+        <v>509</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>194</v>
+        <v>510</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>194</v>
+        <v>511</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>194</v>
+        <v>512</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>331</v>
+        <v>513</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>332</v>
+        <v>514</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>333</v>
+        <v>515</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>194</v>
+        <v>516</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>194</v>
+        <v>517</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>194</v>
+        <v>518</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>194</v>
+        <v>519</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>194</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>334</v>
+        <v>521</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>335</v>
+        <v>522</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>336</v>
+        <v>523</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>194</v>
+        <v>524</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>194</v>
+        <v>525</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>194</v>
+        <v>526</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>194</v>
+        <v>527</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>194</v>
+        <v>528</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>337</v>
+        <v>529</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>338</v>
+        <v>530</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>339</v>
+        <v>531</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>194</v>
+        <v>532</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>194</v>
+        <v>533</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>194</v>
+        <v>534</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>194</v>
+        <v>535</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>194</v>
+        <v>536</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>340</v>
+        <v>537</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>341</v>
+        <v>538</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>342</v>
+        <v>539</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>194</v>
+        <v>540</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>194</v>
+        <v>541</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>194</v>
+        <v>542</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>194</v>
+        <v>543</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>194</v>
+        <v>544</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>343</v>
+        <v>545</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>344</v>
+        <v>546</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>345</v>
+        <v>547</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>194</v>
+        <v>548</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>194</v>
+        <v>549</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>194</v>
+        <v>550</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>194</v>
+        <v>551</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>194</v>
+        <v>552</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>346</v>
+        <v>553</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
@@ -4488,152 +5696,152 @@
     </row>
     <row r="64" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>347</v>
+        <v>554</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>348</v>
+        <v>555</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>349</v>
+        <v>556</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>194</v>
+        <v>557</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>194</v>
+        <v>558</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>194</v>
+        <v>559</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>194</v>
+        <v>560</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>194</v>
+        <v>561</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>350</v>
+        <v>562</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>348</v>
+        <v>555</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>351</v>
+        <v>563</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>352</v>
+        <v>564</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>194</v>
+        <v>565</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>194</v>
+        <v>566</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>194</v>
+        <v>567</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>194</v>
+        <v>568</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>194</v>
+        <v>569</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>353</v>
+        <v>570</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>348</v>
+        <v>555</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>354</v>
+        <v>571</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>355</v>
+        <v>572</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>194</v>
+        <v>573</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>194</v>
+        <v>574</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>194</v>
+        <v>575</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>194</v>
+        <v>576</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>194</v>
+        <v>577</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>356</v>
+        <v>578</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>348</v>
+        <v>555</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>357</v>
+        <v>579</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>358</v>
+        <v>580</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>194</v>
+        <v>581</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>194</v>
+        <v>582</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>194</v>
+        <v>583</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>194</v>
+        <v>584</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>194</v>
+        <v>585</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>359</v>
+        <v>586</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>348</v>
+        <v>555</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>360</v>
+        <v>587</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>361</v>
+        <v>588</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>194</v>
+        <v>589</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>194</v>
+        <v>590</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>194</v>
+        <v>591</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>194</v>
+        <v>592</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>194</v>
+        <v>593</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
-        <v>362</v>
+        <v>594</v>
       </c>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
@@ -4646,181 +5854,181 @@
     </row>
     <row r="70" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>363</v>
+        <v>595</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>364</v>
+        <v>596</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>365</v>
+        <v>597</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>194</v>
+        <v>598</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>194</v>
+        <v>599</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>194</v>
+        <v>600</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>194</v>
+        <v>601</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>194</v>
+        <v>602</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>366</v>
+        <v>603</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>364</v>
+        <v>596</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>367</v>
+        <v>604</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>194</v>
+        <v>605</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>194</v>
+        <v>606</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>194</v>
+        <v>607</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>194</v>
+        <v>608</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>194</v>
+        <v>609</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>368</v>
+        <v>610</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>364</v>
+        <v>596</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>369</v>
+        <v>611</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>370</v>
+        <v>612</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>194</v>
+        <v>613</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>194</v>
+        <v>614</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>194</v>
+        <v>612</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>194</v>
+        <v>615</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>194</v>
+        <v>616</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
-        <v>371</v>
+        <v>617</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>364</v>
+        <v>596</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>372</v>
+        <v>618</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>373</v>
+        <v>619</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>194</v>
+        <v>620</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>194</v>
+        <v>621</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>194</v>
+        <v>622</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>194</v>
+        <v>623</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>194</v>
+        <v>624</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
-        <v>374</v>
+        <v>625</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>364</v>
+        <v>596</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>369</v>
+        <v>611</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>375</v>
+        <v>626</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>194</v>
+        <v>627</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>194</v>
+        <v>628</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>194</v>
+        <v>626</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>194</v>
+        <v>629</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>194</v>
+        <v>630</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
-        <v>376</v>
+        <v>631</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>364</v>
+        <v>596</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>369</v>
+        <v>611</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>377</v>
+        <v>632</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>194</v>
+        <v>633</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>194</v>
+        <v>634</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>194</v>
+        <v>635</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>194</v>
+        <v>636</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>194</v>
+        <v>637</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
-        <v>378</v>
+        <v>638</v>
       </c>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
@@ -4833,239 +6041,239 @@
     </row>
     <row r="77" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
-        <v>379</v>
+        <v>639</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>381</v>
+        <v>641</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>194</v>
+        <v>642</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>194</v>
+        <v>643</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>194</v>
+        <v>644</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>194</v>
+        <v>645</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>194</v>
+        <v>646</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
-        <v>382</v>
+        <v>647</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>383</v>
+        <v>648</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>194</v>
+        <v>649</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>194</v>
+        <v>650</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>194</v>
+        <v>651</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>194</v>
+        <v>652</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>194</v>
+        <v>653</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
-        <v>384</v>
+        <v>654</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>385</v>
+        <v>655</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>386</v>
+        <v>656</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>194</v>
+        <v>657</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>194</v>
+        <v>658</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>194</v>
+        <v>659</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>194</v>
+        <v>660</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>194</v>
+        <v>661</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
-        <v>387</v>
+        <v>662</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>290</v>
+        <v>402</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>388</v>
+        <v>663</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>194</v>
+        <v>664</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>194</v>
+        <v>665</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>194</v>
+        <v>666</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>194</v>
+        <v>667</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>194</v>
+        <v>668</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
-        <v>389</v>
+        <v>669</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>293</v>
+        <v>410</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>390</v>
+        <v>670</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>194</v>
+        <v>671</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>194</v>
+        <v>672</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>194</v>
+        <v>673</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>194</v>
+        <v>674</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>194</v>
+        <v>675</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
-        <v>391</v>
+        <v>676</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>296</v>
+        <v>418</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>392</v>
+        <v>677</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>194</v>
+        <v>678</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>194</v>
+        <v>679</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>194</v>
+        <v>680</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>194</v>
+        <v>681</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>194</v>
+        <v>682</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
-        <v>393</v>
+        <v>683</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>394</v>
+        <v>684</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>395</v>
+        <v>685</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>194</v>
+        <v>686</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>194</v>
+        <v>687</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>194</v>
+        <v>688</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>194</v>
+        <v>689</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>194</v>
+        <v>690</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
-        <v>396</v>
+        <v>691</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>380</v>
+        <v>640</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>397</v>
+        <v>692</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>398</v>
+        <v>693</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>194</v>
+        <v>694</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>194</v>
+        <v>695</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>194</v>
+        <v>696</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>194</v>
+        <v>697</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>194</v>
+        <v>698</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
-        <v>399</v>
+        <v>699</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
@@ -5078,94 +6286,94 @@
     </row>
     <row r="86" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>401</v>
+        <v>701</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>402</v>
+        <v>702</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>194</v>
+        <v>703</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>194</v>
+        <v>704</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>194</v>
+        <v>705</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>194</v>
+        <v>706</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>194</v>
+        <v>707</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
-        <v>403</v>
+        <v>708</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>401</v>
+        <v>701</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>404</v>
+        <v>709</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>405</v>
+        <v>710</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>194</v>
+        <v>711</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>194</v>
+        <v>712</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>194</v>
+        <v>713</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>194</v>
+        <v>714</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>194</v>
+        <v>715</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>406</v>
+        <v>716</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>401</v>
+        <v>701</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>407</v>
+        <v>717</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>408</v>
+        <v>718</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>194</v>
+        <v>719</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>194</v>
+        <v>720</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>194</v>
+        <v>718</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>194</v>
+        <v>721</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>194</v>
+        <v>722</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
-        <v>409</v>
+        <v>723</v>
       </c>
       <c r="B89" s="11"/>
       <c r="C89" s="11"/>
@@ -5178,152 +6386,152 @@
     </row>
     <row r="90" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
-        <v>410</v>
+        <v>724</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>411</v>
+        <v>725</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>412</v>
+        <v>726</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>194</v>
+        <v>727</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>194</v>
+        <v>728</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>194</v>
+        <v>729</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>194</v>
+        <v>730</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>194</v>
+        <v>731</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
-        <v>413</v>
+        <v>732</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>411</v>
+        <v>725</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>414</v>
+        <v>733</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>415</v>
+        <v>734</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>194</v>
+        <v>735</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>194</v>
+        <v>736</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>194</v>
+        <v>737</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>194</v>
+        <v>738</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>194</v>
+        <v>739</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
-        <v>416</v>
+        <v>740</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>411</v>
+        <v>725</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>417</v>
+        <v>741</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>418</v>
+        <v>742</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>194</v>
+        <v>743</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>194</v>
+        <v>744</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>194</v>
+        <v>745</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>194</v>
+        <v>746</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>194</v>
+        <v>747</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
-        <v>419</v>
+        <v>748</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>411</v>
+        <v>725</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>420</v>
+        <v>749</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>421</v>
+        <v>750</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>194</v>
+        <v>750</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>194</v>
+        <v>750</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>194</v>
+        <v>750</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>194</v>
+        <v>750</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>194</v>
+        <v>750</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
-        <v>422</v>
+        <v>751</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>411</v>
+        <v>725</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>423</v>
+        <v>752</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>424</v>
+        <v>753</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>194</v>
+        <v>754</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>194</v>
+        <v>755</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>194</v>
+        <v>756</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>194</v>
+        <v>757</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>194</v>
+        <v>758</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="12" t="s">
-        <v>425</v>
+        <v>759</v>
       </c>
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
@@ -5336,326 +6544,326 @@
     </row>
     <row r="96" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7" t="s">
-        <v>426</v>
+        <v>760</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>176</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>194</v>
+        <v>762</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>194</v>
+        <v>763</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>194</v>
+        <v>764</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>194</v>
+        <v>765</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>194</v>
+        <v>766</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
-        <v>428</v>
+        <v>767</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>429</v>
+        <v>768</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>194</v>
+        <v>770</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>194</v>
+        <v>771</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>194</v>
+        <v>772</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>194</v>
+        <v>773</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>194</v>
+        <v>774</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
-        <v>431</v>
+        <v>775</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>432</v>
+        <v>776</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>433</v>
+        <v>777</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>194</v>
+        <v>778</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>194</v>
+        <v>779</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>194</v>
+        <v>780</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>194</v>
+        <v>781</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>194</v>
+        <v>782</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>435</v>
+        <v>784</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>436</v>
+        <v>785</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>194</v>
+        <v>786</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>194</v>
+        <v>787</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>194</v>
+        <v>788</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>194</v>
+        <v>789</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>194</v>
+        <v>790</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
-        <v>437</v>
+        <v>791</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>438</v>
+        <v>792</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>439</v>
+        <v>793</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>194</v>
+        <v>794</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>194</v>
+        <v>795</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>194</v>
+        <v>796</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>194</v>
+        <v>797</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>194</v>
+        <v>798</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
-        <v>440</v>
+        <v>799</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>441</v>
+        <v>800</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>442</v>
+        <v>801</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>442</v>
+        <v>801</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>443</v>
+        <v>802</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>444</v>
+        <v>803</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>445</v>
+        <v>804</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>446</v>
+        <v>805</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
-        <v>447</v>
+        <v>806</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>441</v>
+        <v>800</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>448</v>
+        <v>807</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>449</v>
+        <v>808</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>450</v>
+        <v>809</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>451</v>
+        <v>810</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>452</v>
+        <v>811</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>453</v>
+        <v>812</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
-        <v>454</v>
+        <v>813</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>441</v>
+        <v>800</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>455</v>
+        <v>814</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>456</v>
+        <v>815</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>455</v>
+        <v>814</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>457</v>
+        <v>816</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>458</v>
+        <v>817</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>455</v>
+        <v>814</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
-        <v>459</v>
+        <v>818</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>460</v>
+        <v>819</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>461</v>
+        <v>820</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>194</v>
+        <v>821</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>194</v>
+        <v>822</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>194</v>
+        <v>823</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>194</v>
+        <v>824</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>194</v>
+        <v>825</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
-        <v>462</v>
+        <v>826</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>463</v>
+        <v>827</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>464</v>
+        <v>828</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>194</v>
+        <v>829</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>194</v>
+        <v>830</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>194</v>
+        <v>831</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>194</v>
+        <v>832</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>194</v>
+        <v>833</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
-        <v>465</v>
+        <v>834</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>427</v>
+        <v>761</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>466</v>
+        <v>835</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>467</v>
+        <v>836</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>194</v>
+        <v>694</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>194</v>
+        <v>695</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>194</v>
+        <v>696</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>194</v>
+        <v>697</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>194</v>
+        <v>698</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="12" t="s">
-        <v>468</v>
+        <v>837</v>
       </c>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
@@ -5668,71 +6876,71 @@
     </row>
     <row r="108" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
-        <v>469</v>
+        <v>838</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>470</v>
+        <v>839</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>471</v>
+        <v>840</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>472</v>
+        <v>841</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>194</v>
+        <v>842</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>194</v>
+        <v>843</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>194</v>
+        <v>844</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>194</v>
+        <v>845</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>194</v>
+        <v>846</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
-        <v>473</v>
+        <v>847</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>470</v>
+        <v>839</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>474</v>
+        <v>848</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>475</v>
+        <v>849</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>194</v>
+        <v>850</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>194</v>
+        <v>851</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>194</v>
+        <v>852</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>194</v>
+        <v>853</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>194</v>
+        <v>854</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7" t="s">
-        <v>476</v>
+        <v>855</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>470</v>
+        <v>839</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>176</v>
@@ -5755,36 +6963,36 @@
     </row>
     <row r="111" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
-        <v>477</v>
+        <v>856</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>470</v>
+        <v>839</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>478</v>
+        <v>857</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>479</v>
+        <v>858</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>479</v>
+        <v>858</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>479</v>
+        <v>858</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>479</v>
+        <v>858</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>479</v>
+        <v>858</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>479</v>
+        <v>858</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="12" t="s">
-        <v>480</v>
+        <v>859</v>
       </c>
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
@@ -5797,152 +7005,152 @@
     </row>
     <row r="113" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
-        <v>481</v>
+        <v>860</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>482</v>
+        <v>861</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>483</v>
+        <v>862</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>484</v>
+        <v>863</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>194</v>
+        <v>864</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>194</v>
+        <v>865</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>194</v>
+        <v>866</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>194</v>
+        <v>867</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>194</v>
+        <v>868</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>485</v>
+        <v>869</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>482</v>
+        <v>861</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>486</v>
+        <v>870</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>487</v>
+        <v>871</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>194</v>
+        <v>872</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>194</v>
+        <v>873</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>194</v>
+        <v>874</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>194</v>
+        <v>875</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>194</v>
+        <v>876</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>488</v>
+        <v>877</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>482</v>
+        <v>861</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>486</v>
+        <v>870</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>489</v>
+        <v>878</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>194</v>
+        <v>879</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>194</v>
+        <v>878</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>194</v>
+        <v>878</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>194</v>
+        <v>880</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>490</v>
+        <v>881</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>482</v>
+        <v>861</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>491</v>
+        <v>882</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>492</v>
+        <v>883</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>492</v>
+        <v>883</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>492</v>
+        <v>883</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>492</v>
+        <v>883</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>492</v>
+        <v>883</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>492</v>
+        <v>883</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="7" t="s">
-        <v>493</v>
+        <v>884</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>482</v>
+        <v>861</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>494</v>
+        <v>885</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>495</v>
+        <v>886</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>194</v>
+        <v>887</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>194</v>
+        <v>888</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>194</v>
+        <v>889</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>194</v>
+        <v>890</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>194</v>
+        <v>891</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="12" t="s">
-        <v>496</v>
+        <v>892</v>
       </c>
       <c r="B118" s="11"/>
       <c r="C118" s="11"/>
@@ -5955,42 +7163,42 @@
     </row>
     <row r="119" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
-        <v>497</v>
+        <v>893</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>498</v>
+        <v>894</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>499</v>
+        <v>895</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>500</v>
+        <v>896</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>194</v>
+        <v>897</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>194</v>
+        <v>898</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>194</v>
+        <v>899</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>194</v>
+        <v>900</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>194</v>
+        <v>901</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="7" t="s">
-        <v>501</v>
+        <v>902</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>498</v>
+        <v>894</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>502</v>
+        <v>903</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>48</v>
@@ -6052,19 +7260,19 @@
         <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>503</v>
+        <v>904</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>504</v>
+        <v>905</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>505</v>
+        <v>906</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>506</v>
+        <v>907</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>507</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6072,19 +7280,19 @@
         <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>500</v>
+        <v>896</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>508</v>
+        <v>909</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>509</v>
+        <v>910</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>510</v>
+        <v>911</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>511</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6092,19 +7300,19 @@
         <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>512</v>
+        <v>897</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>513</v>
+        <v>913</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>514</v>
+        <v>914</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>515</v>
+        <v>915</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>516</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6112,19 +7320,19 @@
         <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>517</v>
+        <v>898</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>518</v>
+        <v>917</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>519</v>
+        <v>918</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>520</v>
+        <v>919</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>521</v>
+        <v>920</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6132,19 +7340,19 @@
         <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>522</v>
+        <v>899</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>523</v>
+        <v>921</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>524</v>
+        <v>922</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>525</v>
+        <v>923</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>526</v>
+        <v>924</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6152,19 +7360,19 @@
         <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>527</v>
+        <v>900</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>528</v>
+        <v>925</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>529</v>
+        <v>926</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>530</v>
+        <v>927</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>531</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
@@ -6172,19 +7380,19 @@
         <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>532</v>
+        <v>901</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>533</v>
+        <v>929</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>534</v>
+        <v>930</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>535</v>
+        <v>931</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>536</v>
+        <v>932</v>
       </c>
     </row>
   </sheetData>
@@ -6210,28 +7418,28 @@
         <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>537</v>
+        <v>933</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>538</v>
+        <v>934</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>539</v>
+        <v>935</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>540</v>
+        <v>936</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>541</v>
+        <v>937</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>542</v>
+        <v>938</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>543</v>
+        <v>939</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>544</v>
+        <v>940</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6239,28 +7447,28 @@
         <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>545</v>
+        <v>941</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>546</v>
+        <v>942</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>547</v>
+        <v>943</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>548</v>
+        <v>944</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>549</v>
+        <v>945</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>550</v>
+        <v>946</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>551</v>
+        <v>947</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>552</v>
+        <v>948</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6268,28 +7476,28 @@
         <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>545</v>
+        <v>941</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>546</v>
+        <v>942</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>547</v>
+        <v>943</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>548</v>
+        <v>944</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>553</v>
+        <v>949</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>554</v>
+        <v>950</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>551</v>
+        <v>947</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>552</v>
+        <v>948</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6297,28 +7505,28 @@
         <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>545</v>
+        <v>941</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>546</v>
+        <v>942</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>547</v>
+        <v>943</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>548</v>
+        <v>944</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>549</v>
+        <v>945</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>554</v>
+        <v>950</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>555</v>
+        <v>951</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>552</v>
+        <v>948</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6326,28 +7534,28 @@
         <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>545</v>
+        <v>941</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>546</v>
+        <v>942</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>547</v>
+        <v>943</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>548</v>
+        <v>944</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>556</v>
+        <v>952</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>554</v>
+        <v>950</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>551</v>
+        <v>947</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>552</v>
+        <v>948</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6355,28 +7563,28 @@
         <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>545</v>
+        <v>941</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>557</v>
+        <v>953</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>558</v>
+        <v>954</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>559</v>
+        <v>955</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>560</v>
+        <v>956</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>561</v>
+        <v>957</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>551</v>
+        <v>947</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>551</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -6384,28 +7592,28 @@
         <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>545</v>
+        <v>941</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>546</v>
+        <v>942</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>547</v>
+        <v>943</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>562</v>
+        <v>958</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>549</v>
+        <v>945</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>563</v>
+        <v>959</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>551</v>
+        <v>947</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>552</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/GitHub Repos/GKIMWebsite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEF55A3-2FE8-A149-94E0-DD56C40FC364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0713BD9E-9834-5A4A-8879-02E6FA704A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,10 +492,10 @@
     <t>nav.link.outputs</t>
   </si>
   <si>
-    <t>Outputs</t>
-  </si>
-  <si>
-    <t>Ergebnisse</t>
+    <t>Deliverables</t>
+  </si>
+  <si>
+    <t>Liefergegenstände</t>
   </si>
   <si>
     <t>Livrables</t>
@@ -504,7 +504,7 @@
     <t>Resultaten</t>
   </si>
   <si>
-    <t>成果</t>
+    <t>交付物</t>
   </si>
   <si>
     <t>Kết quả</t>
@@ -1296,22 +1296,22 @@
     <t>Step 3 title</t>
   </si>
   <si>
-    <t>Deliver — Build-Ready Outputs</t>
-  </si>
-  <si>
-    <t>Liefern — Baufertige Ergebnisse</t>
-  </si>
-  <si>
-    <t>Livrer — Des livrables prêts à construire</t>
-  </si>
-  <si>
-    <t>Opleveren — Bouwklare resultaten</t>
-  </si>
-  <si>
-    <t>交付——可构建的成果</t>
-  </si>
-  <si>
-    <t>Bàn giao — Kết quả sẵn sàng để xây dựng</t>
+    <t>Deliver — Design Deliverables</t>
+  </si>
+  <si>
+    <t>Liefern — Design-Liefergegenstände</t>
+  </si>
+  <si>
+    <t>Livrer — Livrables de conception</t>
+  </si>
+  <si>
+    <t>Opleveren — Ontwerpresultaten</t>
+  </si>
+  <si>
+    <t>交付——设计交付物</t>
+  </si>
+  <si>
+    <t>Bàn giao — Kết quả thiết kế</t>
   </si>
   <si>
     <t>gears.kl</t>
@@ -1395,49 +1395,49 @@
     <t>outputs</t>
   </si>
   <si>
-    <t>What You Actually Get</t>
-  </si>
-  <si>
-    <t>Was Sie tatsächlich erhalten</t>
-  </si>
-  <si>
-    <t>Ce que vous obtenez réellement</t>
-  </si>
-  <si>
-    <t>Wat u daadwerkelijk krijgt</t>
-  </si>
-  <si>
-    <t>您实际获得的内容</t>
-  </si>
-  <si>
-    <t>Những gì bạn thực sự nhận được</t>
+    <t>Design Deliverables</t>
+  </si>
+  <si>
+    <t>Design-Liefergegenstände</t>
+  </si>
+  <si>
+    <t>Livrables de conception</t>
+  </si>
+  <si>
+    <t>Ontwerpresultaten</t>
+  </si>
+  <si>
+    <t>设计交付物</t>
+  </si>
+  <si>
+    <t>Kết quả thiết kế</t>
   </si>
   <si>
     <t>outputs.h</t>
   </si>
   <si>
     <t>Not advisory.
-Production.</t>
+Deliverables.</t>
   </si>
   <si>
     <t>Keine Beratung.
-Produktion.</t>
+Liefergegenstände.</t>
   </si>
   <si>
     <t>Pas de conseil.
-De la production.</t>
+Des livrables.</t>
   </si>
   <si>
     <t>Geen advies.
-Productie.</t>
+Liefergegenstanden.</t>
   </si>
   <si>
     <t>不是咨询。
-而是交付。</t>
+而是交付物。</t>
   </si>
   <si>
     <t>Không phải tư vấn.
-Mà là sản xuất.</t>
+Mà là kết quả bàn giao.</t>
   </si>
   <si>
     <t>outputs.intro.p1</t>
@@ -1494,10 +1494,10 @@
     <t>Output 01 label</t>
   </si>
   <si>
-    <t>Output 01 — Capability Map</t>
-  </si>
-  <si>
-    <t>Ergebnis 01 — Fähigkeitskarte</t>
+    <t>Deliverable 01 — Capability Map</t>
+  </si>
+  <si>
+    <t>Liefergegenstand 01 — Fähigkeitskarte</t>
   </si>
   <si>
     <t>Livrable 01 — Cartographie des capacités</t>
@@ -1506,7 +1506,7 @@
     <t>Resultaat 01 — Capaciteitskaart</t>
   </si>
   <si>
-    <t>成果01——能力图谱</t>
+    <t>交付物01——能力图谱</t>
   </si>
   <si>
     <t>Kết quả 01 — Bản đồ năng lực</t>
@@ -1542,10 +1542,10 @@
     <t>Output 02 label</t>
   </si>
   <si>
-    <t>Output 02 — Workflow Architecture</t>
-  </si>
-  <si>
-    <t>Ergebnis 02 — Workflow-Architektur</t>
+    <t>Deliverable 02 — Workflow Architecture</t>
+  </si>
+  <si>
+    <t>Liefergegenstand 02 — Workflow-Architektur</t>
   </si>
   <si>
     <t>Livrable 02 — Architecture des flux de travail</t>
@@ -1554,7 +1554,7 @@
     <t>Resultaat 02 — Workflowarchitectuur</t>
   </si>
   <si>
-    <t>成果02——工作流架构</t>
+    <t>交付物02——工作流架构</t>
   </si>
   <si>
     <t>Kết quả 02 — Kiến trúc quy trình làm việc</t>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="languages" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="strategic_emphasis" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="strings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="meta_seo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="languages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="strategic_emphasis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="strings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta_seo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="config" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1452,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="11" min="1" max="1"/>
@@ -2795,244 +2795,189 @@
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" s="11">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>struct.label</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>shift.list.1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>shift</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Label above structural advantage quote</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>The core principle of GEARS™</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Das Kernprinzip von GEARS™</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Nguyên tắc cốt lõi của GEARS™</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Most companies still discover what’s wrong after they build it</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Die meisten Unternehmen entdecken Probleme erst nach der Entwicklung</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Hầu hết các công ty vẫn phát hiện ra vấn đề sau khi xây dựng sản phẩm</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>The core principle of GEARS™</t>
+          <t>Most companies still discover what’s wrong after they build it</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" s="11">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>struct.quote</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>shift.list.2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>shift</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Structural advantage quote — key doctrine line</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>AI implements structure, not intention. Business models must be expressed as explicit hierarchies.</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>KI implementiert Struktur, nicht Absicht. Geschäftsmodelle müssen als explizite Hierarchien ausgedrückt werden.</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>AI triển khai cấu trúc, không phải ý định. Mô hình kinh doanh phải được biểu thị dưới dạng các phân cấp rõ ràng.</t>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Requirements are incomplete before the first line of code</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Anforderungen sind unvollständig, bevor die erste Codezeile geschrieben wird</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Các yêu cầu không hoàn chỉnh trước khi viết dòng mã đầu tiên</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>AI implements structure, not intention. Business models must be expressed as explicit hierarchies.</t>
+          <t>Requirements are incomplete before the first line of code</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VISION</t>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>shift.list.3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Logic is inconsistent across teams and systems</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Die Logik ist über Teams und Systeme hinweg inkonsistent</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Logic không nhất quán trên các team và hệ thống</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Logic is inconsistent across teams and systems</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" s="11">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>vision.section_label</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>vision</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Section label</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Vision</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Vision</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Vision</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Visie</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>愿景</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Tầm nhìn</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>shift.list.4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Stakeholders remain misaligned until execution exposes it</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Stakeholder bleiben misaligned, bis die Umsetzung dies aufdeckt</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Các bên liên quan vẫn không thống nhất cho đến khi thực hiện lộ ra</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Stakeholders remain misaligned until execution exposes it</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" s="11">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>vision.h</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>vision</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Vision section heading</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>The AI-Native Business</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Das KI-native Unternehmen</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Kinh doanh native AI</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>shift.list.5</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Validation happens through building instead of before it</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Validierung erfolgt durch Entwicklung statt vorher</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Xác thực diễn ra thông qua xây dựng thay vì trước khi xây dựng</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The AI-Native Business</t>
+          <t>Validation happens through building instead of before it</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" s="11">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>vision.fear.intro</t>
+          <t>struct.label</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>vision</t>
+          <t>shift</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Intro paragraph to the three stakeholder cards</t>
+          <t>Label above structural advantage quote</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>AI raises legitimate questions. What happens to the people inside these businesses? What do customers experience? What does it mean for those who invest? The answer depends entirely on how the system is designed.</t>
+          <t>The core principle of GEARS™</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>KI wirft berechtigte Fragen auf. Was passiert mit den Menschen in diesen Unternehmen? Was erleben Kunden? Was bedeutet es für Investoren? Die Antwort hängt vollständig davon ab, wie das System gestaltet ist.</t>
+          <t>Das Kernprinzip von GEARS™</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -3052,342 +2997,297 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>AI đặt ra những câu hỏi chính đáng. Chuyện gì sẽ xảy ra với những người bên trong những doanh nghiệp này? Khách hàng sẽ trải nghiệm điều gì? Nó có ý nghĩa gì đối với những người đầu tư? Câu trả lời hoàn toàn phụ thuộc vào cách hệ thống được thiết kế.</t>
+          <t>Nguyên tắc cốt lõi của GEARS™</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>AI raises legitimate questions. What happens to the people inside these businesses? What do customers experience? What does it mean for those who invest? The answer depends entirely on how the system is designed.</t>
+          <t>The core principle of GEARS™</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" s="11">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>struct.quote</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>shift</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Structural advantage quote — key doctrine line</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>AI implements structure, not intention. Business models must be expressed as explicit hierarchies.</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>KI implementiert Struktur, nicht Absicht. Geschäftsmodelle müssen als explizite Hierarchien ausgedrückt werden.</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>AI triển khai cấu trúc, không phải ý định. Mô hình kinh doanh phải được biểu thị dưới dạng các phân cấp rõ ràng.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>AI implements structure, not intention. Business models must be expressed as explicit hierarchies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="11">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>vision.section_label</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Section label</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Visie</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>愿景</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Tầm nhìn</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="11">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>vision.h</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Vision section heading</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>The AI-Native Business</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Das KI-native Unternehmen</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Kinh doanh native AI</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>The AI-Native Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="11">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>vision.fear.intro</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Intro paragraph to the three stakeholder cards</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>AI raises legitimate questions. What happens to the people inside these businesses? What do customers experience? What does it mean for those who invest? The answer depends entirely on how the system is designed.</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>KI wirft berechtigte Fragen auf. Was passiert mit den Menschen in diesen Unternehmen? Was erleben Kunden? Was bedeutet es für Investoren? Die Antwort hängt vollständig davon ab, wie das System gestaltet ist.</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>AI đặt ra những câu hỏi chính đáng. Chuyện gì sẽ xảy ra với những người bên trong những doanh nghiệp này? Khách hàng sẽ trải nghiệm điều gì? Nó có ý nghĩa gì đối với những người đầu tư? Câu trả lời hoàn toàn phụ thuộc vào cách hệ thống được thiết kế.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>AI raises legitimate questions. What happens to the people inside these businesses? What do customers experience? What does it mean for those who invest? The answer depends entirely on how the system is designed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="11">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>vision.kl</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>vision</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Closing keyline of vision section</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Not better software.
 A better designed business.</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Nicht bessere Software.
 Ein besser gestaltetes Geschäft.</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>Không phải phần mềm tốt hơn.
 Kinh doanh được thiết kế tốt hơn.</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Not better software.
 A better designed business.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="42" ht="36" customHeight="1" s="11">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  GEARS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1" s="11">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>gears.section_label</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>gears</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Section label</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>GEARS™ — Business-Led System Design</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>GEARS™ — Business-gesteuertes System Design</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>GEARS™ — Thiết kế hệ thống dẫn đầu kinh doanh</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>GEARS™ — Business-Led System Design</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1" s="11">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>gears.h</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>gears</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Section heading</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Define the System Before You Build It</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Definieren Sie das System, bevor Sie es aufbauen</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>Xác định hệ thống trước khi bạn xây dựng nó</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Define the System Before You Build It</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1" s="11">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>gears.intro.p1</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>gears</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Intro paragraph 1</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>GEARS™ is the method GKIM uses to turn business ideas into functioning business engines.</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>GEARS™ ist die Methode, die GKIM verwendet, um Geschäftsideen in funktionierende Geschäftsmaschinen umzuwandeln.</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>GEARS™ là phương pháp GKIM sử dụng để biến các ý tưởng kinh doanh thành những bộ máy kinh doanh hoạt động.</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>GEARS™ is the method GKIM uses to turn business ideas into functioning business engines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1" s="11">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>gears.intro.p2</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>gears</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Intro paragraph 2</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>It does not start with features. It starts with: how the business must actually work to create value.</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Sie beginnt nicht mit Features. Sie beginnt damit: wie das Geschäft tatsächlich arbeiten muss, um Wert zu schaffen.</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Nó không bắt đầu với các tính năng. Nó bắt đầu với: kinh doanh phải thực sự hoạt động như thế nào để tạo ra giá trị.</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>It does not start with features. It starts with: how the business must actually work to create value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1" s="11">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>gears.intro.p3</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>gears</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Intro paragraph 3</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Each gear is a named unit of value creation — defined by what it produces, not how it operates.</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Jedes Zahnrad ist eine benannte Einheit der Wertschöpfung — definiert durch das, was es produziert, nicht wie es arbeitet.</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>Mỗi bánh răng là một đơn vị được đặt tên của việc tạo ra giá trị — được định nghĩa bằng những gì nó tạo ra, không phải cách nó hoạt động.</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Each gear is a named unit of value creation — defined by what it produces, not how it operates.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" s="11">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>gears.step1.title</t>
+          <t>gears.section_label</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -3397,17 +3297,17 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Step 1 title</t>
+          <t>Section label</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Discover — Define the Business Engine</t>
+          <t>GEARS™ — Business-Led System Design</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Erkunden — Definieren Sie die Geschäftsmaschine</t>
+          <t>GEARS™ — Business-gesteuertes System Design</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -3427,19 +3327,19 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Khám phá — Xác định Bộ máy kinh doanh</t>
+          <t>GEARS™ — Thiết kế hệ thống dẫn đầu kinh doanh</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Discover — Define the Business Engine</t>
+          <t>GEARS™ — Business-Led System Design</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" s="11">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>gears.step2.title</t>
+          <t>gears.h</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -3449,17 +3349,17 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Step 2 title</t>
+          <t>Section heading</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Design — Structure the System</t>
+          <t>Define the System Before You Build It</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Gestalten — Strukturieren Sie das System</t>
+          <t>Definieren Sie das System, bevor Sie es aufbauen</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -3479,19 +3379,19 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế — Cấu trúc hệ thống</t>
+          <t>Xác định hệ thống trước khi bạn xây dựng nó</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Design — Structure the System</t>
+          <t>Define the System Before You Build It</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1" s="11">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>gears.step3.title</t>
+          <t>gears.intro.p1</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -3501,17 +3401,17 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Step 3 title</t>
+          <t>Intro paragraph 1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Deliver — Build-Ready Outputs</t>
+          <t>GEARS™ is the method GKIM uses to turn business ideas into functioning business engines.</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Liefern — Baureife Outputs</t>
+          <t>GEARS™ ist die Methode, die GKIM verwendet, um Geschäftsideen in funktionierende Geschäftsmaschinen umzuwandeln.</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -3531,19 +3431,19 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Cung cấp — Kết quả sẵn sàng xây dựng</t>
+          <t>GEARS™ là phương pháp GKIM sử dụng để biến các ý tưởng kinh doanh thành những bộ máy kinh doanh hoạt động.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Deliver — Build-Ready Outputs</t>
+          <t>GEARS™ is the method GKIM uses to turn business ideas into functioning business engines.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1" s="11">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>gears.kl</t>
+          <t>gears.intro.p2</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -3553,17 +3453,17 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Closing keyline</t>
+          <t>Intro paragraph 2</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GEARS™ does not stop at insight. It produces the structure required to build.</t>
+          <t>It does not start with features. It starts with: how the business must actually work to create value.</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>GEARS™ endet nicht bei Erkenntnissen. Es produziert die Struktur, die zum Bauen erforderlich ist.</t>
+          <t>Sie beginnt nicht mit Features. Sie beginnt damit: wie das Geschäft tatsächlich arbeiten muss, um Wert zu schaffen.</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3583,19 +3483,19 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>GEARS™ không dừng lại ở cái nhìn sâu sắc. Nó tạo ra cấu trúc cần thiết để xây dựng.</t>
+          <t>Nó không bắt đầu với các tính năng. Nó bắt đầu với: kinh doanh phải thực sự hoạt động như thế nào để tạo ra giá trị.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>GEARS™ does not stop at insight. It produces the structure required to build.</t>
+          <t>It does not start with features. It starts with: how the business must actually work to create value.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1" s="11">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>gears.naming.title</t>
+          <t>gears.intro.p3</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -3605,17 +3505,17 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Naming discipline callout heading</t>
+          <t>Intro paragraph 3</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Every gear is named with a verb and a noun. Precisely.</t>
+          <t>Each gear is a named unit of value creation — defined by what it produces, not how it operates.</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Jedes Zahnrad wird mit einem Verb und einem Substantiv benannt. Präzise.</t>
+          <t>Jedes Zahnrad ist eine benannte Einheit der Wertschöpfung — definiert durch das, was es produziert, nicht wie es arbeitet.</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -3635,19 +3535,19 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Mỗi bánh răng được đặt tên bằng một động từ và một danh từ. Chính xác.</t>
+          <t>Mỗi bánh răng là một đơn vị được đặt tên của việc tạo ra giá trị — được định nghĩa bằng những gì nó tạo ra, không phải cách nó hoạt động.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Every gear is named with a verb and a noun. Precisely.</t>
+          <t>Each gear is a named unit of value creation — defined by what it produces, not how it operates.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1" s="11">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>gears.naming.body</t>
+          <t>gears.step1.title</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -3657,17 +3557,17 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Naming discipline body text</t>
+          <t>Step 1 title</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>A gear name is a contract. It declares what the gear does and what it acts on. Vague names hide complexity. Precise names make the system legible — and therefore buildable.</t>
+          <t>Discover — Define the Business Engine</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Ein Zahnradname ist ein Vertrag. Er erklärt, was das Zahnrad tut und worauf es einwirkt. Vage Namen verbergen Komplexität. Präzise Namen machen das System lesbar — und daher baubar.</t>
+          <t>Erkunden — Definieren Sie die Geschäftsmaschine</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -3687,46 +3587,46 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Tên của một bánh răng là một hợp đồng. Nó khai báo những gì bánh răng làm và nó tác động lên cái gì. Các tên mơ hồ ẩn giấu độ phức tạp. Những cái tên chính xác làm cho hệ thống dễ đọc — và do đó có thể xây dựng được.</t>
+          <t>Khám phá — Xác định Bộ máy kinh doanh</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>A gear name is a contract. It declares what the gear does and what it acts on. Vague names hide complexity. Precise names make the system legible — and therefore buildable.</t>
+          <t>Discover — Define the Business Engine</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  OUTPUTS</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>gears.step2.title</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1" s="11">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>outputs.section_label</t>
+          <t>gears.step3.title</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>outputs</t>
+          <t>gears</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Section label</t>
+          <t>Step 3 title</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>What You Actually Get</t>
+          <t>Deliver — Build-Ready Outputs</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Was Sie wirklich bekommen</t>
+          <t>Liefern — Baureife Outputs</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3746,335 +3646,290 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Những gì bạn thực sự nhận được</t>
+          <t>Cung cấp — Kết quả sẵn sàng xây dựng</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>What You Actually Get</t>
+          <t>Deliver — Build-Ready Outputs</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1" s="11">
       <c r="A51" s="7" t="inlineStr">
         <is>
+          <t>gears.kl</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>gears</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Closing keyline</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>GEARS™ does not stop at insight. It produces the structure required to build.</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>GEARS™ endet nicht bei Erkenntnissen. Es produziert die Struktur, die zum Bauen erforderlich ist.</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>GEARS™ không dừng lại ở cái nhìn sâu sắc. Nó tạo ra cấu trúc cần thiết để xây dựng.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>GEARS™ does not stop at insight. It produces the structure required to build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1" s="11">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>gears.naming.title</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>gears</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Naming discipline callout heading</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Every gear is named with a verb and a noun. Precisely.</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Jedes Zahnrad wird mit einem Verb und einem Substantiv benannt. Präzise.</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Mỗi bánh răng được đặt tên bằng một động từ và một danh từ. Chính xác.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Every gear is named with a verb and a noun. Precisely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1" s="11">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>gears.naming.body</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>gears</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Naming discipline body text</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>A gear name is a contract. It declares what the gear does and what it acts on. Vague names hide complexity. Precise names make the system legible — and therefore buildable.</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Ein Zahnradname ist ein Vertrag. Er erklärt, was das Zahnrad tut und worauf es einwirkt. Vage Namen verbergen Komplexität. Präzise Namen machen das System lesbar — und daher baubar.</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Tên của một bánh răng là một hợp đồng. Nó khai báo những gì bánh răng làm và nó tác động lên cái gì. Các tên mơ hồ ẩn giấu độ phức tạp. Những cái tên chính xác làm cho hệ thống dễ đọc — và do đó có thể xây dựng được.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>A gear name is a contract. It declares what the gear does and what it acts on. Vague names hide complexity. Precise names make the system legible — and therefore buildable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1" s="11">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OUTPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1" s="11">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>outputs.section_label</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>outputs</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Section label</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>What You Actually Get</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Was Sie wirklich bekommen</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Những gì bạn thực sự nhận được</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>What You Actually Get</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1" s="11">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
           <t>outputs.h</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>outputs</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Section heading</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Not advisory.
 Production.</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>Nicht Beratung.
 Produktion.</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>Không phải tư vấn.
 Sản xuất.</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Not advisory.
 Production.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="36" customHeight="1" s="11">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>outputs.intro.p1</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>Intro paragraph</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Each engagement produces a set of connected outputs that together define how your business works as a system.</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Jedes Projekt erzeugt eine Reihe verbundener Outputs, die zusammen definieren, wie Ihr Geschäft als System funktioniert.</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>Mỗi cam kết tạo ra một tập hợp các kết quả được kết nối với nhau mà lại định nghĩa cách kinh doanh của bạn hoạt động như một hệ thống.</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Each engagement produces a set of connected outputs that together define how your business works as a system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1" s="11">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>outputs.intro.p2</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Second intro sentence</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>The hierarchy is the source of truth. Everything else is a projection of it.</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Die Hierarchie ist die Quelle der Wahrheit. Alles andere ist eine Projektion davon.</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>Phân cấp là nguồn sự thật. Mọi thứ khác là hình chiếu của nó.</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>The hierarchy is the source of truth. Everything else is a projection of it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1" s="11">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>output.1.label</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>Output 01 label</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Output 01 — Capability Map</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Output 01 — Capability Map</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>Kết quả 01 — Bản đồ khả năng</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Output 01 — Capability Map</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1" s="11">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>output.1.title</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>Output 01 title</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Business Engine Definition</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Definition der Geschäftsmaschine</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>Định nghĩa Bộ máy kinh doanh</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Business Engine Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1" s="11">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>output.2.label</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>Output 02 label</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Output 02 — Workflow Architecture</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Output 02 — Workflow-Architektur</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>Kết quả 02 — Kiến trúc Quy trình làm việc</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Output 02 — Workflow Architecture</t>
-        </is>
-      </c>
-    </row>
     <row r="57" ht="36" customHeight="1" s="11">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>output.2.title</t>
+          <t>outputs.intro.p1</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -4084,17 +3939,17 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Output 02 title</t>
+          <t>Intro paragraph</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Process &amp; Authority Design</t>
+          <t>Each engagement produces a set of connected outputs that together define how your business works as a system.</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Prozess- und Autoritätsdesign</t>
+          <t>Jedes Projekt erzeugt eine Reihe verbundener Outputs, die zusammen definieren, wie Ihr Geschäft als System funktioniert.</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -4114,19 +3969,19 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế quy trình và thẩm quyền</t>
+          <t>Mỗi cam kết tạo ra một tập hợp các kết quả được kết nối với nhau mà lại định nghĩa cách kinh doanh của bạn hoạt động như một hệ thống.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Process &amp; Authority Design</t>
+          <t>Each engagement produces a set of connected outputs that together define how your business works as a system.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1" s="11">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>output.3.title</t>
+          <t>outputs.intro.p2</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -4136,17 +3991,17 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Output 03 title</t>
+          <t>Second intro sentence</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Decision Structures &amp; Rules</t>
+          <t>The hierarchy is the source of truth. Everything else is a projection of it.</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Entscheidungsstrukturen und Regeln</t>
+          <t>Die Hierarchie ist die Quelle der Wahrheit. Alles andere ist eine Projektion davon.</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -4166,19 +4021,19 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Cấu trúc quyết định và quy tắc</t>
+          <t>Phân cấp là nguồn sự thật. Mọi thứ khác là hình chiếu của nó.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Decision Structures &amp; Rules</t>
+          <t>The hierarchy is the source of truth. Everything else is a projection of it.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1" s="11">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>output.4.title</t>
+          <t>output.1.label</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -4188,17 +4043,17 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Output 04 title</t>
+          <t>Output 01 label</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Build Specification (PRD)</t>
+          <t>Output 01 — Capability Map</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Build-Spezifikation (PRD)</t>
+          <t>Output 01 — Capability Map</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -4218,19 +4073,19 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Đặc tả xây dựng (PRD)</t>
+          <t>Kết quả 01 — Bản đồ khả năng</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Build Specification (PRD)</t>
+          <t>Output 01 — Capability Map</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1" s="11">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>output.5.title</t>
+          <t>output.1.title</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -4240,17 +4095,17 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Output 05 title</t>
+          <t>Output 01 title</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>KPIs &amp; Observability Design</t>
+          <t>Business Engine Definition</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>KPIs und Observability-Design</t>
+          <t>Definition der Geschäftsmaschine</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -4270,19 +4125,19 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế KPI và quan sát</t>
+          <t>Định nghĩa Bộ máy kinh doanh</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>KPIs &amp; Observability Design</t>
+          <t>Business Engine Definition</t>
         </is>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1" s="11">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>output.6.title</t>
+          <t>output.2.label</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -4292,17 +4147,17 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Output 06 title</t>
+          <t>Output 02 label</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Machine-Consumable System Spec</t>
+          <t>Output 02 — Workflow Architecture</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Maschinenlesbarer Systemspec</t>
+          <t>Output 02 — Workflow-Architektur</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -4322,19 +4177,19 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Đặc tả hệ thống dạng máy có thể sử dụng được</t>
+          <t>Kết quả 02 — Kiến trúc Quy trình làm việc</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Machine-Consumable System Spec</t>
+          <t>Output 02 — Workflow Architecture</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1" s="11">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>outputs.foot</t>
+          <t>output.2.title</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -4344,17 +4199,17 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Footer text below output grid</t>
+          <t>Output 02 title</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>For most teams, it's the first time the business becomes something that can actually be tested and reasoned about.</t>
+          <t>Process &amp; Authority Design</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Für die meisten Teams ist es das erste Mal, dass das Geschäft zu etwas wird, das tatsächlich getestet und durchdacht werden kann.</t>
+          <t>Prozess- und Autoritätsdesign</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -4374,46 +4229,71 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>Đối với hầu hết các nhóm, đó là lần đầu tiên kinh doanh trở thành một cái gì đó có thể thực sự được kiểm tra và suy luận.</t>
+          <t>Thiết kế quy trình và thẩm quyền</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>For most teams, it's the first time the business becomes something that can actually be tested and reasoned about.</t>
+          <t>Process &amp; Authority Design</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CASE</t>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>output.3.title</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>outputs</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>System Logic Design</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Systemlogik-Design</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Thiết kế Logic Hệ thống</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>System Logic Design</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1" s="11">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>case.section_label</t>
+          <t>output.4.title</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>outputs</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Section label</t>
+          <t>Output 04 title</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Proven in Real Systems</t>
+          <t>Build Specification (PRD)</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Bewährt in echten Systemen</t>
+          <t>Build-Spezifikation (PRD)</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -4433,39 +4313,39 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Được chứng minh trong các hệ thống thực</t>
+          <t>Đặc tả xây dựng (PRD)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Proven in Real Systems</t>
+          <t>Build Specification (PRD)</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1" s="11">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>case.tag</t>
+          <t>output.5.title</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>outputs</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Orange tag above heading</t>
+          <t>Output 05 title</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Flagship Case Study</t>
+          <t>KPIs &amp; Observability Design</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Flaggschiff-Fallstudie</t>
+          <t>KPIs und Observability-Design</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -4485,39 +4365,39 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Trường hợp điển hình chính</t>
+          <t>Thiết kế KPI và quan sát</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Flagship Case Study</t>
+          <t>KPIs &amp; Observability Design</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1" s="11">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>case.h</t>
+          <t>output.6.title</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>outputs</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Case study heading</t>
+          <t>Output 06 title</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Designing a $1B Genetics Business System</t>
+          <t>Machine-Consumable System Spec</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Gestaltung eines 1-Milliarden-Dollar-Genetik-Geschäftssystems</t>
+          <t>Maschinenlesbarer Systemspec</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -4537,39 +4417,39 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế hệ thống kinh doanh di truyền 1 tỷ USD</t>
+          <t>Đặc tả hệ thống dạng máy có thể sử dụng được</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Designing a $1B Genetics Business System</t>
+          <t>Machine-Consumable System Spec</t>
         </is>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1" s="11">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>case.sub</t>
+          <t>outputs.foot</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>case</t>
+          <t>outputs</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Case study subheading</t>
+          <t>Footer text below output grid</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>How a complex, multi-actor healthcare platform was structured to scale — before volume exposed its weaknesses.</t>
+          <t>For most teams, it's the first time the business becomes something that can actually be tested and reasoned about.</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Wie eine komplexe, mehrakteurige Healthcare-Plattform strukturiert wurde, um zu skalieren — bevor das Volumen ihre Schwächen enthüllte.</t>
+          <t>Für die meisten Teams ist es das erste Mal, dass das Geschäft zu etwas wird, das tatsächlich getestet und durchdacht werden kann.</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -4589,98 +4469,53 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Cách một nền tảng chăm sóc sức khỏe phức tạp, đa diễn viên được cấu trúc để mở rộng — trước khi khối lượng phơi bày những điểm yếu của nó.</t>
+          <t>Đối với hầu hết các nhóm, đó là lần đầu tiên kinh doanh trở thành một cái gì đó có thể thực sự được kiểm tra và suy luận.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>How a complex, multi-actor healthcare platform was structured to scale — before volume exposed its weaknesses.</t>
+          <t>For most teams, it's the first time the business becomes something that can actually be tested and reasoned about.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1" s="11">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>case.kl</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>case</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>Pull quote from case study</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>The system scaled because it was designed to work — not because it was iterated into shape.</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Das System skalierte, weil es zum Funktionieren entworfen wurde — nicht weil es iterativ in Form gebracht wurde.</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>Hệ thống mở rộng vì nó được thiết kế để hoạt động — không phải vì nó được lặp lại thành hình dạng.</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>The system scaled because it was designed to work — not because it was iterated into shape.</t>
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CASE</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FOR</t>
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>case.section_label</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1" s="11">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>for.section_label</t>
+          <t>case.tag</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>case</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Section label</t>
+          <t>Orange tag above heading</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Who This Is For</t>
+          <t>Flagship Case Study</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Für wen dies ist</t>
+          <t>Flaggschiff-Fallstudie</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -4700,39 +4535,39 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Đây là dành cho ai</t>
+          <t>Trường hợp điển hình chính</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Who This Is For</t>
+          <t>Flagship Case Study</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1" s="11">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>for.h</t>
+          <t>case.h</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>case</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Section heading</t>
+          <t>Case study heading</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Built for the people who have to get it right</t>
+          <t>Designing a $1B Genetics Business System</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Gebaut für diejenigen, die es richtig machen müssen</t>
+          <t>Gestaltung eines 1-Milliarden-Dollar-Genetik-Geschäftssystems</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -4752,39 +4587,39 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Được xây dựng cho những người phải làm đúng</t>
+          <t>Thiết kế hệ thống kinh doanh di truyền 1 tỷ USD</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Built for the people who have to get it right</t>
+          <t>Designing a $1B Genetics Business System</t>
         </is>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1" s="11">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>for.founders.role</t>
+          <t>case.sub</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>case</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Role label</t>
+          <t>Case study subheading</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Founders</t>
+          <t>How a complex, multi-actor healthcare platform was structured to scale — before volume exposed its weaknesses.</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Gründer</t>
+          <t>Wie eine komplexe, mehrakteurige Healthcare-Plattform strukturiert wurde, um zu skalieren — bevor das Volumen ihre Schwächen enthüllte.</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -4804,39 +4639,39 @@
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Nhà sáng lập</t>
+          <t>Cách một nền tảng chăm sóc sức khỏe phức tạp, đa diễn viên được cấu trúc để mở rộng — trước khi khối lượng phơi bày những điểm yếu của nó.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Founders</t>
+          <t>How a complex, multi-actor healthcare platform was structured to scale — before volume exposed its weaknesses.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1" s="11">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>for.founders.body</t>
+          <t>case.kl</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>case</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Pull quote from case study</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Turn ideas into structured, buildable systems. Build the right business, not just fast software.</t>
+          <t>The system scaled because it was designed to work — not because it was iterated into shape.</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Wandeln Sie Ideen in strukturierte, baubare Systeme um. Bauen Sie das richtige Geschäft, nicht nur schnelle Software.</t>
+          <t>Das System skalierte, weil es zum Funktionieren entworfen wurde — nicht weil es iterativ in Form gebracht wurde.</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -4856,71 +4691,26 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Biến ý tưởng thành những hệ thống có cấu trúc, có thể xây dựng được. Xây dựng kinh doanh đúng, không chỉ phần mềm nhanh.</t>
+          <t>Hệ thống mở rộng vì nó được thiết kế để hoạt động — không phải vì nó được lặp lại thành hình dạng.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Turn ideas into structured, buildable systems. Build the right business, not just fast software.</t>
+          <t>The system scaled because it was designed to work — not because it was iterated into shape.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1" s="11">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>for.operators.role</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>Role label</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Operators</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>Operatoren</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>Nhà điều hành</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Operators</t>
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FOR</t>
         </is>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1" s="11">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>for.investors.role</t>
+          <t>for.section_label</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -4930,17 +4720,17 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Role label</t>
+          <t>Section label</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Investors &amp; PE</t>
+          <t>Who This Is For</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Investoren &amp; PE</t>
+          <t>Für wen dies ist</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -4960,46 +4750,71 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Nhà đầu tư &amp; PE</t>
+          <t>Đây là dành cho ai</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Investors &amp; PE</t>
+          <t>Who This Is For</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LADDER</t>
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>for.h</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Built for founders, operators, and investors who think in systems.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Entwickelt für Gründer, Betreiber und Investoren, die in Systemen denken.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Được xây dựng cho những nhà sáng lập, nhà điều hành và các nhà đầu tư có tư duy hệ thống.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Built for founders, operators, and investors who think in systems.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1" s="11">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>ladder.section_label</t>
+          <t>for.founders.role</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ladder</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Section label</t>
+          <t>Role label</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>How We Work</t>
+          <t>Founders</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Wie wir arbeiten</t>
+          <t>Gründer</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -5019,335 +4834,290 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Cách chúng tôi làm việc</t>
+          <t>Nhà sáng lập</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>How We Work</t>
+          <t>Founders</t>
         </is>
       </c>
     </row>
     <row r="78" ht="36" customHeight="1" s="11">
       <c r="A78" s="7" t="inlineStr">
         <is>
+          <t>for.founders.body</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Turn ideas into structured, buildable systems. Build the right business, not just fast software.</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Wandeln Sie Ideen in strukturierte, baubare Systeme um. Bauen Sie das richtige Geschäft, nicht nur schnelle Software.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Biến ý tưởng thành những hệ thống có cấu trúc, có thể xây dựng được. Xây dựng kinh doanh đúng, không chỉ phần mềm nhanh.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Turn ideas into structured, buildable systems. Build the right business, not just fast software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1" s="11">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>for.operators.role</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Role label</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Operators</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Operatoren</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>Nhà điều hành</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Operators</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1" s="11">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>for.investors.role</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Role label</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Investors &amp; PE</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Investoren &amp; PE</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Nhà đầu tư &amp; PE</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Investors &amp; PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1" s="11">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LADDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1" s="11">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>ladder.section_label</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>ladder</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Section label</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>How We Work</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Wie wir arbeiten</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>Cách chúng tôi làm việc</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>How We Work</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1" s="11">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
           <t>ladder.h</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>ladder</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>Section heading</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Start anywhere.
 Go as far as you need.</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>Beginnen Sie überall.
 Gehen Sie so weit wie nötig.</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>Bắt đầu ở bất kỳ nơi nào.
 Đi xa như bạn cần.</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Start anywhere.
 Go as far as you need.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="36" customHeight="1" s="11">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>ladder.sub</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>ladder</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>Subheading</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Most clients begin with a single session. No commitment beyond that.</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>Die meisten Kunden beginnen mit einer einzelnen Sitzung. Keine Verpflichtung darüber hinaus.</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>Hầu hết khách hàng bắt đầu với một phiên duy nhất. Không có cam kết nào vượt ra ngoài điều đó.</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Most clients begin with a single session. No commitment beyond that.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="36" customHeight="1" s="11">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>ladder.step1.title</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>ladder</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>Step 1 title</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Discovery Session</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>Discovery Session</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>Phiên khám phá</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Discovery Session</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="36" customHeight="1" s="11">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>ladder.step2.title</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>ladder</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>Step 2 title</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>GEARS™ System Design</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>GEARS™ System Design</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Thiết kế hệ thống GEARS™</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>GEARS™ System Design</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="36" customHeight="1" s="11">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>ladder.step3.title</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>ladder</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Step 3 title</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Build Partnership</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>Build Partnership</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>Kết hợp xây dựng</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Build Partnership</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="36" customHeight="1" s="11">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>ladder.step4.title</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>ladder</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>Step 4 title</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Operate &amp; Evolve</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>Betreiben &amp; Weiterentwickeln</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>Vận hành và phát triển</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Operate &amp; Evolve</t>
-        </is>
-      </c>
-    </row>
     <row r="84" ht="36" customHeight="1" s="11">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>ladder.step1.cta</t>
+          <t>ladder.sub</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
@@ -5357,17 +5127,17 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>CTA link text</t>
+          <t>Subheading</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Book a session</t>
+          <t>Most clients begin with a single session. No commitment beyond that.</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Sitzung buchen</t>
+          <t>Die meisten Kunden beginnen mit einer einzelnen Sitzung. Keine Verpflichtung darüber hinaus.</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -5387,46 +5157,71 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>Đặt lịch một phiên</t>
+          <t>Hầu hết khách hàng bắt đầu với một phiên duy nhất. Không có cam kết nào vượt ra ngoài điều đó.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Book a session</t>
+          <t>Most clients begin with a single session. No commitment beyond that.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TESTI</t>
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>ladder.step1.title</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ladder</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Discovery Session</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Discovery-Sitzung</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Phiên Khám phá</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Discovery Session</t>
         </is>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1" s="11">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>testi.section_label</t>
+          <t>ladder.step2.title</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>testi</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Section label</t>
+          <t>Step 2 title</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Trusted by Operators</t>
+          <t>GEARS™ System Design</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Vertraut von Operatoren</t>
+          <t>GEARS™ System Design</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -5446,39 +5241,39 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Được tin tưởng bởi các nhà điều hành</t>
+          <t>Thiết kế hệ thống GEARS™</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Trusted by Operators</t>
+          <t>GEARS™ System Design</t>
         </is>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1" s="11">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>testi.quote</t>
+          <t>ladder.step3.title</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>testi</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Testimonial quote</t>
+          <t>Step 3 title</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>"GKIM helped brainstorm my vision and build it into a well thought out business, product and technology offering. The team have excelled at execution."</t>
+          <t>Build Partnership</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>"GKIM hat mir geholfen, meine Vision zu entwickeln und sie in ein durchdachtes Geschäfts-, Produkt- und Technologieangebot umzuwandeln. Das Team hat sich bei der Umsetzung hervorgetan."</t>
+          <t>Build Partnership</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -5498,39 +5293,39 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>"GKIM đã giúp tôi động não về tầm nhìn của mình và xây dựng nó thành một ưu đãi kinh doanh, sản phẩm và công nghệ được suy nghĩ kỹ lưỡng. Đội ngũ đã xuất sắc trong việc thực thi."</t>
+          <t>Kết hợp xây dựng</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>"GKIM helped brainstorm my vision and build it into a well thought out business, product and technology offering. The team have excelled at execution."</t>
+          <t>Build Partnership</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1" s="11">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>testi.attr</t>
+          <t>ladder.step4.title</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>testi</t>
+          <t>ladder</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Attribution below quote</t>
+          <t>Step 4 title</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Operate &amp; Evolve</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Gründer &amp; CEO</t>
+          <t>Betreiben &amp; Weiterentwickeln</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -5550,98 +5345,78 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>Nhà sáng lập &amp; CEO</t>
+          <t>Vận hành và phát triển</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Operate &amp; Evolve</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ABOUT</t>
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>ladder.step1.cta</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ladder</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Book a session</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Sitzung buchen</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Đặt lịch phiên</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Book a session</t>
         </is>
       </c>
     </row>
     <row r="90" ht="36" customHeight="1" s="11">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>about.section_label</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>Section label</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Why GKIM Exists</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Warum GKIM existiert</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>Tại sao GKIM tồn tại</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Why GKIM Exists</t>
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TESTI</t>
         </is>
       </c>
     </row>
     <row r="91" ht="36" customHeight="1" s="11">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>about.h</t>
+          <t>testi.section_label</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>testi</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>About section heading</t>
+          <t>Section label</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Built by Someone Who Has Done This Before</t>
+          <t>Trusted by Operators</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Gebaut von jemandem, der dies schon einmal getan hat</t>
+          <t>Vertraut von Operatoren</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -5661,39 +5436,39 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>Được xây dựng bởi ai đó đã thực hiện điều này trước đây</t>
+          <t>Được tin tưởng bởi các nhà điều hành</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Built by Someone Who Has Done This Before</t>
+          <t>Trusted by Operators</t>
         </is>
       </c>
     </row>
     <row r="92" ht="36" customHeight="1" s="11">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>about.letter.salutation</t>
+          <t>testi.quote</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>testi</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Letter opening</t>
+          <t>Testimonial quote</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>To the Founders and Leaders Building the Future,</t>
+          <t>"GKIM helped brainstorm my vision and build it into a well thought out business, product and technology offering. The team have excelled at execution."</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>An die Gründer und Führungskräfte, die die Zukunft gestalten,</t>
+          <t>"GKIM hat mir geholfen, meine Vision zu entwickeln und sie in ein durchdachtes Geschäfts-, Produkt- und Technologieangebot umzuwandeln. Das Team hat sich bei der Umsetzung hervorgetan."</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -5713,39 +5488,39 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>Gửi các nhà sáng lập và lãnh đạo đang xây dựng tương lai,</t>
+          <t>"GKIM đã giúp tôi động não về tầm nhìn của mình và xây dựng nó thành một ưu đãi kinh doanh, sản phẩm và công nghệ được suy nghĩ kỹ lưỡng. Đội ngũ đã xuất sắc trong việc thực thi."</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>To the Founders and Leaders Building the Future,</t>
+          <t>"GKIM helped brainstorm my vision and build it into a well thought out business, product and technology offering. The team have excelled at execution."</t>
         </is>
       </c>
     </row>
     <row r="93" ht="36" customHeight="1" s="11">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>about.sig</t>
+          <t>testi.attr</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>testi</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Attribution below quote</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>— Ian Morrison</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>— Ian Morrison</t>
+          <t>Gründer &amp; CEO</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -5765,98 +5540,53 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>— Ian Morrison</t>
+          <t>Nhà sáng lập &amp; CEO</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>— Ian Morrison</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
     </row>
     <row r="94" ht="36" customHeight="1" s="11">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>about.belief.title</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>Belief box title</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>What Makes GKIM Different</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>Was GKIM unterscheidet</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>Điều gì làm cho GKIM khác biệt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>What Makes GKIM Different</t>
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ABOUT</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  START</t>
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>about.section_label</t>
         </is>
       </c>
     </row>
     <row r="96" ht="36" customHeight="1" s="11">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>start.section_label</t>
+          <t>about.h</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>about</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Section label</t>
+          <t>About section heading</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Talk to GKIM</t>
+          <t>Built by Someone Who Has Done This Before</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Mit GKIM sprechen</t>
+          <t>Gebaut von jemandem, der dies schon einmal getan hat</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -5876,39 +5606,39 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>Liên hệ GKIM</t>
+          <t>Được xây dựng bởi ai đó đã thực hiện điều này trước đây</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Talk to GKIM</t>
+          <t>Built by Someone Who Has Done This Before</t>
         </is>
       </c>
     </row>
     <row r="97" ht="36" customHeight="1" s="11">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>start.h</t>
+          <t>about.letter.salutation</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>about</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Contact section heading</t>
+          <t>Letter opening</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Before you build or scale, understand how your business actually works.</t>
+          <t>To the Founders and Leaders Building the Future,</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Bevor Sie bauen oder skalieren, verstehen Sie, wie Ihr Geschäft tatsächlich funktioniert.</t>
+          <t>An die Gründer und Führungskräfte, die die Zukunft gestalten,</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -5928,39 +5658,39 @@
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>Trước khi bạn xây dựng hoặc mở rộng quy mô, hãy hiểu cách kinh doanh của bạn thực sự hoạt động.</t>
+          <t>Gửi các nhà sáng lập và lãnh đạo đang xây dựng tương lai,</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Before you build or scale, understand how your business actually works.</t>
+          <t>To the Founders and Leaders Building the Future,</t>
         </is>
       </c>
     </row>
     <row r="98" ht="36" customHeight="1" s="11">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>start.sub</t>
+          <t>about.sig</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>about</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Contact section subheading</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>This is not a sales call. It is a working session to understand your business model, explore how the system currently operates, and identify gaps, risks, and assumptions.</t>
+          <t>— Ian Morrison</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Dies ist kein Verkaufsgespräch. Es ist eine Arbeitssitzung, um Ihr Geschäftsmodell zu verstehen, zu erkunden, wie das System derzeit funktioniert, und Lücken, Risiken und Annahmen zu identifizieren.</t>
+          <t>— Ian Morrison</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -5980,39 +5710,39 @@
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>Đây không phải là cuộc gọi bán hàng. Nó là một phiên làm việc để hiểu mô hình kinh doanh của bạn, khám phá cách hệ thống hiện đang hoạt động, và xác định những khoảng trống, rủi ro và giả định.</t>
+          <t>— Ian Morrison</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>This is not a sales call. It is a working session to understand your business model, explore how the system currently operates, and identify gaps, risks, and assumptions.</t>
+          <t>— Ian Morrison</t>
         </is>
       </c>
     </row>
     <row r="99" ht="36" customHeight="1" s="11">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>start.kl</t>
+          <t>about.belief.title</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>about</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Keyline below items list</t>
+          <t>Belief box title</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Clarity replaces assumption.</t>
+          <t>What Makes GKIM Different</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Klarheit ersetzt Annahmen.</t>
+          <t>Was GKIM unterscheidet</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -6032,71 +5762,26 @@
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>Sự rõ ràng thay thế giả định.</t>
+          <t>Điều gì làm cho GKIM khác biệt</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Clarity replaces assumption.</t>
+          <t>What Makes GKIM Different</t>
         </is>
       </c>
     </row>
     <row r="100" ht="36" customHeight="1" s="11">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>form.intro</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>Form intro text</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Tell us what you're building, where you are in the journey, and what feels unclear or not working.</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>Erzählen Sie uns, was Sie bauen, wo Sie sich auf der Reise befinden und was unklar oder nicht funktionierend wirkt.</t>
-        </is>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>Hãy cho chúng tôi biết bạn đang xây dựng cái gì, bạn đang ở đâu trong cuộc hành trình, và điều gì cảm thấy không rõ ràng hoặc không hoạt động.</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Tell us what you're building, where you are in the journey, and what feels unclear or not working.</t>
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  START</t>
         </is>
       </c>
     </row>
     <row r="101" ht="36" customHeight="1" s="11">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>form.label.name</t>
+          <t>start.section_label</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
@@ -6106,49 +5791,49 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Form field label</t>
+          <t>Section label</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Naam</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>Tên</t>
+          <t>Talk to GKIM</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Mit GKIM sprechen</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>Liên hệ GKIM</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Talk to GKIM</t>
         </is>
       </c>
     </row>
     <row r="102" ht="36" customHeight="1" s="11">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>form.label.company</t>
+          <t>start.h</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -6158,49 +5843,49 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Form field label</t>
+          <t>Contact section heading</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Unternehmen</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Entreprise</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Bedrijf</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>公司</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Công ty</t>
+          <t>Before you build or scale, understand how your business actually works.</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Bevor Sie bauen oder skalieren, verstehen Sie, wie Ihr Geschäft tatsächlich funktioniert.</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>Trước khi bạn xây dựng hoặc mở rộng quy mô, hãy hiểu cách kinh doanh của bạn thực sự hoạt động.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Before you build or scale, understand how your business actually works.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="36" customHeight="1" s="11">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>form.label.email</t>
+          <t>start.sub</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
@@ -6210,49 +5895,49 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Form field label</t>
+          <t>Contact section subheading</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>E-Mail</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>邮箱</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
+          <t>This is not a sales call. It is a working session to understand your business model, explore how the system currently operates, and identify gaps, risks, and assumptions.</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Dies ist kein Verkaufsgespräch. Es ist eine Arbeitssitzung, um Ihr Geschäftsmodell zu verstehen, zu erkunden, wie das System derzeit funktioniert, und Lücken, Risiken und Annahmen zu identifizieren.</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>Đây không phải là cuộc gọi bán hàng. Nó là một phiên làm việc để hiểu mô hình kinh doanh của bạn, khám phá cách hệ thống hiện đang hoạt động, và xác định những khoảng trống, rủi ro và giả định.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>This is not a sales call. It is a working session to understand your business model, explore how the system currently operates, and identify gaps, risks, and assumptions.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="36" customHeight="1" s="11">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>form.label.message</t>
+          <t>start.kl</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
@@ -6262,17 +5947,17 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Form textarea label</t>
+          <t>Keyline below items list</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>What are you building or what isn't working?</t>
+          <t>Clarity replaces assumption.</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Was bauen Sie oder was funktioniert nicht?</t>
+          <t>Klarheit ersetzt Annahmen.</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
@@ -6292,19 +5977,19 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>Bạn đang xây dựng cái gì hoặc cái gì không hoạt động?</t>
+          <t>Sự rõ ràng thay thế giả định.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>What are you building or what isn't working?</t>
+          <t>Clarity replaces assumption.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="36" customHeight="1" s="11">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>form.placeholder.message</t>
+          <t>form.intro</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -6314,17 +5999,17 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Form textarea placeholder</t>
+          <t>Form intro text</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Share as much or as little as you'd like...</t>
+          <t>Tell us what you're building, where you are in the journey, and what feels unclear or not working.</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Teilen Sie so viel oder so wenig mit, wie Sie möchten...</t>
+          <t>Erzählen Sie uns, was Sie bauen, wo Sie sich auf der Reise befinden und was unklar oder nicht funktionierend wirkt.</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -6344,19 +6029,19 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Chia sẻ bao nhiêu hoặc ít như bạn muốn...</t>
+          <t>Hãy cho chúng tôi biết bạn đang xây dựng cái gì, bạn đang ở đâu trong cuộc hành trình, và điều gì cảm thấy không rõ ràng hoặc không hoạt động.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Share as much or as little as you'd like...</t>
+          <t>Tell us what you're building, where you are in the journey, and what feels unclear or not working.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="36" customHeight="1" s="11">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>form.btn</t>
+          <t>form.label.name</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -6366,128 +6051,153 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Form submit button</t>
+          <t>Form field label</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Book a Session</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>Sitzung buchen</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>Đặt lịch một phiên</t>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Naam</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Tên</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Book a Session</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CTA</t>
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>form.label.company</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Unternehmen</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Công ty</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Company</t>
         </is>
       </c>
     </row>
     <row r="108" ht="36" customHeight="1" s="11">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>cta.h</t>
+          <t>form.label.email</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>cta</t>
+          <t>start</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Final CTA heading</t>
+          <t>Form field label</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Design the business before you build it</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>Gestalten Sie das Geschäft, bevor Sie es bauen</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>Thiết kế kinh doanh trước khi bạn xây dựng nó</t>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>邮箱</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Design the business before you build it</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="109" ht="36" customHeight="1" s="11">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>cta.body</t>
+          <t>form.label.message</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>cta</t>
+          <t>start</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Final CTA body</t>
+          <t>Form textarea label</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Most teams start with code. The best teams start with clarity.</t>
+          <t>What are you building or what isn't working?</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>Die meisten Teams beginnen mit Code. Die besten Teams beginnen mit Klarheit.</t>
+          <t>Was bauen Sie oder was funktioniert nicht?</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
@@ -6507,150 +6217,150 @@
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>Hầu hết các nhóm bắt đầu bằng mã. Các đội tốt nhất bắt đầu với sự rõ ràng.</t>
+          <t>Bạn đang xây dựng cái gì hoặc cái gì không hoạt động?</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Most teams start with code. The best teams start with clarity.</t>
+          <t>What are you building or what isn't working?</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1" s="11">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>cta.btn.primary</t>
+          <t>form.placeholder.message</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>cta</t>
+          <t>start</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Primary CTA button</t>
+          <t>Form textarea placeholder</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Talk to GKIM</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Mit GKIM sprechen</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Discutons</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Contact opnemen</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>联系我们</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>Liên hệ GKIM</t>
+          <t>Share as much or as little as you'd like...</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Teilen Sie so viel oder so wenig mit, wie Sie möchten...</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>Chia sẻ bao nhiêu hoặc ít như bạn muốn...</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Talk to GKIM</t>
+          <t>Share as much or as little as you'd like...</t>
         </is>
       </c>
     </row>
     <row r="111" ht="36" customHeight="1" s="11">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>cta.btn.secondary</t>
+          <t>form.btn</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>cta</t>
+          <t>start</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Secondary CTA — email link</t>
+          <t>Form submit button</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>hello@gkim.digital</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>hello@gkim.digital</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>hello@gkim.digital</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>hello@gkim.digital</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>hello@gkim.digital</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>hello@gkim.digital</t>
+          <t>Book a Session</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>Sitzung buchen</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Đặt lịch một phiên</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>hello@gkim.digital</t>
+          <t>Book a Session</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FOOTER</t>
+          <t xml:space="preserve">  CTA</t>
         </is>
       </c>
     </row>
     <row r="113" ht="36" customHeight="1" s="11">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>footer.tag</t>
+          <t>cta.h</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>cta</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Footer tagline below logo</t>
+          <t>Final CTA heading</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>We define the missing layer between strategy and engineering — how your business actually works as a system.</t>
+          <t>Design the business before you build it</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Wir definieren die fehlende Schicht zwischen Strategie und Technik — wie Ihr Geschäft tatsächlich als System funktioniert.</t>
+          <t>Gestalten Sie das Geschäft, bevor Sie es bauen</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -6670,39 +6380,39 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>Chúng tôi định nghĩa lớp bị thiếu giữa chiến lược và kỹ thuật — cách kinh doanh của bạn thực sự hoạt động như một hệ thống.</t>
+          <t>Thiết kế kinh doanh trước khi bạn xây dựng nó</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>We define the missing layer between strategy and engineering — how your business actually works as a system.</t>
+          <t>Design the business before you build it</t>
         </is>
       </c>
     </row>
     <row r="114" ht="36" customHeight="1" s="11">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>footer.col.explore</t>
+          <t>cta.body</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>cta</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Footer column heading</t>
+          <t>Final CTA body</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Most teams start with code. The best teams start with clarity.</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Erkunden</t>
+          <t>Die meisten Teams beginnen mit Code. Die besten Teams beginnen mit Klarheit.</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
@@ -6722,202 +6432,182 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>Khám phá</t>
+          <t>Hầu hết các nhóm bắt đầu bằng mã. Các đội tốt nhất bắt đầu với sự rõ ràng.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Most teams start with code. The best teams start with clarity.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="36" customHeight="1" s="11">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>footer.col.contact</t>
+          <t>cta.btn.primary</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>footer</t>
+          <t>cta</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Footer column heading</t>
+          <t>Primary CTA button</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>Kontakt</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H115" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>Liên hệ</t>
+          <t>Talk to GKIM</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Mit GKIM sprechen</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Discutons</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Contact opnemen</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>联系我们</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Liên hệ GKIM</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Talk to GKIM</t>
         </is>
       </c>
     </row>
     <row r="116" ht="36" customHeight="1" s="11">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>footer.copyright</t>
+          <t>cta.btn.secondary</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Secondary CTA — email link</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>hello@gkim.digital</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>hello@gkim.digital</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>hello@gkim.digital</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>hello@gkim.digital</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>hello@gkim.digital</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>hello@gkim.digital</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>hello@gkim.digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1" s="11">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FOOTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>footer.tag</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>footer</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>Copyright line</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>© GKIM Digital Ltd.</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>© GKIM Digital Ltd.</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>© GKIM Digital Ltd.</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>© GKIM Digital Ltd.</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>© GKIM Digital Ltd.</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>© GKIM Digital Ltd.</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>© GKIM Digital Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="36" customHeight="1" s="11">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>footer.descriptor</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>footer</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>Descriptor line</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>System definition. AI-native business design.</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>Systemdefinition. KI-natives Business Design.</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>Định nghĩa hệ thống. Thiết kế kinh doanh native AI.</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>System definition. AI-native business design.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  META</t>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Design your AI-native business.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Gestalten Sie Ihr KI-natives Geschäft.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Thiết kế doanh nghiệp của bạn theo hướng AI-native.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Design your AI-native business.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="36" customHeight="1" s="11">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>page.title</t>
+          <t>footer.col.explore</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>footer</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Browser tab title — keep under 60 chars</t>
+          <t>Footer column heading</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>GKIM Digital — Design Your AI-Native Business</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>GKIM Digital — Gestalten Sie Ihr KI-natives Geschäft</t>
+          <t>Erkunden</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -6937,86 +6627,283 @@
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>GKIM Digital — Thiết kế kinh doanh của bạn với AI</t>
+          <t>Khám phá</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>GKIM Digital — Design Your AI-Native Business</t>
+          <t>Explore</t>
         </is>
       </c>
     </row>
     <row r="120" ht="36" customHeight="1" s="11">
       <c r="A120" s="7" t="inlineStr">
         <is>
+          <t>footer.col.contact</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Footer column heading</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Kontakt</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>footer.copyright</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Copyright line</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>© GKIM Digital Ltd.</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>© GKIM Digital Ltd.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>© GKIM Digital Ltd.</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>© GKIM Digital Ltd.</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>© GKIM Digital Ltd.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>© GKIM Digital Ltd.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>© GKIM Digital Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>footer.descriptor</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Descriptor line</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>System definition. AI-native business design.</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>Systemdefinition. KI-natives Business Design.</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>Định nghĩa hệ thống. Thiết kế kinh doanh native AI.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>System definition. AI-native business design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  META</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>page.title</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Browser tab title — keep under 60 chars</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>GKIM Digital — Design Your AI-Native Business</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>GKIM Digital — Gestalten Sie Ihr KI-natives Geschäft</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>— TO BE TRANSLATED —</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>GKIM Digital — Thiết kế kinh doanh của bạn với AI</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>GKIM Digital — Design Your AI-Native Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
           <t>page.lang</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>meta</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>HTML lang attribute — do not translate</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>fr</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>nl</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>zh-Hans</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>vi</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A95:I95"/>
-    <mergeCell ref="A112:I112"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A63:I63"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A89:I89"/>
-    <mergeCell ref="A107:I107"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A69:I69"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7463,7 +7350,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -1452,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="11" min="1" max="1"/>
@@ -6900,6 +6900,692 @@
       <c r="J125" t="inlineStr">
         <is>
           <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>papers.title</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Go-deeper bridge section heading</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>GKIM Papers —
+Original thinking on
+AI-native business design</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>GKIM Papers —
+Originäres Denken über
+KI-native Geschäftsmodelle</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>GKIM Papers —
+Tư duy độc lập về
+thiết kế kinh doanh theo hướng AI</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>GKIM Papers —
+Original thinking on
+AI-native business design</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>papers.sub</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Fifteen papers across five themes. Written for founders, operators, and investors who want to understand the architecture of what's coming.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Fünfzehn Papiere über fünf Themen. Geschrieben für Gründer, Operatoren und Investoren, die die Architektur der kommenden Entwicklungen verstehen möchten.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Mười lăm bài viết trên năm chủ đề. Viết cho các nhà sáng lập, những người điều hành và nhà đầu tư muốn hiểu rõ kiến trúc của những gì sắp tới.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Fifteen papers across five themes. Written for founders, operators, and investors who want to understand the architecture of what's coming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>papers.s1.section</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Category label</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Grundlagen</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Nền tảng</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>papers.s1.name</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Category subtitle</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>What is an AI-Native Business?</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Was ist ein KI-natives Geschäftsmodell?</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Kinh doanh theo hướng AI là gì?</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>What is an AI-Native Business?</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>papers.s1.count</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Paper count label</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>3 Papiere</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3 bài viết</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>papers.s2.section</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Category label</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>The Case For</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Das Argument dafür</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Lý do để tin tưởng</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>The Case For</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>papers.s2.name</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Category subtitle</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>The Strategic &amp; Economic Argument</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Das strategische und ökonomische Argument</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Lập luận chiến lược và kinh tế</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>The Strategic &amp; Economic Argument</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>papers.s2.count</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>3 Papiere</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>3 bài viết</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>papers.s3.section</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Category label</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Vertrauen und Sicherheit</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Tin tưởng &amp; An toàn</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>papers.s3.name</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Category subtitle</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Governance, Humans &amp; Accountability</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Governance, Menschen und Verantwortung</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Quản lý, Con người &amp; Trách nhiệm</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Governance, Humans &amp; Accountability</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>papers.s3.count</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>3 Papiere</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3 bài viết</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>papers.s4.section</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Category label</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Founder's Playbook</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Playbook für Gründer</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Sổ tay nhà sáng lập</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Founder's Playbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>papers.s4.name</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Category subtitle</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Practical Conviction for Builders</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Praktische Überzeugung für Builder</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Quyết tâm thực tiễn cho những người xây dựng</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Practical Conviction for Builders</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>papers.s4.count</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>3 Papiere</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>3 bài viết</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>papers.s5.section</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Category label</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Architecture &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Architektur und Lebenszyklus</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Kiến trúc &amp; Vòng đời</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Architecture &amp; Lifecycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>papers.s5.name</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Category subtitle</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>How These Businesses Are Built</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Wie diese Geschäftsmodelle aufgebaut sind</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Cách các doanh nghiệp này được xây dựng</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>How These Businesses Are Built</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>papers.s5.count</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>3 Papiere</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>3 bài viết</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>papers.foot</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Footer note</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Each paper is 7–11 minutes. Full PDFs coming soon. Written from Cambridge — not from a conference stage.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Jedes Papier dauert 7–11 Minuten zum Lesen. Vollständige PDFs folgen in Kürze. Geschrieben aus Cambridge — nicht von einer Konferenzbühne.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Mỗi bài viết mất 7–11 phút để đọc. Toàn bộ PDF sẽ ra mắt sớm. Viết từ Cambridge — không phải từ một sân khấu hội thảo.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Each paper is 7–11 minutes. Full PDFs coming soon. Written from Cambridge — not from a conference stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>papers.cta</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CTA link text</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Read GKIM Papers →</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>GKIM Papers lesen →</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Đọc GKIM Papers →</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Read GKIM Papers →</t>
         </is>
       </c>
     </row>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="11" min="1" max="1"/>
@@ -871,6 +871,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>flag</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="36" customHeight="1" s="11">
       <c r="A2" s="2" t="inlineStr">
@@ -913,6 +918,11 @@
           <t>Canonical — default. Global audience. Current site copy.</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🇬🇧</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1" s="11">
       <c r="A3" s="2" t="inlineStr">
@@ -955,6 +965,11 @@
           <t>Priority European market. Emphasis on rigour, methodology, enterprise credibility.</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🇩🇪</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1" s="11">
       <c r="A4" s="2" t="inlineStr">
@@ -997,6 +1012,11 @@
           <t>Strategic framing, intellectual positioning. Paris/Brussels audience.</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🇫🇷</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1" s="11">
       <c r="A5" s="2" t="inlineStr">
@@ -1039,6 +1059,11 @@
           <t>Commercial directness. Amsterdam/Rotterdam tech and VC audience.</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🇳🇱</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1" s="11">
       <c r="A6" s="2" t="inlineStr">
@@ -1081,6 +1106,11 @@
           <t>Systems thinking, enterprise value, Cambridge credibility. APAC enterprise.</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🇨🇳</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1" s="11">
       <c r="A7" s="2" t="inlineStr">
@@ -1121,6 +1151,11 @@
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>HCMC office presence, regional expertise, founder story. Vietnam market.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🇻🇳</t>
         </is>
       </c>
     </row>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -164,13 +164,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,18 +539,18 @@
   <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="11" min="1" max="1"/>
-    <col width="80" customWidth="1" style="11" min="2" max="2"/>
+    <col width="22" customWidth="1" style="12" min="1" max="1"/>
+    <col width="80" customWidth="1" style="12" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="11">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="12">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>GKIM Digital — Multilingual Content Workbook</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="11">
+    <row r="2" ht="30" customHeight="1" s="12">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
@@ -562,11 +562,11 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="11">
+    <row r="3" ht="18" customHeight="1" s="12">
       <c r="A3" s="3" t="n"/>
       <c r="B3" s="2" t="n"/>
     </row>
-    <row r="4" ht="18" customHeight="1" s="11">
+    <row r="4" ht="18" customHeight="1" s="12">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>SHEETS</t>
@@ -574,7 +574,7 @@
       </c>
       <c r="B4" s="2" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="11">
+    <row r="5" ht="18" customHeight="1" s="12">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>1. README</t>
@@ -586,7 +586,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="11">
+    <row r="6" ht="30" customHeight="1" s="12">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2. languages</t>
@@ -598,7 +598,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="11">
+    <row r="7" ht="30" customHeight="1" s="12">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>3. strategic_emphasis</t>
@@ -610,7 +610,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="11">
+    <row r="8" ht="30" customHeight="1" s="12">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>4. strings</t>
@@ -622,7 +622,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="11">
+    <row r="9" ht="30" customHeight="1" s="12">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>5. meta_seo</t>
@@ -634,7 +634,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="11">
+    <row r="10" ht="30" customHeight="1" s="12">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>6. config</t>
@@ -646,11 +646,11 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" s="11">
+    <row r="11" ht="18" customHeight="1" s="12">
       <c r="A11" s="3" t="n"/>
       <c r="B11" s="2" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="11">
+    <row r="12" ht="18" customHeight="1" s="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>HOW TO USE</t>
@@ -658,7 +658,7 @@
       </c>
       <c r="B12" s="2" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="11">
+    <row r="13" ht="30" customHeight="1" s="12">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Step 1</t>
@@ -670,7 +670,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="11">
+    <row r="14" ht="30" customHeight="1" s="12">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Step 2</t>
@@ -682,7 +682,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="11">
+    <row r="15" ht="30" customHeight="1" s="12">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Step 3</t>
@@ -694,7 +694,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="11">
+    <row r="16" ht="30" customHeight="1" s="12">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Step 4</t>
@@ -706,7 +706,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="11">
+    <row r="17" ht="30" customHeight="1" s="12">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Step 5</t>
@@ -718,11 +718,11 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" s="11">
+    <row r="18" ht="18" customHeight="1" s="12">
       <c r="A18" s="3" t="n"/>
       <c r="B18" s="2" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="11">
+    <row r="19" ht="18" customHeight="1" s="12">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>RULES</t>
@@ -730,7 +730,7 @@
       </c>
       <c r="B19" s="2" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="11">
+    <row r="20" ht="18" customHeight="1" s="12">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Do not rename sheets</t>
@@ -742,7 +742,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="11">
+    <row r="21" ht="30" customHeight="1" s="12">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Do not rename column headers</t>
@@ -754,7 +754,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" s="11">
+    <row r="22" ht="18" customHeight="1" s="12">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Keep the key column</t>
@@ -766,7 +766,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="11">
+    <row r="23" ht="30" customHeight="1" s="12">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Mark status</t>
@@ -778,11 +778,11 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" s="11">
+    <row r="24" ht="18" customHeight="1" s="12">
       <c r="A24" s="3" t="n"/>
       <c r="B24" s="2" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="11">
+    <row r="25" ht="18" customHeight="1" s="12">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Version</t>
@@ -794,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1" s="11">
+    <row r="26" ht="18" customHeight="1" s="12">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Maintained by</t>
@@ -823,14 +823,14 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="11" min="1" max="1"/>
-    <col width="18" customWidth="1" style="11" min="2" max="3"/>
-    <col width="12" customWidth="1" style="11" min="4" max="5"/>
-    <col width="10" customWidth="1" style="11" min="6" max="7"/>
-    <col width="45" customWidth="1" style="11" min="8" max="8"/>
+    <col width="8" customWidth="1" style="12" min="1" max="1"/>
+    <col width="18" customWidth="1" style="12" min="2" max="3"/>
+    <col width="12" customWidth="1" style="12" min="4" max="5"/>
+    <col width="10" customWidth="1" style="12" min="6" max="7"/>
+    <col width="45" customWidth="1" style="12" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="11">
+    <row r="1" ht="22" customHeight="1" s="12">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>code</t>
@@ -877,7 +877,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" s="11">
+    <row r="2" ht="36" customHeight="1" s="12">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>en</t>
@@ -924,7 +924,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" s="11">
+    <row r="3" ht="36" customHeight="1" s="12">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>de</t>
@@ -971,7 +971,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" s="11">
+    <row r="4" ht="36" customHeight="1" s="12">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>fr</t>
@@ -997,7 +997,7 @@
           <t>fr</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" s="11">
+    <row r="5" ht="36" customHeight="1" s="12">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>nl</t>
@@ -1044,7 +1044,7 @@
           <t>nl</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" s="11">
+    <row r="6" ht="36" customHeight="1" s="12">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>zh</t>
@@ -1091,7 +1091,7 @@
           <t>zh-Hans</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" s="11">
+    <row r="7" ht="36" customHeight="1" s="12">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>vi</t>
@@ -1161,6 +1161,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1173,16 +1174,16 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="11" min="1" max="1"/>
-    <col width="25" customWidth="1" style="11" min="2" max="2"/>
-    <col width="40" customWidth="1" style="11" min="3" max="3"/>
-    <col width="20" customWidth="1" style="11" min="4" max="4"/>
-    <col width="40" customWidth="1" style="11" min="5" max="6"/>
-    <col width="25" customWidth="1" style="11" min="7" max="7"/>
-    <col width="35" customWidth="1" style="11" min="8" max="8"/>
+    <col width="10" customWidth="1" style="12" min="1" max="1"/>
+    <col width="25" customWidth="1" style="12" min="2" max="2"/>
+    <col width="40" customWidth="1" style="12" min="3" max="3"/>
+    <col width="20" customWidth="1" style="12" min="4" max="4"/>
+    <col width="40" customWidth="1" style="12" min="5" max="6"/>
+    <col width="25" customWidth="1" style="12" min="7" max="7"/>
+    <col width="35" customWidth="1" style="12" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="11">
+    <row r="1" ht="22" customHeight="1" s="12">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>language</t>
@@ -1224,7 +1225,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="72" customHeight="1" s="11">
+    <row r="2" ht="72" customHeight="1" s="12">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>en</t>
@@ -1266,7 +1267,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1" s="11">
+    <row r="3" ht="72" customHeight="1" s="12">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>de</t>
@@ -1308,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1" s="11">
+    <row r="4" ht="72" customHeight="1" s="12">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>fr</t>
@@ -1350,7 +1351,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1" s="11">
+    <row r="5" ht="72" customHeight="1" s="12">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>nl</t>
@@ -1392,7 +1393,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1" s="11">
+    <row r="6" ht="72" customHeight="1" s="12">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>zh</t>
@@ -1434,7 +1435,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1" s="11">
+    <row r="7" ht="72" customHeight="1" s="12">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>vi</t>
@@ -1490,14 +1491,14 @@
   <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="11" min="1" max="1"/>
-    <col width="14" customWidth="1" style="11" min="2" max="2"/>
-    <col width="30" customWidth="1" style="11" min="3" max="3"/>
-    <col width="45" customWidth="1" style="11" min="4" max="6"/>
-    <col width="28" customWidth="1" style="11" min="7" max="8"/>
+    <col width="28" customWidth="1" style="12" min="1" max="1"/>
+    <col width="14" customWidth="1" style="12" min="2" max="2"/>
+    <col width="30" customWidth="1" style="12" min="3" max="3"/>
+    <col width="45" customWidth="1" style="12" min="4" max="6"/>
+    <col width="28" customWidth="1" style="12" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="11">
+    <row r="1" ht="22" customHeight="1" s="12">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>key</t>
@@ -1550,13 +1551,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  NAV</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" s="11">
+    <row r="3" ht="36" customHeight="1" s="12">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>nav.section_label</t>
@@ -1608,7 +1609,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" s="11">
+    <row r="4" ht="36" customHeight="1" s="12">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>nav.link.vision</t>
@@ -1660,7 +1661,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" s="11">
+    <row r="5" ht="36" customHeight="1" s="12">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>nav.link.gears</t>
@@ -1712,7 +1713,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" s="11">
+    <row r="6" ht="36" customHeight="1" s="12">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>nav.link.outputs</t>
@@ -1764,7 +1765,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" s="11">
+    <row r="7" ht="36" customHeight="1" s="12">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>nav.link.case</t>
@@ -1816,7 +1817,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" s="11">
+    <row r="8" ht="36" customHeight="1" s="12">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>nav.link.about</t>
@@ -1868,7 +1869,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" s="11">
+    <row r="9" ht="36" customHeight="1" s="12">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>nav.cta</t>
@@ -1921,13 +1922,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  HERO</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1" s="11">
+    <row r="11" ht="36" customHeight="1" s="12">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>hero.eyebrow</t>
@@ -1979,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" s="11">
+    <row r="12" ht="36" customHeight="1" s="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>hero.h1</t>
@@ -2031,7 +2032,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" s="11">
+    <row r="13" ht="36" customHeight="1" s="12">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>hero.sub</t>
@@ -2083,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" s="11">
+    <row r="14" ht="36" customHeight="1" s="12">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>hero.support</t>
@@ -2135,7 +2136,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" s="11">
+    <row r="15" ht="36" customHeight="1" s="12">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>hero.cta.primary</t>
@@ -2187,7 +2188,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" s="11">
+    <row r="16" ht="36" customHeight="1" s="12">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>hero.cta.secondary</t>
@@ -2240,13 +2241,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  STATS</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1" s="11">
+    <row r="18" ht="36" customHeight="1" s="12">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>stat.1.label</t>
@@ -2298,7 +2299,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1" s="11">
+    <row r="19" ht="36" customHeight="1" s="12">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>stat.2.label</t>
@@ -2350,7 +2351,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1" s="11">
+    <row r="20" ht="36" customHeight="1" s="12">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>stat.3.label</t>
@@ -2402,7 +2403,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1" s="11">
+    <row r="21" ht="36" customHeight="1" s="12">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>stat.4.label</t>
@@ -2454,7 +2455,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="11">
+    <row r="22" ht="36" customHeight="1" s="12">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>stat.tag</t>
@@ -2507,13 +2508,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  SHIFT</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1" s="11">
+    <row r="24" ht="36" customHeight="1" s="12">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>shift.section_label</t>
@@ -2565,7 +2566,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1" s="11">
+    <row r="25" ht="36" customHeight="1" s="12">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>shift.h</t>
@@ -2617,7 +2618,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1" s="11">
+    <row r="26" ht="36" customHeight="1" s="12">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>shift.p1</t>
@@ -2669,7 +2670,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1" s="11">
+    <row r="27" ht="36" customHeight="1" s="12">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>shift.p2</t>
@@ -2721,7 +2722,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1" s="11">
+    <row r="28" ht="36" customHeight="1" s="12">
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>shift.p3</t>
@@ -2773,7 +2774,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1" s="11">
+    <row r="29" ht="36" customHeight="1" s="12">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t>shift.quote</t>
@@ -2829,7 +2830,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1" s="11">
+    <row r="30" ht="36" customHeight="1" s="12">
       <c r="A30" t="inlineStr">
         <is>
           <t>shift.list.1</t>
@@ -2861,7 +2862,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1" s="11">
+    <row r="31" ht="36" customHeight="1" s="12">
       <c r="A31" t="inlineStr">
         <is>
           <t>shift.list.2</t>
@@ -2925,7 +2926,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1" s="11">
+    <row r="33" ht="36" customHeight="1" s="12">
       <c r="A33" t="inlineStr">
         <is>
           <t>shift.list.4</t>
@@ -2957,7 +2958,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1" s="11">
+    <row r="34" ht="36" customHeight="1" s="12">
       <c r="A34" t="inlineStr">
         <is>
           <t>shift.list.5</t>
@@ -2989,7 +2990,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1" s="11">
+    <row r="35" ht="36" customHeight="1" s="12">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>struct.label</t>
@@ -3041,7 +3042,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1" s="11">
+    <row r="36" ht="36" customHeight="1" s="12">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>struct.quote</t>
@@ -3094,13 +3095,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  VISION</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1" s="11">
+    <row r="38" ht="36" customHeight="1" s="12">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>vision.section_label</t>
@@ -3152,7 +3153,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="36" customHeight="1" s="11">
+    <row r="39" ht="36" customHeight="1" s="12">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>vision.h</t>
@@ -3204,7 +3205,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="36" customHeight="1" s="11">
+    <row r="40" ht="36" customHeight="1" s="12">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>vision.fear.intro</t>
@@ -3256,7 +3257,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="36" customHeight="1" s="11">
+    <row r="41" ht="36" customHeight="1" s="12">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t>vision.kl</t>
@@ -3312,14 +3313,14 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="36" customHeight="1" s="11">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="42" ht="36" customHeight="1" s="12">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  GEARS</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="36" customHeight="1" s="11">
+    <row r="43" ht="36" customHeight="1" s="12">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>gears.section_label</t>
@@ -3371,7 +3372,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="36" customHeight="1" s="11">
+    <row r="44" ht="36" customHeight="1" s="12">
       <c r="A44" s="7" t="inlineStr">
         <is>
           <t>gears.h</t>
@@ -3423,7 +3424,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="36" customHeight="1" s="11">
+    <row r="45" ht="36" customHeight="1" s="12">
       <c r="A45" s="7" t="inlineStr">
         <is>
           <t>gears.intro.p1</t>
@@ -3475,7 +3476,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="36" customHeight="1" s="11">
+    <row r="46" ht="36" customHeight="1" s="12">
       <c r="A46" s="7" t="inlineStr">
         <is>
           <t>gears.intro.p2</t>
@@ -3527,7 +3528,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="36" customHeight="1" s="11">
+    <row r="47" ht="36" customHeight="1" s="12">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>gears.intro.p3</t>
@@ -3579,7 +3580,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="36" customHeight="1" s="11">
+    <row r="48" ht="36" customHeight="1" s="12">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>gears.step1.title</t>
@@ -3638,7 +3639,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="36" customHeight="1" s="11">
+    <row r="50" ht="36" customHeight="1" s="12">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>gears.step3.title</t>
@@ -3690,7 +3691,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="36" customHeight="1" s="11">
+    <row r="51" ht="36" customHeight="1" s="12">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>gears.kl</t>
@@ -3742,7 +3743,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="36" customHeight="1" s="11">
+    <row r="52" ht="36" customHeight="1" s="12">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>gears.naming.title</t>
@@ -3794,7 +3795,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="36" customHeight="1" s="11">
+    <row r="53" ht="36" customHeight="1" s="12">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>gears.naming.body</t>
@@ -3846,14 +3847,14 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="36" customHeight="1" s="11">
-      <c r="A54" s="12" t="inlineStr">
+    <row r="54" ht="36" customHeight="1" s="12">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  OUTPUTS</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="36" customHeight="1" s="11">
+    <row r="55" ht="36" customHeight="1" s="12">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>outputs.section_label</t>
@@ -3905,7 +3906,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="36" customHeight="1" s="11">
+    <row r="56" ht="36" customHeight="1" s="12">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>outputs.h</t>
@@ -3961,7 +3962,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="36" customHeight="1" s="11">
+    <row r="57" ht="36" customHeight="1" s="12">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>outputs.intro.p1</t>
@@ -4013,7 +4014,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="36" customHeight="1" s="11">
+    <row r="58" ht="36" customHeight="1" s="12">
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>outputs.intro.p2</t>
@@ -4065,7 +4066,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="36" customHeight="1" s="11">
+    <row r="59" ht="36" customHeight="1" s="12">
       <c r="A59" s="7" t="inlineStr">
         <is>
           <t>output.1.label</t>
@@ -4117,7 +4118,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="36" customHeight="1" s="11">
+    <row r="60" ht="36" customHeight="1" s="12">
       <c r="A60" s="7" t="inlineStr">
         <is>
           <t>output.1.title</t>
@@ -4169,7 +4170,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="36" customHeight="1" s="11">
+    <row r="61" ht="36" customHeight="1" s="12">
       <c r="A61" s="7" t="inlineStr">
         <is>
           <t>output.2.label</t>
@@ -4221,7 +4222,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="36" customHeight="1" s="11">
+    <row r="62" ht="36" customHeight="1" s="12">
       <c r="A62" s="7" t="inlineStr">
         <is>
           <t>output.2.title</t>
@@ -4305,7 +4306,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="36" customHeight="1" s="11">
+    <row r="64" ht="36" customHeight="1" s="12">
       <c r="A64" s="7" t="inlineStr">
         <is>
           <t>output.4.title</t>
@@ -4357,7 +4358,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="36" customHeight="1" s="11">
+    <row r="65" ht="36" customHeight="1" s="12">
       <c r="A65" s="7" t="inlineStr">
         <is>
           <t>output.5.title</t>
@@ -4409,7 +4410,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="36" customHeight="1" s="11">
+    <row r="66" ht="36" customHeight="1" s="12">
       <c r="A66" s="7" t="inlineStr">
         <is>
           <t>output.6.title</t>
@@ -4461,7 +4462,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="36" customHeight="1" s="11">
+    <row r="67" ht="36" customHeight="1" s="12">
       <c r="A67" s="7" t="inlineStr">
         <is>
           <t>outputs.foot</t>
@@ -4513,8 +4514,8 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="36" customHeight="1" s="11">
-      <c r="A68" s="12" t="inlineStr">
+    <row r="68" ht="36" customHeight="1" s="12">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  CASE</t>
         </is>
@@ -4527,7 +4528,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="36" customHeight="1" s="11">
+    <row r="70" ht="36" customHeight="1" s="12">
       <c r="A70" s="7" t="inlineStr">
         <is>
           <t>case.tag</t>
@@ -4579,7 +4580,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="36" customHeight="1" s="11">
+    <row r="71" ht="36" customHeight="1" s="12">
       <c r="A71" s="7" t="inlineStr">
         <is>
           <t>case.h</t>
@@ -4631,7 +4632,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="36" customHeight="1" s="11">
+    <row r="72" ht="36" customHeight="1" s="12">
       <c r="A72" s="7" t="inlineStr">
         <is>
           <t>case.sub</t>
@@ -4683,7 +4684,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="36" customHeight="1" s="11">
+    <row r="73" ht="36" customHeight="1" s="12">
       <c r="A73" s="7" t="inlineStr">
         <is>
           <t>case.kl</t>
@@ -4735,14 +4736,14 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="36" customHeight="1" s="11">
-      <c r="A74" s="12" t="inlineStr">
+    <row r="74" ht="36" customHeight="1" s="12">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  FOR</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="36" customHeight="1" s="11">
+    <row r="75" ht="36" customHeight="1" s="12">
       <c r="A75" s="7" t="inlineStr">
         <is>
           <t>for.section_label</t>
@@ -4826,7 +4827,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="36" customHeight="1" s="11">
+    <row r="77" ht="36" customHeight="1" s="12">
       <c r="A77" s="7" t="inlineStr">
         <is>
           <t>for.founders.role</t>
@@ -4878,7 +4879,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="36" customHeight="1" s="11">
+    <row r="78" ht="36" customHeight="1" s="12">
       <c r="A78" s="7" t="inlineStr">
         <is>
           <t>for.founders.body</t>
@@ -4930,7 +4931,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="36" customHeight="1" s="11">
+    <row r="79" ht="36" customHeight="1" s="12">
       <c r="A79" s="7" t="inlineStr">
         <is>
           <t>for.operators.role</t>
@@ -4982,7 +4983,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="36" customHeight="1" s="11">
+    <row r="80" ht="36" customHeight="1" s="12">
       <c r="A80" s="7" t="inlineStr">
         <is>
           <t>for.investors.role</t>
@@ -5034,14 +5035,14 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="36" customHeight="1" s="11">
-      <c r="A81" s="12" t="inlineStr">
+    <row r="81" ht="36" customHeight="1" s="12">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  LADDER</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="36" customHeight="1" s="11">
+    <row r="82" ht="36" customHeight="1" s="12">
       <c r="A82" s="7" t="inlineStr">
         <is>
           <t>ladder.section_label</t>
@@ -5093,7 +5094,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="36" customHeight="1" s="11">
+    <row r="83" ht="36" customHeight="1" s="12">
       <c r="A83" s="7" t="inlineStr">
         <is>
           <t>ladder.h</t>
@@ -5149,7 +5150,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="36" customHeight="1" s="11">
+    <row r="84" ht="36" customHeight="1" s="12">
       <c r="A84" s="7" t="inlineStr">
         <is>
           <t>ladder.sub</t>
@@ -5233,7 +5234,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="36" customHeight="1" s="11">
+    <row r="86" ht="36" customHeight="1" s="12">
       <c r="A86" s="7" t="inlineStr">
         <is>
           <t>ladder.step2.title</t>
@@ -5285,7 +5286,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="36" customHeight="1" s="11">
+    <row r="87" ht="36" customHeight="1" s="12">
       <c r="A87" s="7" t="inlineStr">
         <is>
           <t>ladder.step3.title</t>
@@ -5337,7 +5338,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="36" customHeight="1" s="11">
+    <row r="88" ht="36" customHeight="1" s="12">
       <c r="A88" s="7" t="inlineStr">
         <is>
           <t>ladder.step4.title</t>
@@ -5421,14 +5422,14 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="36" customHeight="1" s="11">
-      <c r="A90" s="12" t="inlineStr">
+    <row r="90" ht="36" customHeight="1" s="12">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  TESTI</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="36" customHeight="1" s="11">
+    <row r="91" ht="36" customHeight="1" s="12">
       <c r="A91" s="7" t="inlineStr">
         <is>
           <t>testi.section_label</t>
@@ -5480,7 +5481,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1" s="11">
+    <row r="92" ht="36" customHeight="1" s="12">
       <c r="A92" s="7" t="inlineStr">
         <is>
           <t>testi.quote</t>
@@ -5532,7 +5533,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1" s="11">
+    <row r="93" ht="36" customHeight="1" s="12">
       <c r="A93" s="7" t="inlineStr">
         <is>
           <t>testi.attr</t>
@@ -5584,8 +5585,8 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="36" customHeight="1" s="11">
-      <c r="A94" s="12" t="inlineStr">
+    <row r="94" ht="36" customHeight="1" s="12">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  ABOUT</t>
         </is>
@@ -5598,7 +5599,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="36" customHeight="1" s="11">
+    <row r="96" ht="36" customHeight="1" s="12">
       <c r="A96" s="7" t="inlineStr">
         <is>
           <t>about.h</t>
@@ -5650,7 +5651,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="36" customHeight="1" s="11">
+    <row r="97" ht="36" customHeight="1" s="12">
       <c r="A97" s="7" t="inlineStr">
         <is>
           <t>about.letter.salutation</t>
@@ -5702,7 +5703,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="36" customHeight="1" s="11">
+    <row r="98" ht="36" customHeight="1" s="12">
       <c r="A98" s="7" t="inlineStr">
         <is>
           <t>about.sig</t>
@@ -5754,7 +5755,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="36" customHeight="1" s="11">
+    <row r="99" ht="36" customHeight="1" s="12">
       <c r="A99" s="7" t="inlineStr">
         <is>
           <t>about.belief.title</t>
@@ -5806,14 +5807,14 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="36" customHeight="1" s="11">
-      <c r="A100" s="12" t="inlineStr">
+    <row r="100" ht="36" customHeight="1" s="12">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  START</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="36" customHeight="1" s="11">
+    <row r="101" ht="36" customHeight="1" s="12">
       <c r="A101" s="7" t="inlineStr">
         <is>
           <t>start.section_label</t>
@@ -5865,7 +5866,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="36" customHeight="1" s="11">
+    <row r="102" ht="36" customHeight="1" s="12">
       <c r="A102" s="7" t="inlineStr">
         <is>
           <t>start.h</t>
@@ -5917,7 +5918,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="36" customHeight="1" s="11">
+    <row r="103" ht="36" customHeight="1" s="12">
       <c r="A103" s="7" t="inlineStr">
         <is>
           <t>start.sub</t>
@@ -5969,7 +5970,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="36" customHeight="1" s="11">
+    <row r="104" ht="36" customHeight="1" s="12">
       <c r="A104" s="7" t="inlineStr">
         <is>
           <t>start.kl</t>
@@ -6021,7 +6022,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="36" customHeight="1" s="11">
+    <row r="105" ht="36" customHeight="1" s="12">
       <c r="A105" s="7" t="inlineStr">
         <is>
           <t>form.intro</t>
@@ -6073,7 +6074,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="36" customHeight="1" s="11">
+    <row r="106" ht="36" customHeight="1" s="12">
       <c r="A106" s="7" t="inlineStr">
         <is>
           <t>form.label.name</t>
@@ -6157,7 +6158,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="36" customHeight="1" s="11">
+    <row r="108" ht="36" customHeight="1" s="12">
       <c r="A108" s="7" t="inlineStr">
         <is>
           <t>form.label.email</t>
@@ -6209,7 +6210,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="36" customHeight="1" s="11">
+    <row r="109" ht="36" customHeight="1" s="12">
       <c r="A109" s="7" t="inlineStr">
         <is>
           <t>form.label.message</t>
@@ -6261,7 +6262,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="36" customHeight="1" s="11">
+    <row r="110" ht="36" customHeight="1" s="12">
       <c r="A110" s="7" t="inlineStr">
         <is>
           <t>form.placeholder.message</t>
@@ -6313,7 +6314,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="36" customHeight="1" s="11">
+    <row r="111" ht="36" customHeight="1" s="12">
       <c r="A111" s="7" t="inlineStr">
         <is>
           <t>form.btn</t>
@@ -6366,13 +6367,13 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="12" t="inlineStr">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  CTA</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="36" customHeight="1" s="11">
+    <row r="113" ht="36" customHeight="1" s="12">
       <c r="A113" s="7" t="inlineStr">
         <is>
           <t>cta.h</t>
@@ -6424,7 +6425,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="36" customHeight="1" s="11">
+    <row r="114" ht="36" customHeight="1" s="12">
       <c r="A114" s="7" t="inlineStr">
         <is>
           <t>cta.body</t>
@@ -6476,7 +6477,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="36" customHeight="1" s="11">
+    <row r="115" ht="36" customHeight="1" s="12">
       <c r="A115" s="7" t="inlineStr">
         <is>
           <t>cta.btn.primary</t>
@@ -6528,7 +6529,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="36" customHeight="1" s="11">
+    <row r="116" ht="36" customHeight="1" s="12">
       <c r="A116" s="7" t="inlineStr">
         <is>
           <t>cta.btn.secondary</t>
@@ -6580,8 +6581,8 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="36" customHeight="1" s="11">
-      <c r="A117" s="12" t="inlineStr">
+    <row r="117" ht="36" customHeight="1" s="12">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  FOOTER</t>
         </is>
@@ -6619,7 +6620,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="36" customHeight="1" s="11">
+    <row r="119" ht="36" customHeight="1" s="12">
       <c r="A119" s="7" t="inlineStr">
         <is>
           <t>footer.col.explore</t>
@@ -6671,7 +6672,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="36" customHeight="1" s="11">
+    <row r="120" ht="36" customHeight="1" s="12">
       <c r="A120" s="7" t="inlineStr">
         <is>
           <t>footer.col.contact</t>
@@ -6723,7 +6724,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="26" customHeight="1" s="12">
       <c r="A121" s="7" t="inlineStr">
         <is>
           <t>footer.copyright</t>
@@ -6775,7 +6776,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="65" customHeight="1" s="12">
       <c r="A122" s="7" t="inlineStr">
         <is>
           <t>footer.descriptor</t>
@@ -6828,13 +6829,13 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="12" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  META</t>
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="78" customHeight="1" s="12">
       <c r="A124" s="7" t="inlineStr">
         <is>
           <t>page.title</t>
@@ -7638,12 +7639,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="11" min="1" max="1"/>
-    <col width="50" customWidth="1" style="11" min="2" max="2"/>
-    <col width="80" customWidth="1" style="11" min="3" max="3"/>
-    <col width="50" customWidth="1" style="11" min="4" max="4"/>
-    <col width="80" customWidth="1" style="11" min="5" max="5"/>
-    <col width="40" customWidth="1" style="11" min="6" max="6"/>
+    <col width="10" customWidth="1" style="12" min="1" max="1"/>
+    <col width="50" customWidth="1" style="12" min="2" max="2"/>
+    <col width="80" customWidth="1" style="12" min="3" max="3"/>
+    <col width="50" customWidth="1" style="12" min="4" max="4"/>
+    <col width="80" customWidth="1" style="12" min="5" max="5"/>
+    <col width="40" customWidth="1" style="12" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7678,7 +7679,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="54" customHeight="1" s="11">
+    <row r="2" ht="54" customHeight="1" s="12">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>en</t>
@@ -7710,7 +7711,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="54" customHeight="1" s="11">
+    <row r="3" ht="54" customHeight="1" s="12">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>de</t>
@@ -7742,7 +7743,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="54" customHeight="1" s="11">
+    <row r="4" ht="54" customHeight="1" s="12">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>fr</t>
@@ -7774,7 +7775,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1" s="11">
+    <row r="5" ht="54" customHeight="1" s="12">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>nl</t>
@@ -7806,7 +7807,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1" s="11">
+    <row r="6" ht="54" customHeight="1" s="12">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>zh</t>
@@ -7838,7 +7839,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1" s="11">
+    <row r="7" ht="54" customHeight="1" s="12">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>vi</t>
@@ -7884,15 +7885,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="11" min="1" max="1"/>
-    <col width="12" customWidth="1" style="11" min="2" max="2"/>
-    <col width="30" customWidth="1" style="11" min="3" max="4"/>
-    <col width="45" customWidth="1" style="11" min="5" max="5"/>
-    <col width="14" customWidth="1" style="11" min="6" max="7"/>
-    <col width="12" customWidth="1" style="11" min="8" max="9"/>
+    <col width="10" customWidth="1" style="12" min="1" max="1"/>
+    <col width="12" customWidth="1" style="12" min="2" max="2"/>
+    <col width="30" customWidth="1" style="12" min="3" max="4"/>
+    <col width="45" customWidth="1" style="12" min="5" max="5"/>
+    <col width="14" customWidth="1" style="12" min="6" max="7"/>
+    <col width="12" customWidth="1" style="12" min="8" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="11">
+    <row r="1" ht="28" customHeight="1" s="12">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>language</t>
@@ -7939,7 +7940,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" s="11">
+    <row r="2" ht="28" customHeight="1" s="12">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>en</t>
@@ -7986,7 +7987,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" s="11">
+    <row r="3" ht="28" customHeight="1" s="12">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>de</t>
@@ -8033,7 +8034,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" s="11">
+    <row r="4" ht="28" customHeight="1" s="12">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>fr</t>
@@ -8080,7 +8081,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" s="11">
+    <row r="5" ht="28" customHeight="1" s="12">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>nl</t>
@@ -8127,7 +8128,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" s="11">
+    <row r="6" ht="28" customHeight="1" s="12">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>zh</t>
@@ -8174,7 +8175,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" s="11">
+    <row r="7" ht="28" customHeight="1" s="12">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>vi</t>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -997,9 +997,9 @@
           <t>fr</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>draft</t>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1044,9 +1044,9 @@
           <t>nl</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>draft</t>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1091,9 +1091,9 @@
           <t>zh-Hans</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>draft</t>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Livrables</t>
+          <t>Résultats</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>成果</t>
+          <t>交付成果</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Case Study</t>
+          <t>Casestudy</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>关于</t>
+          <t>关于我们</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1897,17 +1897,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Discutons</t>
+          <t>Parlez à GKIM</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Contact opnemen</t>
+          <t>Neem contact op met GKIM</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>联系我们</t>
+          <t>联系 GKIM</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1951,22 +1951,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Business-System-Design</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Conception de systèmes métier</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>Business System Design</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Conception de systèmes</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Systeem Ontwerp</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>商业系统设计</t>
+          <t>业务系统设计</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2003,22 +2003,22 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Gestalten Sie Ihr KI-natives Geschäft</t>
+          <t>Gestalten Sie Ihr KI-natives Unternehmen</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Concevez votre entreprise native IA</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ontwerp uw AI-native bedrijf</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>设计您的AI原生企业</t>
+          <t>设计您的 AI 原生业务</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2055,22 +2055,22 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Wettbewerbsvorteil ist nicht länger strategisch. Er ist strukturell.</t>
+          <t>Wettbewerbsvorteil ist nicht mehr strategisch. Er ist strukturell.</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>L'avantage compétitif n'est plus stratégique. Il est structurel.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Competitief voordeel is niet langer strategisch. Het is structureel.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>竞争优势不再是战略问题，而是结构问题。</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -2107,22 +2107,22 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Wir definieren die fehlende Schicht zwischen Strategie und Technik — wie Ihr Geschäft tatsächlich als System funktioniert, das Wert schafft.</t>
+          <t>Wir definieren die fehlende Ebene zwischen Strategie und Entwicklung — wie Ihr Unternehmen als System tatsächlich funktioniert, um Wert zu schaffen.</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Nous définissons la couche manquante entre la stratégie et l'ingénierie — comment votre entreprise fonctionne réellement en tant que système conçu pour créer de la valeur.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>We definiëren de ontbrekende laag tussen strategie en engineering — hoe uw bedrijf daadwerkelijk als een systeem werkt dat waarde creëert.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>我们定义了战略与工程之间缺失的层次——您的业务如何作为一个系统运作，以创造价值。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -2164,17 +2164,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Discutons</t>
+          <t>Parlez à GKIM</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Contact opnemen</t>
+          <t>Neem contact op met GKIM</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>联系我们</t>
+          <t>联系 GKIM</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Voir les livrables</t>
+          <t>Découvrez ce que vous obtenez</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Bekijk resultaten</t>
+          <t>Zie wat u krijgt</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>查看成果</t>
+          <t>了解您将获得什么</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2270,22 +2270,22 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Entworfene Business Systeme</t>
+          <t>Entworfene Business-Systeme</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Systèmes métier conçus</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Business Systems Ontworpen</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>已设计的业务系统</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -2322,22 +2322,22 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Strukturierte tägliche Transaktionen</t>
+          <t>Täglich strukturierte Transaktionen</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Transactions quotidiennes structurées</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Dagelijkse Transacties Gestructureerd</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>已结构化的日交易量</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Bereitgestellte Systeme</t>
+          <t>Gelieferte Systeme</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Systèmes livrés</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Systemen Opgeleverd</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>已交付的系统</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -2426,22 +2426,22 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Schnittstelle zwischen Strategie und Technik</t>
+          <t>Strategie- und Engineering-Schnittstelle</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Intersection stratégie et ingénierie</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Strategie &amp; Engineering Kruispunt</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>战略与工程的交汇点</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -2478,22 +2478,22 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Von Tag eins für Skalierbarkeit ausgelegt — nicht später umgestaltet.</t>
+          <t>Von Tag eins für Skalierung ausgelegt — nicht später umgestaltet.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Conçu pour l'échelle dès le premier jour — non refactorisé ultérieurement.</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ontworpen voor schaal vanaf dag één — niet later ervan afgeleid.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>从第一天起就为规模化设计——而非事后重构。</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Le Changement</t>
+          <t>Le changement</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2589,22 +2589,22 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Unternehmen beginnen anders auszusehen</t>
+          <t>Unternehmen beginnen, anders auszusehen</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Les entreprises commencent à avoir un autre aspect</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Bedrijven Zien Er Steeds Anders Uit</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>业务正在呈现不同的样貌</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>L'IA a donné à chaque entreprise la même vitesse de construction.</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>AI heeft elk bedrijf dezelfde bouwsnelheid gegeven.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>AI 为每家公司提供了相同的构建速度。</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -2693,22 +2693,22 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Aber Geschwindigkeit spielt keine Rolle, wenn das Geschäft nie richtig als System definiert wurde. Dort scheitern die meisten digitalen Unternehmen.</t>
+          <t>Aber Geschwindigkeit ist nutzlos, wenn das Unternehmen nie als System richtig definiert wurde. Hier brechen die meisten digitalen Unternehmen zusammen.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Mais la vitesse n'a pas d'importance si l'entreprise n'a jamais été correctement définie en tant que système. C'est là que la plupart des entreprises numériques échouent.</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Maar snelheid maakt niet uit als het bedrijf nooit goed als systeem is gedefinieerd. Dat is waar de meeste digitale bedrijven falen.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>但如果业务从未被恰当地定义为一个系统，速度就无关紧要。这正是大多数数字业务崩溃的地方。</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -2745,22 +2745,22 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Die Einschränkung hat sich von der Entwicklung zur Definition verschoben.</t>
+          <t>Das Engpass hat sich von der Entwicklung zur Definition verschoben.</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>La contrainte s'est déplacée du développement à la définition.</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>De beperking is verschoven van ontwikkeling — naar definitie.</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>制约因素已从开发转变为定义。</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -2804,17 +2804,20 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>La vitesse n'est pas l'avantage.
+La conception l'est.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Snelheid is niet het voordeel.
+Ontwerp is.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>速度不是优势。
+设计才是。</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -2848,7 +2851,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Die meisten Unternehmen entdecken Probleme erst nach der Entwicklung</t>
+          <t>Die meisten Unternehmen entdecken Probleme erst nach dem Bau</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>La plupart des entreprises découvrent ce qui ne va pas après avoir construit</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>De meeste bedrijven ontdekken wat er mis is nadat zij het hebben gebouwd</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>大多数公司在构建后才发现问题所在</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2883,6 +2901,21 @@
           <t>Anforderungen sind unvollständig, bevor die erste Codezeile geschrieben wird</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Les exigences sont incomplètes avant la première ligne de code</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Vereisten zijn onvolledig voordat de eerste regel code wordt geschreven</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>在编写第一行代码前，需求就不完整</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>Các yêu cầu không hoàn chỉnh trước khi viết dòng mã đầu tiên</t>
@@ -2915,6 +2948,21 @@
           <t>Die Logik ist über Teams und Systeme hinweg inkonsistent</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>La logique est incohérente entre les équipes et les systèmes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Logica is inconsistent tussen teams en systemen</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>逻辑在团队和系统间不一致</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Logic không nhất quán trên các team và hệ thống</t>
@@ -2944,7 +2992,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stakeholder bleiben misaligned, bis die Umsetzung dies aufdeckt</t>
+          <t>Stakeholder bleiben uneinig, bis die Umsetzung es offenbart</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Les parties prenantes restent désalignées jusqu'à ce que l'exécution l'expose</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Stakeholders blijven niet aligned totdat uitvoering dit blootlegt</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>直到执行暴露问题，利益相关者才保持一致</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2976,7 +3039,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Validierung erfolgt durch Entwicklung statt vorher</t>
+          <t>Validierung erfolgt durch Bau statt davor</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>La validation se fait par la construction plutôt qu'avant</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Validatie vindt plaats door te bouwen in plaats van daarvoor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>验证是通过构建而非在构建前进行</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3018,17 +3096,17 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Le principe fondamental de GEARS™</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Het kernprincipe van GEARS™</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ 的核心原则</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -3070,17 +3148,17 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>L'IA implémente la structure, non l'intention. Les modèles commerciaux doivent être exprimés comme des hiérarchies explicites.</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>AI implementeert structuur, niet intentie. Businessmodellen moeten worden uitgedrukt als expliciete hiërarchieën.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>AI 实现结构，而非意图。业务模式必须表达为明确的层级。</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -3181,17 +3259,17 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>L'entreprise native IA</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Het AI-native Bedrijf</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>AI 原生业务</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -3228,22 +3306,22 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>KI wirft berechtigte Fragen auf. Was passiert mit den Menschen in diesen Unternehmen? Was erleben Kunden? Was bedeutet es für Investoren? Die Antwort hängt vollständig davon ab, wie das System gestaltet ist.</t>
+          <t>KI wirft berechtigte Fragen auf. Was passiert mit den Menschen in diesen Unternehmen? Was erleben Kunden? Was bedeutet es für Investoren? Die Antwort hängt ganz davon ab, wie das System gestaltet ist.</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>L'IA soulève des questions légitimes. Qu'advient-il des personnes au sein de ces entreprises ? Qu'expérimentent les clients ? Qu'est-ce que cela signifie pour ceux qui investissent ? La réponse dépend entièrement de la conception du système.</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>AI roept rechtmatige vragen op. Wat gebeurt er met de mensen in deze bedrijven? Wat ervaren klanten? Wat betekent het voor degenen die investeren? Het antwoord hangt volledig af van hoe het systeem is ontworpen.</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>AI 提出了合理的问题。这些业务内部的人会发生什么？客户会体验到什么？这对投资者意味着什么？答案完全取决于系统的设计方式。</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -3282,22 +3360,25 @@
       <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Nicht bessere Software.
-Ein besser gestaltetes Geschäft.</t>
+Ein bessser gestaltetes Unternehmen.</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Pas un meilleur logiciel.
+Une entreprise mieux conçue.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Niet betere software.
+Een beter ontworpen bedrijf.</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>不是更好的软件。
+而是设计更好的业务。</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -3343,22 +3424,22 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>GEARS™ — Business-gesteuertes System Design</t>
+          <t>GEARS™ — Business-gesteuertes System-Design</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ — Conception de systèmes dirigée par l'entreprise</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ — Business-Led System Design</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ — 业务驱动的系统设计</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -3395,22 +3476,22 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Definieren Sie das System, bevor Sie es aufbauen</t>
+          <t>Definieren Sie das System, bevor Sie es bauen</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Définissez le système avant de le construire</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Definieer het Systeem Voordat U Het Bouwt</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>在构建前定义系统</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -3447,22 +3528,22 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>GEARS™ ist die Methode, die GKIM verwendet, um Geschäftsideen in funktionierende Geschäftsmaschinen umzuwandeln.</t>
+          <t>GEARS™ ist die Methode, die GKIM verwendet, um Geschäftsideen in funktionierende Business-Engines umzuwandeln.</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ est la méthode que GKIM utilise pour transformer les idées commerciales en moteurs commerciaux fonctionnels.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ is de methode die GKIM gebruikt om bedrijfsideeën in functionerende bedrijfsmotoren om te zetten.</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ 是 GKIM 用来将业务创意转化为运行的业务引擎的方法。</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -3499,22 +3580,22 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Sie beginnt nicht mit Features. Sie beginnt damit: wie das Geschäft tatsächlich arbeiten muss, um Wert zu schaffen.</t>
+          <t>Es beginnt nicht mit Features. Es beginnt mit: Wie das Unternehmen tatsächlich funktionieren muss, um Wert zu schaffen.</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Elle ne commence pas par les fonctionnalités. Elle commence par : comment l'entreprise doit réellement fonctionner pour créer de la valeur.</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Het begint niet met features. Het begint met: hoe het bedrijf daadwerkelijk moet werken om waarde te creëren.</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>它不从功能开始，而是从以下问题开始：业务必须如何实际运作以创造价值。</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
@@ -3551,22 +3632,22 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Jedes Zahnrad ist eine benannte Einheit der Wertschöpfung — definiert durch das, was es produziert, nicht wie es arbeitet.</t>
+          <t>Jedes Zahnrad ist eine benannte Einheit der Wertschöpfung — definiert durch das, was es produziert, nicht wie es funktioniert.</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Chaque engrenage est une unité nommée de création de valeur — définie par ce qu'elle produit, non par son fonctionnement.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Elk tandwiel is een benoemde eenheid van waardecreatie — gedefinieerd door wat het produceert, niet hoe het werkt.</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>每个齿轮是一个具名的价值创造单元——由它产生什么来定义，而非如何操作。</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -3603,22 +3684,22 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Erkunden — Definieren Sie die Geschäftsmaschine</t>
+          <t>Entdecken — Definieren Sie die Business-Engine</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Découvrir — Définir le moteur commercial</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ontdekken — Definieer de Bedrijfsmotor</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>发现——定义业务引擎</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -3662,22 +3743,22 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Liefern — Baureife Outputs</t>
+          <t>Liefern — Build-ready Outputs</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Livrer — Résultats prêts à la construction</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Opleveren — Build-Ready Resultaten</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>交付——可构建的成果</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -3719,17 +3800,17 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ ne s'arrête pas à l'insight. Il produit la structure requise pour construire.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ stopt niet bij inzicht. Het produceert de structuur die nodig is om te bouwen.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ 不仅仅提供洞见，它还提供构建所需的结构。</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -3766,22 +3847,22 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Jedes Zahnrad wird mit einem Verb und einem Substantiv benannt. Präzise.</t>
+          <t>Jedes Zahnrad ist mit einem Verb und einem Nomen benannt. Präzise.</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Chaque engrenage est nommé avec un verbe et un nom. Précisément.</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Elk tandwiel wordt benoemd met een werkwoord en een zelfstandig naamwoord. Precies.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>每个齿轮都用动词和名词精确命名。</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
@@ -3818,22 +3899,22 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Ein Zahnradname ist ein Vertrag. Er erklärt, was das Zahnrad tut und worauf es einwirkt. Vage Namen verbergen Komplexität. Präzise Namen machen das System lesbar — und daher baubar.</t>
+          <t>Ein Zahnradname ist ein Vertrag. Er erklärt, was das Zahnrad tut und worum es sich kümmert. Vage Namen verbergen Komplexität. Präzise Namen machen das System verständlich — und daher baubar.</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Un nom d'engrenage est un contrat. Il déclare ce que l'engrenage fait et sur quoi il agit. Les noms vagues cachent la complexité. Les noms précis rendent le système lisible — et donc constructible.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Een tandwielnaam is een contract. Het verklaart wat het tandwiel doet en waarop het inwerkt. Vage namen verbergen complexiteit. Nauwkeurige namen maken het systeem leesbaar — en dus bouwbaar.</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>齿轮名称是一份契约。它声明齿轮做什么以及作用于什么。模糊的名称隐藏复杂性，精确的名称使系统清晰易懂——因此也可构建。</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -3877,22 +3958,22 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Was Sie wirklich bekommen</t>
+          <t>Was Sie wirklich erhalten</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ce que vous obtenez réellement</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Wat U Daadwerkelijk Krijgt</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>您实际获得的</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
@@ -3930,23 +4011,26 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Nicht Beratung.
+          <t>Nicht beratend.
 Produktion.</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Pas du conseil.
+De la production.</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Geen advies.
+Productie.</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>不是咨询建议。
+而是生产成果。</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -3985,22 +4069,22 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Jedes Projekt erzeugt eine Reihe verbundener Outputs, die zusammen definieren, wie Ihr Geschäft als System funktioniert.</t>
+          <t>Jedes Engagement produziert eine Reihe verbundener Outputs, die zusammen definieren, wie Ihr Unternehmen als System funktioniert.</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Chaque engagement produit un ensemble de résultats connectés qui définissent ensemble comment votre entreprise fonctionne en tant que système.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Elke samenwerking produceert een set verbonden resultaten die tezamen definiëren hoe uw bedrijf als een systeem werkt.</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>每次合作都产生一套相互关联的成果，共同定义您的业务如何作为一个系统运作。</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -4042,17 +4126,17 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>La hiérarchie est la source de vérité. Tout le reste en est une projection.</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>De hiërarchie is de bron van waarheid. Al het overige is een projectie ervan.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>层级是事实的唯一来源，其他一切都是它的投影。</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
@@ -4094,17 +4178,17 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Résultat 01 — Carte des capacités</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Resultaat 01 — Capability Map</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>成果 01 — 能力地图</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -4141,22 +4225,22 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Definition der Geschäftsmaschine</t>
+          <t>Business-Engine-Definition</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Définition du moteur commercial</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Bedrijfsmotor Definitie</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>业务引擎定义</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
@@ -4198,17 +4282,17 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Résultat 02 — Architecture de flux</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Resultaat 02 — Workflow Architecture</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>成果 02 — 工作流架构</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -4250,17 +4334,17 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Conception des processus et de l'autorité</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Proces &amp; Autoriteit Ontwerp</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>流程与权限设计</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -4292,7 +4376,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Systemlogik-Design</t>
+          <t>System-Logic-Design</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Conception de la logique système</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>System Logic Ontwerp</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>系统逻辑设计</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4334,17 +4433,17 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Spécification de construction (PRD)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Build Specification (PRD)</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>构建规范（PRD）</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
@@ -4381,22 +4480,22 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>KPIs und Observability-Design</t>
+          <t>KPIs und Observability Design</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Conception des KPI et de l'observabilité</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>KPI's &amp; Observability Ontwerp</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>KPI 与可观测性设计</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -4433,22 +4532,22 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Maschinenlesbarer Systemspec</t>
+          <t>Maschinenlesbares Systemspez</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Spécification système consommable par machine</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Machine-Consumable System Spec</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>机器可读系统规范</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
@@ -4485,22 +4584,22 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Für die meisten Teams ist es das erste Mal, dass das Geschäft zu etwas wird, das tatsächlich getestet und durchdacht werden kann.</t>
+          <t>Für die meisten Teams ist es das erste Mal, dass das Unternehmen zu etwas wird, das tatsächlich getestet und durchdacht werden kann.</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Pour la plupart des équipes, c'est la première fois que l'entreprise devient quelque chose qui peut réellement être testé et analysé.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Voor de meeste teams is het de eerste keer dat het bedrijf iets wordt dat daadwerkelijk kan worden getest en redenering kan worden toegepast.</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>对大多数团队而言，这是业务第一次成为可以真正测试和推理的东西。</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
@@ -4556,17 +4655,17 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Étude de cas phare</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Flagship Casestudy</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>旗舰案例研究</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
@@ -4603,22 +4702,22 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Gestaltung eines 1-Milliarden-Dollar-Genetik-Geschäftssystems</t>
+          <t>Gestaltung eines $1B-Genetik-Geschäftssystems</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Conception d'un système commercial en génétique d'un milliard de dollars</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Het ontwerpen van een $1B Genetica Bedrijfssysteem</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>设计一个 10 亿美元遗传学业务系统</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -4655,22 +4754,22 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Wie eine komplexe, mehrakteurige Healthcare-Plattform strukturiert wurde, um zu skalieren — bevor das Volumen ihre Schwächen enthüllte.</t>
+          <t>Wie eine komplexe, Multi-Actor-Healthcare-Plattform strukturiert wurde, um zu skalieren — bevor Volumen ihre Schwächen offenbarte.</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Comment une plateforme de soins de santé complexe et multi-acteurs a été structurée pour évoluer — avant que le volume n'expose ses faiblesses.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Hoe een complex, multi-actor gezondheidszorgplatform werd gestructureerd om te schalen — voordat volume haar zwakten blootlegde.</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>一个复杂的多方参与医疗保健平台如何被结构化以实现扩展——在流量暴露其弱点之前。</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -4707,22 +4806,22 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Das System skalierte, weil es zum Funktionieren entworfen wurde — nicht weil es iterativ in Form gebracht wurde.</t>
+          <t>Das System skalierte, weil es funktionieren sollte — nicht weil es in Form iteriert wurde.</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Le système a évolué parce qu'il a été conçu pour fonctionner — non pas parce qu'il a été itéré jusqu'à prendre forme.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Het systeem schaalde omdat het was ontworpen om te werken — niet omdat het in vorm werd geïtereerd.</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>该系统之所以扩展，是因为它被设计成可运行的——而非通过迭代被塑造成可运行的。</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -4766,22 +4865,22 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Für wen dies ist</t>
+          <t>Wer das ist</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>À qui c'est destiné</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Voor Wie Dit Is</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>这是为谁准备的</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
@@ -4813,7 +4912,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Entwickelt für Gründer, Betreiber und Investoren, die in Systemen denken.</t>
+          <t>Gebaut für Gründer, Betreiber und Investoren, die in Systemen denken.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Construit pour les fondateurs, opérateurs et investisseurs qui pensent en systèmes.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gebouwd voor ondernemers, operators en investeerders die in systemen denken.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>为以系统思维思考的创始人、运营者和投资者而生。</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4855,17 +4969,17 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Fondateurs</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ondernemers</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>创始人</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
@@ -4902,22 +5016,22 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Wandeln Sie Ideen in strukturierte, baubare Systeme um. Bauen Sie das richtige Geschäft, nicht nur schnelle Software.</t>
+          <t>Verwandeln Sie Ideen in strukturierte, baubare Systeme. Bauen Sie das richtige Unternehmen, nicht nur schnelle Software.</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Transformez les idées en systèmes structurés et constructibles. Construisez la bonne entreprise, pas juste un logiciel rapide.</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Zet ideeën om in gestructureerde, bouwbare systemen. Bouw het juiste bedrijf, niet alleen snelle software.</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>将创意转化为结构化、可构建的系统。构建正确的业务，而非仅仅快速软件。</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
@@ -4954,22 +5068,22 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Operatoren</t>
+          <t>Betreiber</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Opérateurs</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Operators</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>运营者</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -5011,17 +5125,17 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Investisseurs et capital-investissement</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Investeerders &amp; PE</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>投资者与私募股权</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
@@ -5070,17 +5184,17 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Comment nous travaillons</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Hoe We Werken</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>我们的工作方式</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -5124,17 +5238,20 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Commencez n'importe où.
+Allez aussi loin que vous le souhaitez.</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Begin overal.
+Ga zo ver als u nodig hebt.</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>从任何地方开始。
+根据需要深入推进。</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -5178,17 +5295,17 @@
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>La plupart de nos clients commencent par une seule séance. Aucun engagement au-delà de cela.</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>De meeste klanten beginnen met een enkele sessie. Geen verplichting voorbij dat.</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>大多数客户从一次会议开始，没有超越此外的承诺。</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -5223,6 +5340,21 @@
           <t>Discovery-Sitzung</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Séance de découverte</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Discovery Session</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>发现会议</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>Phiên Khám phá</t>
@@ -5257,22 +5389,22 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
+          <t>GEARS™ System-Design</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Conception de système GEARS™</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
           <t>GEARS™ System Design</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GEARS™ 系统设计</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -5309,22 +5441,22 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
+          <t>Build-Partnerschaft</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Partenariat de construction</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
           <t>Build Partnership</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>— TO BE TRANSLATED —</t>
-        </is>
-      </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>构建合作伙伴关系</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
@@ -5361,22 +5493,22 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Betreiben &amp; Weiterentwickeln</t>
+          <t>Betreiben &amp; Entwickeln</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Opérer et évoluer</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Bedrijfsvoering &amp; Evolutie</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>运营与演进</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
@@ -5411,6 +5543,21 @@
           <t>Sitzung buchen</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Réservez une séance</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Boek een sessie</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>预约会议</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>Đặt lịch phiên</t>
@@ -5452,22 +5599,22 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Vertraut von Operatoren</t>
+          <t>Vertraut von Betreibern</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Approuvé par les opérateurs</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Vertrouwd door Operators</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>值得信赖的运营者</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -5504,22 +5651,22 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>"GKIM hat mir geholfen, meine Vision zu entwickeln und sie in ein durchdachtes Geschäfts-, Produkt- und Technologieangebot umzuwandeln. Das Team hat sich bei der Umsetzung hervorgetan."</t>
+          <t>"GKIM hat mir geholfen, meine Vision zu ideensammeln und sie in ein durchdachtes Unternehmen, Produkt und Technologieangebot umzuwandeln. Das Team hat bei der Umsetzung hervorragende Leistungen erbracht."</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>« GKIM m'a aidé à réfléchir à ma vision et à la transformer en une offre commerciale, produit et technologie bien pensée. L'équipe a excellé dans l'exécution. »</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>"GKIM hielp bij het brainstormen van mijn visie en het opbouwen ervan in een goed doordacht bedrijfs-, product- en technologie-aanbod. Het team heeft zich uitstekend ingespannen bij de uitvoering."</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>"GKIM 帮助我将愿景头脑风暴并将其构建成经过深思熟虑的业务、产品和技术方案。该团队在执行方面表现出色。"</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
@@ -5561,17 +5708,17 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Fondateur et PDG</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Oprichter &amp; CEO</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>创始人兼首席执行官</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -5622,22 +5769,22 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Gebaut von jemandem, der dies schon einmal getan hat</t>
+          <t>Gebaut von jemandem, der dies schon getan hat</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Construit par quelqu'un qui a déjà fait cela</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Gebouwd door Iemand Die Dit Eerder Heeft Gedaan</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>由有过此经验的人创建</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
@@ -5674,22 +5821,22 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>An die Gründer und Führungskräfte, die die Zukunft gestalten,</t>
+          <t>An die Gründer und Führungskräfte, die die Zukunft bauen,</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Aux fondateurs et aux leaders qui construisent l'avenir,</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Aan de Oprichters en Leiders die de Toekomst Bouwen,</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>致正在打造未来的创始人和领导者，</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -5731,17 +5878,17 @@
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>— Ian Morrison</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>— Ian Morrison</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>— Ian Morrison</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
@@ -5783,17 +5930,17 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ce qui rend GKIM différent</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Wat Maakt GKIM Anders</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>是什么使 GKIM 与众不同</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -5842,17 +5989,17 @@
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Parlez à GKIM</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Neem Contact Op Met GKIM</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>联系 GKIM</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -5889,22 +6036,22 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Bevor Sie bauen oder skalieren, verstehen Sie, wie Ihr Geschäft tatsächlich funktioniert.</t>
+          <t>Bevor Sie bauen oder skalieren, verstehen Sie, wie Ihr Unternehmen wirklich funktioniert.</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Avant de construire ou de développer, comprenez comment votre entreprise fonctionne réellement.</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Voordat u bouwt of schaalt, begrijpt u hoe uw bedrijf daadwerkelijk werkt.</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>在构建或扩展前，了解您的业务实际运作方式。</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
@@ -5946,17 +6093,17 @@
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ce n'est pas un appel de vente. C'est une séance de travail pour comprendre votre modèle commercial, explorer comment le système fonctionne actuellement, et identifier les lacunes, les risques et les hypothèses.</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Dit is geen verkoopgesprek. Het is een werkzitting om uw bedrijfsmodel te begrijpen, de huidige werking van het systeem te onderzoeken en hiaten, risico's en aannames te identificeren.</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>这不是销售电话，而是一次工作会议，旨在了解您的商业模式，探索系统当前的运作方式，并识别差距、风险和假设。</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
@@ -5993,22 +6140,22 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Klarheit ersetzt Annahmen.</t>
+          <t>Klarheit ersetzt Annahme.</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>La clarté remplace l'hypothèse.</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Helderheid vervangt aanname.</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>清晰取代假设。</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
@@ -6045,22 +6192,22 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Erzählen Sie uns, was Sie bauen, wo Sie sich auf der Reise befinden und was unklar oder nicht funktionierend wirkt.</t>
+          <t>Sagen Sie uns, was Sie bauen, wo Sie sich auf der Reise befinden und was unklar oder nicht funktionierend wirkt.</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Dites-nous ce que vous construisez, où vous en êtes dans le parcours, et ce qui vous semble peu clair ou ne fonctionne pas.</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Vertel ons wat u bouwt, waar u zich in de reis bevindt en wat onduidelijk is of niet werkt.</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>告诉我们您正在构建什么，您在历程中处于何位置，以及什么感觉不清楚或不起作用。</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
@@ -6112,7 +6259,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -6147,6 +6294,21 @@
           <t>Unternehmen</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Entreprise</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Bedrijf</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>Công ty</t>
@@ -6196,7 +6358,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>邮箱</t>
+          <t>电子邮件</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -6238,17 +6400,17 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Qu'êtes-vous en train de construire ou qu'est-ce qui ne fonctionne pas ?</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Wat bouwt u of wat werkt niet?</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>您在构建什么或什么不起作用？</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
@@ -6290,17 +6452,17 @@
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Partagez autant ou aussi peu que vous le souhaitez...</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Deel zoveel of zo weinig als je wilt...</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>尽可能多或少地分享……</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
@@ -6342,17 +6504,17 @@
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Réservez une séance</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Boek een Sessie</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>预约会议</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
@@ -6396,22 +6558,22 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Gestalten Sie das Geschäft, bevor Sie es bauen</t>
+          <t>Gestalten Sie das Unternehmen, bevor Sie es bauen</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Concevez l'entreprise avant de la construire</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Ontwerp het bedrijf voordat u het bouwt</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>在构建前设计业务</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
@@ -6453,17 +6615,17 @@
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>La plupart des équipes commencent par le code. Les meilleures équipes commencent par la clarté.</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>De meeste teams beginnen met code. De beste teams beginnen met helderheid.</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>大多数团队从代码开始，最好的团队从清晰开始。</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
@@ -6505,17 +6667,17 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Discutons</t>
+          <t>Parlez à GKIM</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Contact opnemen</t>
+          <t>Neem contact op met GKIM</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>联系我们</t>
+          <t>联系 GKIM</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6606,7 +6768,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gestalten Sie Ihr KI-natives Geschäft.</t>
+          <t>Gestalten Sie Ihr KI-natives Unternehmen.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Concevez votre entreprise native IA.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ontwerp uw AI-native bedrijf.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>设计您的 AI 原生业务。</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6648,17 +6825,17 @@
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Explorer</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Verkennen</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>探索</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
@@ -6700,17 +6877,17 @@
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>联系</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
@@ -6799,22 +6976,22 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Systemdefinition. KI-natives Business Design.</t>
+          <t>System-Definition. KI-natives Business-Design.</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>Définition du système. Conception d'entreprise native IA.</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>System definitie. AI-native bedrijfsontwerp.</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>系统定义。AI 原生业务设计。</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
@@ -6858,22 +7035,22 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>GKIM Digital — Gestalten Sie Ihr KI-natives Geschäft</t>
+          <t>GKIM Digital — Gestalten Sie Ihr KI-natives Unternehmen</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GKIM Digital — Concevez votre entreprise native IA</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GKIM Digital — Ontwerp Uw AI-Native Bedrijf</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>— TO BE TRANSLATED —</t>
+          <t>GKIM Digital — 设计您的 AI 原生业务</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
@@ -6915,7 +7092,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -6925,7 +7102,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>zh-Hans</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -6965,8 +7142,29 @@
       <c r="E126" t="inlineStr">
         <is>
           <t>GKIM Papers —
-Originäres Denken über
-KI-native Geschäftsmodelle</t>
+Originalgedanken zu
+KI-nativem Business-Design</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Documents GKIM —
+Réflexion originale sur
+la conception d'entreprise native IA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>GKIM Papers —
+Origineel denken over
+AI-native bedrijfsontwerp</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>GKIM 论文 —
+关于 AI 原生业务设计的
+原创思考</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7002,7 +7200,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Fünfzehn Papiere über fünf Themen. Geschrieben für Gründer, Operatoren und Investoren, die die Architektur der kommenden Entwicklungen verstehen möchten.</t>
+          <t>Fünfzehn Papiere in fünf Themen. Geschrieben für Gründer, Betreiber und Investoren, die die Architektur der kommenden Zukunft verstehen möchten.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Quinze documents sur cinq thèmes. Rédigés pour les fondateurs, opérateurs et investisseurs qui souhaitent comprendre l'architecture de ce qui arrive.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Vijftien papers over vijf thema's. Geschreven voor ondernemers, operators en investeerders die de architectuur van wat eraan komt willen begrijpen.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>跨越五个主题的十五篇论文。为希望理解未来架构的创始人、运营者和投资者而写。</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7042,6 +7255,21 @@
           <t>Grundlagen</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Fondations</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Fundamenten</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr">
         <is>
           <t>Nền tảng</t>
@@ -7076,7 +7304,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Was ist ein KI-natives Geschäftsmodell?</t>
+          <t>Was ist ein KI-natives Unternehmen?</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Qu'est-ce qu'une entreprise native IA ?</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Wat is een AI-Native Bedrijf?</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>什么是 AI 原生业务？</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7116,6 +7359,21 @@
           <t>3 Papiere</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>3 documents</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>3 篇论文</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
           <t>3 bài viết</t>
@@ -7150,7 +7408,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Das Argument dafür</t>
+          <t>Die Argumentation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>L'argument en faveur</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Het Geval Voor</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>支持理由</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7187,7 +7460,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Das strategische und ökonomische Argument</t>
+          <t>Das strategische und wirtschaftliche Argument</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>L'argument stratégique et économique</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Het Strategische &amp; Economische Argument</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>战略与经济论证</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7222,6 +7510,21 @@
           <t>3 Papiere</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>3 documents</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>3 篇论文</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>3 bài viết</t>
@@ -7256,7 +7559,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vertrauen und Sicherheit</t>
+          <t>Vertrauen &amp; Sicherheit</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Confiance et sécurité</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Vertrouwen &amp; Veiligheid</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>信任与安全</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7293,7 +7611,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Governance, Menschen und Verantwortung</t>
+          <t>Governance, Menschen &amp; Rechenschaftspflicht</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Gouvernance, humains et responsabilité</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Governance, Mensen &amp; Accountability</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>治理、人员与问责</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7328,6 +7661,21 @@
           <t>3 Papiere</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>3 documents</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>3 篇论文</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>3 bài viết</t>
@@ -7362,7 +7710,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Playbook für Gründer</t>
+          <t>Gründer-Playbook</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Playbook des fondateurs</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Oprichtersplaybook</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>创始人手册</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7402,6 +7765,21 @@
           <t>Praktische Überzeugung für Builder</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Conviction pratique pour les constructeurs</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Praktische Overtuiging voor Bouwers</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>构建者的实用信念</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>Quyết tâm thực tiễn cho những người xây dựng</t>
@@ -7434,6 +7812,21 @@
           <t>3 Papiere</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>3 documents</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>3 篇论文</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t>3 bài viết</t>
@@ -7468,7 +7861,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Architektur und Lebenszyklus</t>
+          <t>Architektur &amp; Lebenszyklus</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Architecture et cycle de vie</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Architectuur &amp; Levenscyclus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>架构与生命周期</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7505,7 +7913,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Wie diese Geschäftsmodelle aufgebaut sind</t>
+          <t>Wie diese Unternehmen gebaut werden</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Comment ces entreprises sont construites</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Hoe Deze Bedrijven Worden Gebouwd</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>这些业务如何被构建</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7540,6 +7963,21 @@
           <t>3 Papiere</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>3 documents</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>3 papers</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>3 篇论文</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>3 bài viết</t>
@@ -7574,7 +8012,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jedes Papier dauert 7–11 Minuten zum Lesen. Vollständige PDFs folgen in Kürze. Geschrieben aus Cambridge — nicht von einer Konferenzbühne.</t>
+          <t>Jedes Papier dauert 7–11 Minuten. Vollständige PDFs folgen in Kürze. Geschrieben aus Cambridge — nicht von einer Konferenzbühne.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Chaque document dure 7 à 11 minutes. Les PDF complets arrivent bientôt. Rédigés de Cambridge — non pas depuis une scène de conférence.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Elk paper is 7–11 minuten. Volledige PDF's binnenkort beschikbaar. Geschreven vanuit Cambridge — niet vanaf een conferentiepodum.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>每篇论文为 7-11 分钟阅读量。完整 PDF 即将推出。由剑桥撰写——而非来自会议舞台。</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7612,6 +8065,21 @@
       <c r="E144" t="inlineStr">
         <is>
           <t>GKIM Papers lesen →</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Lire les documents GKIM →</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Lees GKIM Papers →</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>阅读 GKIM 论文 →</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -1772,7 +1772,7 @@
     <row r="14" ht="36" customHeight="1" s="12">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hero.h1.part1</t>
+          <t>hero.h1.line1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hero h1 — text before the accented phrase</t>
+          <t>Hero h1 — first line</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Your business should</t>
+          <t>Partnering for success in the</t>
         </is>
       </c>
     </row>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hero h1 — yellow-highlighted phrase</t>
+          <t>Hero h1 — yellow accented phrase (second line)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>run, learn, and improve</t>
+          <t>AI-native future</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" s="12">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hero.h1.part2</t>
+          <t>hero.subtitle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hero h1 — text after the accented phrase</t>
+          <t>Hero subtitle — displayed below the main title</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>on its own.</t>
+          <t>Your business should run, learn, and improve on its own.</t>
         </is>
       </c>
     </row>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -952,7 +952,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:S137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="12" min="1" max="1"/>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>04 / The GEARS Approach</t>
+          <t>05 / The GEARS Approach</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>05 / Commercial Proof</t>
+          <t>06 / Commercial Proof</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>06 / The Human Role</t>
+          <t>07 / The Human Role</t>
         </is>
       </c>
     </row>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>03 / The GKIM View</t>
+          <t>04 / The GKIM View</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>06 / Commercial Proof</t>
+          <t>05 / Commercial Proof</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>07 / The Human Role</t>
+          <t>06 / The Human Role</t>
         </is>
       </c>
     </row>

--- a/gkim-content.xlsx
+++ b/gkim-content.xlsx
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S137"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="12" min="1" max="1"/>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Telehealth OS</t>
+          <t>Healthcare OS</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A genetics-led operating system built as integrated business architecture</t>
+          <t>Clinical workflows, compliance and patient engagement, designed as one system</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Designed from inception, not retrofitted onto legacy operations</t>
+          <t>For businesses starting out, and businesses starting over</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>01 / The Shift</t>
+          <t>The Shift</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI is changing the structure of business,</t>
+          <t>AI is Changing the Structure of Business</t>
         </is>
       </c>
     </row>
@@ -2107,11 +2107,6 @@
           <t>Section heading — second line (after line break on desktop)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>not just the software.</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="36" customHeight="1" s="12">
       <c r="A31" t="inlineStr">
@@ -2131,7 +2126,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>For decades, businesses scaled through human coordination: meetings, departments, reporting layers, and fragmented systems. Software accelerated execution, but the business itself stayed hard to design, understand, and evolve.</t>
+          <t>For decades, businesses scaled through human coordination: meetings, departments, reporting layers, and fragmented systems. Software accelerated execution, but the business operation itself stayed hard to evolve.</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2148,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI is now compressing the distance between intention and execution.</t>
+          <t>What a business knows has always lived in people's heads and disconnected systems. It can now be captured, modelled, and run.</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>The companies that win the next decade won't merely use AI tools.</t>
+          <t>The companies that win the next decade will design their businesses</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2192,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>They'll design</t>
+          <t>as</t>
         </is>
       </c>
     </row>
@@ -2239,11 +2234,6 @@
           <t>Large statement — text after the highlighted phrase</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>for their businesses.</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2695,7 +2685,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>04 / The GKIM View</t>
+          <t>The GKIM View</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3361,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>05 / Commercial Proof</t>
+          <t>Commercial Proof</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3869,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>06 / The Human Role</t>
+          <t>The Human Role</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3891,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>This is not about replacing humans.</t>
+          <t>This isn't about replacing your team.</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3913,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>It's about elevating them.</t>
+          <t>It's about accelerating them.</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3935,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AI-native business design removes friction so people can operate at their highest level of contribution. AI expands execution capacity: coordinating workflows, analysing systems, surfacing optimisation, and automating the repetitive. Humans stay where humans matter most.</t>
+          <t>AI-native business removes friction so team can operate at their highest level of contribution. AI expands execution capacity. The work gets more interesting, not less.</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3979,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Humans set the goals and direct strategy</t>
+          <t>You set the goals and direct strategy</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4023,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Humans exercise judgment on what matters</t>
+          <t>You exercise judgment on what matters</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4067,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Humans build the relationships that carry value</t>
+          <t>You build the relationships that carry value</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4111,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Humans shape the customer value being created</t>
+          <t>You shape the customer value being created</t>
         </is>
       </c>
     </row>
@@ -4165,173 +4155,384 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Humans oversee how the system evolves</t>
+          <t>You oversee how the system evolves</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FINAL CTA</t>
+          <t xml:space="preserve">  BENEFITS</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>cta.eyebrow</t>
+          <t>benefits.eyebrow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>cta</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Final CTA section eyebrow</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Design the business before you build the software</t>
+          <t>The Benefits</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>cta.h2</t>
+          <t>benefits.h2</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cta</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Final CTA heading</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Let's build your AI-native business.</t>
+          <t>What Changes When the Business is AI-Native</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>cta.btn</t>
+          <t>benefits.item1.title</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>cta</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Final CTA button label</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Book a discovery call</t>
+          <t>Quote faster</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FOOTER</t>
+          <t>benefits.item1.desc</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Because the answer isn't in one person's head.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>footer.tag</t>
+          <t>benefits.item2.title</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>footer</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Footer tagline below logo</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Designing AI-native business systems through GEARS. Define → Design → Simulate → Build → Operate → Evolve.</t>
+          <t>Grow without hiring behind it</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>footer.proof</t>
+          <t>benefits.item2.desc</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>footer</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Footer nav link — Commercial Proof section</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Commercial Proof</t>
+          <t>Capacity stops being headcount.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>footer.copy</t>
+          <t>benefits.item3.title</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>footer</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Footer copyright suffix (after © year)</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>GKIM. All rights reserved.</t>
+          <t>Change the model in a week</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>benefits.item3.desc</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>It's documented, not remembered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>benefits.item4.title</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Improve without a project</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>benefits.item4.desc</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Optimisation is continuous, not quarterly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>benefits.item5.title</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>See it live</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>benefits.item5.desc</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>benefits</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Reporting stops being a person's job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FINAL CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cta.eyebrow</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Final CTA section eyebrow</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Design the business before you build the software</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cta.h2</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Final CTA heading</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Let's build your AI-native business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>cta.btn</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Final CTA button label</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Book a discovery call</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FOOTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>footer.tag</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Footer tagline below logo</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Designing AI-native business systems through GEARS. Define → Design → Simulate → Build → Operate → Evolve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>footer.proof</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Footer nav link — Commercial Proof section</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Commercial Proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>footer.copy</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Footer copyright suffix (after © year)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>GKIM. All rights reserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>footer.tagline</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>footer</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Footer bottom-right tagline</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Design the business before you build the software.</t>
         </is>
